--- a/Greyform/Python_Application/PinAllocationBOMforPBU_T1am.xlsx
+++ b/Greyform/Python_Application/PinAllocationBOMforPBU_T1am.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MokZhiZhuan\OneDrive - WINSYS TECHNOLOGY PTE LTD\Documents\GitHub\GreyForm_UI\Greyform\Python_Application\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D631DECF-2B37-46E4-B6F4-AE18CAF6176C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{534C980F-46BD-49E5-BADD-F4C8F4ED3DF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="735" windowWidth="23235" windowHeight="15465" xr2:uid="{10577398-EA94-4D34-AF72-AAEF7879495C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{10577398-EA94-4D34-AF72-AAEF7879495C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="152">
   <si>
     <t>Wall</t>
   </si>
@@ -75,12 +74,6 @@
     <t>Stage 3</t>
   </si>
   <si>
-    <t>Wall 1</t>
-  </si>
-  <si>
-    <t>BSS.10 Glass</t>
-  </si>
-  <si>
     <t>Fitting</t>
   </si>
   <si>
@@ -108,18 +101,6 @@
     <t>Round</t>
   </si>
   <si>
-    <t>LP1S3b1</t>
-  </si>
-  <si>
-    <t>LP1S3b2</t>
-  </si>
-  <si>
-    <t>LP1S3b3</t>
-  </si>
-  <si>
-    <t>LP1S3b4</t>
-  </si>
-  <si>
     <t>Basic Wall:BSS.20mm Wall Finishes</t>
   </si>
   <si>
@@ -201,36 +182,9 @@
     <t>LP3S3a4</t>
   </si>
   <si>
-    <t>BSS.GESSI.SM</t>
-  </si>
-  <si>
-    <t>LP3S3b1</t>
-  </si>
-  <si>
-    <t>LP3S3b2</t>
-  </si>
-  <si>
-    <t>LP3S3b3</t>
-  </si>
-  <si>
-    <t>LP3S3b4</t>
-  </si>
-  <si>
     <t>BSS.HAND SHOWER SET.MASTER BATH</t>
   </si>
   <si>
-    <t>LP3S3c1</t>
-  </si>
-  <si>
-    <t>LP3S3c2</t>
-  </si>
-  <si>
-    <t>LP3S3c3</t>
-  </si>
-  <si>
-    <t>LP3S3c4</t>
-  </si>
-  <si>
     <t>TMP3S2b1</t>
   </si>
   <si>
@@ -433,6 +387,111 @@
   </si>
   <si>
     <t>BSS.TECE.AP</t>
+  </si>
+  <si>
+    <t>BSS.GOMGO.TR.GG</t>
+  </si>
+  <si>
+    <t>BSS.TECE.CONCEALED CISTERN</t>
+  </si>
+  <si>
+    <t>LP5S3a1</t>
+  </si>
+  <si>
+    <t>LP5S3a2</t>
+  </si>
+  <si>
+    <t>LP5S3a3</t>
+  </si>
+  <si>
+    <t>LP5S3b1</t>
+  </si>
+  <si>
+    <t>LP5S3b2</t>
+  </si>
+  <si>
+    <t>LP5S3b3</t>
+  </si>
+  <si>
+    <t>BSS.MIRROR CABINET.C5-MASTER BATH</t>
+  </si>
+  <si>
+    <t>LP5S3c1</t>
+  </si>
+  <si>
+    <t>LP5S3c2</t>
+  </si>
+  <si>
+    <t>LP5S3c3</t>
+  </si>
+  <si>
+    <t>LP5S3c4</t>
+  </si>
+  <si>
+    <t>LP5S3d1</t>
+  </si>
+  <si>
+    <t>LP5S3d2</t>
+  </si>
+  <si>
+    <t>LP5S3d3</t>
+  </si>
+  <si>
+    <t>LP5S3d4</t>
+  </si>
+  <si>
+    <t>BSS.BASIN CABINET.C5-MASTER BATH</t>
+  </si>
+  <si>
+    <t>LP5S3a4</t>
+  </si>
+  <si>
+    <t>LP5S3b4</t>
+  </si>
+  <si>
+    <t>LP5S3a5</t>
+  </si>
+  <si>
+    <t>BSS.FLOOR DRAIN_100</t>
+  </si>
+  <si>
+    <t>Square</t>
+  </si>
+  <si>
+    <t>LP7S3a1</t>
+  </si>
+  <si>
+    <t>LP7S3a2</t>
+  </si>
+  <si>
+    <t>LP7S3a3</t>
+  </si>
+  <si>
+    <t>LP7S3a4</t>
+  </si>
+  <si>
+    <t>LP7S3b1</t>
+  </si>
+  <si>
+    <t>LP7S3b2</t>
+  </si>
+  <si>
+    <t>LP7S3b3</t>
+  </si>
+  <si>
+    <t>LP7S3b4</t>
+  </si>
+  <si>
+    <t>LP5S3b5</t>
+  </si>
+  <si>
+    <t>LP4S3a1</t>
+  </si>
+  <si>
+    <t>LP4S3a2</t>
+  </si>
+  <si>
+    <t>BSS.GOMGO.PH.GG-6106</t>
   </si>
 </sst>
 </file>
@@ -493,7 +552,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -514,31 +573,11 @@
     </border>
     <border>
       <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="medium">
         <color indexed="64"/>
       </right>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -602,17 +641,6 @@
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -700,7 +728,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -708,82 +736,85 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -792,21 +823,28 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -1142,7 +1180,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45C9410D-7727-4F15-9679-20A483A9E846}">
-  <dimension ref="A1:L100"/>
+  <dimension ref="A1:L111"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.42578125" bestFit="1" customWidth="1"/>
@@ -1158,37 +1196,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="35"/>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
+      <c r="A1" s="38"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="36" t="s">
-        <v>96</v>
-      </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
-      <c r="L2" s="38"/>
+      <c r="A2" s="39" t="s">
+        <v>81</v>
+      </c>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="41"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -1221,635 +1259,625 @@
       <c r="K3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="6" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="39" t="s">
-        <v>12</v>
-      </c>
+      <c r="A4" s="36"/>
       <c r="B4" s="2">
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>13</v>
+        <v>117</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G4" s="2">
         <v>4</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="36"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="8" t="s">
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="36"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="33"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="2" t="s">
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="36"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="33"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="33"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="2" t="s">
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="36"/>
+      <c r="B8" s="2">
+        <v>3</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="2">
+        <v>8</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J8" s="8"/>
+      <c r="K8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L8" s="9"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="36"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J9" s="8"/>
+      <c r="K9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L9" s="9"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="36"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J10" s="8"/>
+      <c r="K10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L10" s="9"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="36"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J11" s="8"/>
+      <c r="K11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L11" s="9"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="36"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="33"/>
-      <c r="B8" s="2">
-        <v>2</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8" s="2">
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J12" s="8"/>
+      <c r="K12" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L12" s="9"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="36"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J13" s="8"/>
+      <c r="K13" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L13" s="9"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="36"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J14" s="8"/>
+      <c r="K14" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L14" s="9"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="36"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J15" s="8"/>
+      <c r="K15" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L15" s="9"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="36"/>
+      <c r="B16" s="2">
         <v>4</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I8" s="2" t="s">
+      <c r="C16" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16" s="2">
+        <v>16</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="J8" s="28"/>
-      <c r="K8" s="28"/>
-      <c r="L8" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="33"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J9" s="28"/>
-      <c r="K9" s="28"/>
-      <c r="L9" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="33"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="J10" s="28"/>
-      <c r="K10" s="28"/>
-      <c r="L10" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="33"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="J11" s="28"/>
-      <c r="K11" s="28"/>
-      <c r="L11" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="33"/>
-      <c r="B12" s="2">
-        <v>2</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G12" s="2">
-        <v>4</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="33"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J13" s="9"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="33"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="33"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="33"/>
-      <c r="B16" s="2">
-        <v>3</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E16" s="4"/>
-      <c r="F16" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G16" s="2">
-        <v>8</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="I16" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J16" s="8"/>
+      <c r="K16" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L16" s="9"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="36"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J17" s="8"/>
+      <c r="K17" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L17" s="9"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="36"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="J16" s="9"/>
-      <c r="K16" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L16" s="10"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="33"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="2" t="s">
+      <c r="J18" s="8"/>
+      <c r="K18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L18" s="9"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="36"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J17" s="9"/>
-      <c r="K17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L17" s="10"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="33"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="J18" s="9"/>
-      <c r="K18" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L18" s="10"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="33"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="J19" s="9"/>
-      <c r="K19" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L19" s="10"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L19" s="9"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="33"/>
+      <c r="A20" s="36"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2" t="s">
-        <v>27</v>
+        <v>99</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
+        <v>54</v>
+      </c>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
       <c r="H20" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="J20" s="9"/>
-      <c r="K20" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L20" s="10"/>
+        <v>103</v>
+      </c>
+      <c r="J20" s="8"/>
+      <c r="K20" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L20" s="9"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="33"/>
+      <c r="A21" s="36"/>
       <c r="B21" s="2"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
       <c r="I21" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="J21" s="9"/>
-      <c r="K21" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L21" s="10"/>
+        <v>104</v>
+      </c>
+      <c r="J21" s="8"/>
+      <c r="K21" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L21" s="9"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="33"/>
+      <c r="A22" s="11"/>
       <c r="B22" s="2"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
       <c r="I22" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="J22" s="9"/>
-      <c r="K22" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L22" s="10"/>
+        <v>105</v>
+      </c>
+      <c r="J22" s="8"/>
+      <c r="K22" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L22" s="9"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="33"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="J23" s="9"/>
-      <c r="K23" s="5" t="s">
-        <v>18</v>
+      <c r="A23" s="12"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="J23" s="21"/>
+      <c r="K23" s="15" t="s">
+        <v>16</v>
       </c>
       <c r="L23" s="10"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="33"/>
+      <c r="A24" s="36" t="s">
+        <v>36</v>
+      </c>
       <c r="B24" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E24" s="4"/>
+        <v>22</v>
+      </c>
+      <c r="E24" s="3"/>
       <c r="F24" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="G24" s="2">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I24" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L24" s="24"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" s="36"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K25" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L25" s="24"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" s="36"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L26" s="24"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" s="36"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="J24" s="9"/>
-      <c r="K24" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L24" s="10"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="33"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
-      <c r="I25" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="J25" s="9"/>
-      <c r="K25" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L25" s="10"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="33"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J26" s="9"/>
-      <c r="K26" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L26" s="10"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="33"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="J27" s="9"/>
-      <c r="K27" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L27" s="10"/>
+      <c r="K27" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L27" s="24"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="33"/>
+      <c r="A28" s="36"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="2" t="s">
-        <v>29</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
       <c r="I28" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="J28" s="9"/>
-      <c r="K28" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L28" s="10"/>
+        <v>39</v>
+      </c>
+      <c r="K28" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L28" s="24"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="33"/>
+      <c r="A29" s="36"/>
       <c r="B29" s="2"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
       <c r="I29" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="J29" s="9"/>
-      <c r="K29" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L29" s="10"/>
+        <v>40</v>
+      </c>
+      <c r="K29" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L29" s="24"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="12"/>
+      <c r="A30" s="36"/>
       <c r="B30" s="2"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
       <c r="I30" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="J30" s="9"/>
-      <c r="K30" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L30" s="10"/>
+        <v>100</v>
+      </c>
+      <c r="K30" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L30" s="24"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="12"/>
+      <c r="A31" s="37"/>
       <c r="B31" s="2"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
       <c r="I31" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="J31" s="9"/>
-      <c r="K31" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L31" s="10"/>
+        <v>101</v>
+      </c>
+      <c r="J31" s="2"/>
+      <c r="K31" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L31" s="30"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15"/>
-      <c r="J32" s="14"/>
-      <c r="K32" s="16"/>
-      <c r="L32" s="11"/>
+      <c r="A32" s="36" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="16">
+        <v>1</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="G32" s="16">
+        <v>4</v>
+      </c>
+      <c r="H32" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="I32" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="J32" s="23"/>
+      <c r="K32" s="23"/>
+      <c r="L32" s="26" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="32" t="s">
-        <v>42</v>
-      </c>
-      <c r="B33" s="2">
-        <v>1</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E33" s="4"/>
-      <c r="F33" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G33" s="2">
-        <v>8</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>29</v>
-      </c>
+      <c r="A33" s="36"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
       <c r="I33" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="K33" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L33" s="25"/>
+        <v>45</v>
+      </c>
+      <c r="J33" s="27"/>
+      <c r="K33" s="27"/>
+      <c r="L33" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="33"/>
+      <c r="A34" s="36"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
@@ -1858,15 +1886,16 @@
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="K34" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L34" s="25"/>
+        <v>46</v>
+      </c>
+      <c r="J34" s="27"/>
+      <c r="K34" s="27"/>
+      <c r="L34" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="33"/>
+      <c r="A35" s="36"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
@@ -1875,53 +1904,62 @@
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K35" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L35" s="25"/>
+        <v>47</v>
+      </c>
+      <c r="J35" s="27"/>
+      <c r="K35" s="27"/>
+      <c r="L35" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="33"/>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
+      <c r="A36" s="36"/>
+      <c r="B36" s="2">
+        <v>2</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E36" s="3"/>
+      <c r="F36" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G36" s="2">
+        <v>8</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="I36" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="K36" s="5" t="s">
-        <v>18</v>
+        <v>55</v>
+      </c>
+      <c r="K36" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="L36" s="25"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A37" s="33"/>
+      <c r="A37" s="36"/>
       <c r="B37" s="2"/>
-      <c r="C37" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>69</v>
-      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
       <c r="I37" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="K37" s="5" t="s">
-        <v>18</v>
+        <v>56</v>
+      </c>
+      <c r="K37" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="L37" s="25"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38" s="33"/>
+      <c r="A38" s="36"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
@@ -1930,15 +1968,15 @@
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
       <c r="I38" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="K38" s="5" t="s">
-        <v>18</v>
+        <v>57</v>
+      </c>
+      <c r="K38" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="L38" s="25"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39" s="33"/>
+      <c r="A39" s="36"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
@@ -1947,149 +1985,115 @@
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
       <c r="I39" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="K39" s="5" t="s">
-        <v>18</v>
+        <v>58</v>
+      </c>
+      <c r="K39" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="L39" s="25"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A40" s="34"/>
-      <c r="B40" s="2"/>
+      <c r="A40" s="36"/>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
       <c r="I40" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="J40" s="2"/>
-      <c r="K40" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L40" s="29"/>
+        <v>49</v>
+      </c>
+      <c r="K40" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L40" s="9"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A41" s="32" t="s">
-        <v>49</v>
-      </c>
-      <c r="B41" s="17">
-        <v>1</v>
-      </c>
-      <c r="C41" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="D41" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="E41" s="17"/>
-      <c r="F41" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="G41" s="17">
-        <v>4</v>
-      </c>
-      <c r="H41" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="I41" s="17" t="s">
+      <c r="A41" s="36"/>
+      <c r="I41" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="J41" s="24"/>
-      <c r="K41" s="24"/>
-      <c r="L41" s="27" t="s">
-        <v>18</v>
-      </c>
+      <c r="K41" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L41" s="9"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A42" s="33"/>
-      <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
-      <c r="H42" s="2"/>
+      <c r="A42" s="36"/>
       <c r="I42" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="J42" s="28"/>
-      <c r="K42" s="28"/>
-      <c r="L42" s="8" t="s">
-        <v>18</v>
-      </c>
+      <c r="K42" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L42" s="9"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A43" s="33"/>
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="2" t="s">
+      <c r="A43" s="37"/>
+      <c r="B43" s="13"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="13"/>
+      <c r="H43" s="13"/>
+      <c r="I43" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="J43" s="28"/>
-      <c r="K43" s="28"/>
-      <c r="L43" s="8" t="s">
-        <v>18</v>
-      </c>
+      <c r="J43" s="13"/>
+      <c r="K43" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L43" s="10"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A44" s="33"/>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2"/>
+      <c r="A44" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="B44" s="2">
+        <v>1</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E44" s="3"/>
+      <c r="F44" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G44" s="2">
+        <v>5</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="I44" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="J44" s="28"/>
-      <c r="K44" s="28"/>
-      <c r="L44" s="8" t="s">
-        <v>18</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="J44" s="27"/>
+      <c r="K44" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L44" s="9"/>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A45" s="33"/>
-      <c r="B45" s="2">
-        <v>2</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="A45" s="36"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
       <c r="E45" s="2"/>
-      <c r="F45" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G45" s="2">
-        <v>4</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>16</v>
-      </c>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
       <c r="I45" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="J45" s="28"/>
-      <c r="K45" s="28"/>
-      <c r="L45" s="8" t="s">
-        <v>18</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="J45" s="27"/>
+      <c r="K45" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L45" s="9"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A46" s="33"/>
+      <c r="A46" s="36"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
@@ -2098,16 +2102,16 @@
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
       <c r="I46" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="J46" s="28"/>
-      <c r="K46" s="28"/>
-      <c r="L46" s="8" t="s">
-        <v>18</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="J46" s="27"/>
+      <c r="K46" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L46" s="9"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A47" s="33"/>
+      <c r="A47" s="36"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
@@ -2116,16 +2120,16 @@
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
       <c r="I47" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="J47" s="28"/>
-      <c r="K47" s="28"/>
-      <c r="L47" s="8" t="s">
-        <v>18</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="J47" s="27"/>
+      <c r="K47" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L47" s="9"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A48" s="33"/>
+      <c r="A48" s="36"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
@@ -2134,146 +2138,108 @@
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
       <c r="I48" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="J48" s="28"/>
-      <c r="K48" s="28"/>
-      <c r="L48" s="8" t="s">
-        <v>18</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="J48" s="27"/>
+      <c r="K48" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L48" s="9"/>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A49" s="33"/>
-      <c r="B49" s="2">
-        <v>3</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G49" s="2">
+      <c r="A49" s="36"/>
+      <c r="I49" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="K49" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L49" s="9"/>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50" s="36"/>
+      <c r="I50" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="K50" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L50" s="9"/>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A51" s="36"/>
+      <c r="I51" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="K51" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L51" s="9"/>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A52" s="36"/>
+      <c r="C52" s="28" t="s">
+        <v>151</v>
+      </c>
+      <c r="I52" s="42" t="s">
+        <v>149</v>
+      </c>
+      <c r="K52" s="43"/>
+      <c r="L52" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A53" s="37"/>
+      <c r="B53" s="13"/>
+      <c r="C53" s="13"/>
+      <c r="D53" s="13"/>
+      <c r="E53" s="13"/>
+      <c r="F53" s="13"/>
+      <c r="G53" s="13"/>
+      <c r="H53" s="13"/>
+      <c r="I53" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="J53" s="13"/>
+      <c r="K53" s="13"/>
+      <c r="L53" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A54" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="B54" s="2">
+        <v>1</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E54" s="3"/>
+      <c r="F54" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G54" s="2">
         <v>4</v>
       </c>
-      <c r="H49" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I49" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="J49" s="28"/>
-      <c r="K49" s="28"/>
-      <c r="L49" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A50" s="33"/>
-      <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
-      <c r="I50" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="J50" s="28"/>
-      <c r="K50" s="28"/>
-      <c r="L50" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A51" s="33"/>
-      <c r="B51" s="2"/>
-      <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
-      <c r="E51" s="2"/>
-      <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="J51" s="28"/>
-      <c r="K51" s="28"/>
-      <c r="L51" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A52" s="33"/>
-      <c r="B52" s="2"/>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
-      <c r="E52" s="2"/>
-      <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
-      <c r="H52" s="2"/>
-      <c r="I52" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="J52" s="28"/>
-      <c r="K52" s="28"/>
-      <c r="L52" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A53" s="33"/>
-      <c r="B53" s="2">
-        <v>4</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E53" s="4"/>
-      <c r="F53" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G53" s="2">
-        <v>8</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="I53" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="K53" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L53" s="26"/>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A54" s="33"/>
-      <c r="B54" s="2"/>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
-      <c r="E54" s="2"/>
-      <c r="F54" s="2"/>
-      <c r="G54" s="2"/>
-      <c r="H54" s="2"/>
+      <c r="H54" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="I54" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="K54" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L54" s="26"/>
+        <v>67</v>
+      </c>
+      <c r="K54" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L54" s="25"/>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A55" s="33"/>
+      <c r="A55" s="36"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
@@ -2282,15 +2248,15 @@
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
       <c r="I55" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="K55" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L55" s="26"/>
+        <v>68</v>
+      </c>
+      <c r="K55" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L55" s="25"/>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A56" s="33"/>
+      <c r="A56" s="36"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
       <c r="D56" s="2"/>
@@ -2299,97 +2265,102 @@
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
       <c r="I56" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="K56" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L56" s="26"/>
+        <v>69</v>
+      </c>
+      <c r="K56" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L56" s="25"/>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A57" s="33"/>
+      <c r="A57" s="36"/>
+      <c r="B57" s="2"/>
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2"/>
       <c r="I57" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="K57" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L57" s="10"/>
+        <v>70</v>
+      </c>
+      <c r="K57" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L57" s="25"/>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A58" s="33"/>
+      <c r="A58" s="36"/>
+      <c r="B58" s="2"/>
+      <c r="C58" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2"/>
       <c r="I58" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="K58" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L58" s="10"/>
+        <v>119</v>
+      </c>
+      <c r="L58" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A59" s="33"/>
+      <c r="A59" s="36"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2"/>
       <c r="I59" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="K59" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L59" s="10"/>
+        <v>120</v>
+      </c>
+      <c r="L59" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A60" s="34"/>
-      <c r="B60" s="14"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
-      <c r="I60" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="J60" s="14"/>
-      <c r="K60" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="L60" s="11"/>
+      <c r="A60" s="36"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
+      <c r="E60" s="2"/>
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
+      <c r="I60" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="L60" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A61" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="B61" s="2">
-        <v>1</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E61" s="4"/>
-      <c r="F61" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G61" s="2">
-        <v>5</v>
-      </c>
-      <c r="H61" s="2" t="s">
-        <v>29</v>
-      </c>
+      <c r="A61" s="36"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
+      <c r="F61" s="2"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="2"/>
       <c r="I61" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="J61" s="28"/>
-      <c r="K61" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L61" s="10"/>
+        <v>135</v>
+      </c>
+      <c r="L61" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A62" s="33"/>
+      <c r="A62" s="36"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
       <c r="D62" s="2"/>
@@ -2398,34 +2369,36 @@
       <c r="G62" s="2"/>
       <c r="H62" s="2"/>
       <c r="I62" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="J62" s="28"/>
-      <c r="K62" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L62" s="10"/>
+        <v>137</v>
+      </c>
+      <c r="L62" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A63" s="33"/>
+      <c r="A63" s="36"/>
       <c r="B63" s="2"/>
-      <c r="C63" s="2"/>
-      <c r="D63" s="2"/>
+      <c r="C63" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="E63" s="2"/>
-      <c r="F63" s="2"/>
+      <c r="F63" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
       <c r="I63" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="J63" s="28"/>
-      <c r="K63" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L63" s="10"/>
+        <v>122</v>
+      </c>
+      <c r="L63" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A64" s="33"/>
+      <c r="A64" s="36"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
       <c r="D64" s="2"/>
@@ -2434,16 +2407,14 @@
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
       <c r="I64" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="J64" s="28"/>
-      <c r="K64" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L64" s="10"/>
+        <v>123</v>
+      </c>
+      <c r="L64" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A65" s="33"/>
+      <c r="A65" s="36"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
       <c r="D65" s="2"/>
@@ -2452,85 +2423,84 @@
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
       <c r="I65" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="J65" s="28"/>
-      <c r="K65" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L65" s="10"/>
+        <v>124</v>
+      </c>
+      <c r="L65" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A66" s="33"/>
+      <c r="A66" s="36"/>
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="2"/>
+      <c r="E66" s="2"/>
+      <c r="F66" s="2"/>
+      <c r="G66" s="2"/>
+      <c r="H66" s="2"/>
       <c r="I66" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="K66" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L66" s="10"/>
+        <v>136</v>
+      </c>
+      <c r="L66" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A67" s="33"/>
+      <c r="A67" s="36"/>
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="2"/>
+      <c r="E67" s="2"/>
+      <c r="F67" s="2"/>
+      <c r="G67" s="2"/>
+      <c r="H67" s="2"/>
       <c r="I67" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="K67" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L67" s="10"/>
+        <v>148</v>
+      </c>
+      <c r="L67" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A68" s="34"/>
-      <c r="B68" s="14"/>
-      <c r="C68" s="14"/>
-      <c r="D68" s="14"/>
-      <c r="E68" s="14"/>
-      <c r="F68" s="14"/>
-      <c r="G68" s="14"/>
-      <c r="H68" s="14"/>
-      <c r="I68" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="J68" s="14"/>
-      <c r="K68" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="L68" s="11"/>
+      <c r="A68" s="36"/>
+      <c r="B68" s="2"/>
+      <c r="C68" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G68" s="2"/>
+      <c r="H68" s="2"/>
+      <c r="I68" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="L68" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A69" s="32" t="s">
-        <v>80</v>
-      </c>
-      <c r="B69" s="2">
-        <v>1</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E69" s="4"/>
-      <c r="F69" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G69" s="2">
-        <v>4</v>
-      </c>
-      <c r="H69" s="2" t="s">
-        <v>29</v>
-      </c>
+      <c r="A69" s="36"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="2"/>
+      <c r="F69" s="2"/>
+      <c r="G69" s="2"/>
+      <c r="H69" s="2"/>
       <c r="I69" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="K69" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L69" s="26"/>
+        <v>127</v>
+      </c>
+      <c r="L69" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A70" s="33"/>
+      <c r="A70" s="36"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
       <c r="D70" s="2"/>
@@ -2539,15 +2509,14 @@
       <c r="G70" s="2"/>
       <c r="H70" s="2"/>
       <c r="I70" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="K70" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L70" s="26"/>
+        <v>128</v>
+      </c>
+      <c r="L70" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A71" s="33"/>
+      <c r="A71" s="36"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
       <c r="D71" s="2"/>
@@ -2556,270 +2525,270 @@
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
       <c r="I71" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="K71" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L71" s="26"/>
+        <v>129</v>
+      </c>
+      <c r="L71" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A72" s="34"/>
-      <c r="B72" s="14"/>
-      <c r="C72" s="14"/>
-      <c r="D72" s="14"/>
-      <c r="E72" s="14"/>
-      <c r="F72" s="14"/>
-      <c r="G72" s="14"/>
-      <c r="H72" s="14"/>
+      <c r="A72" s="36"/>
+      <c r="B72" s="2"/>
+      <c r="C72" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G72" s="2"/>
+      <c r="H72" s="2"/>
       <c r="I72" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="J72" s="14"/>
-      <c r="K72" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="L72" s="11"/>
+        <v>130</v>
+      </c>
+      <c r="L72" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A73" s="32" t="s">
-        <v>89</v>
-      </c>
-      <c r="B73" s="17">
-        <v>1</v>
-      </c>
-      <c r="C73" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="D73" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="E73" s="18"/>
-      <c r="F73" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="G73" s="17">
-        <v>8</v>
-      </c>
-      <c r="H73" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="I73" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="J73" s="19"/>
-      <c r="K73" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="L73" s="23"/>
+      <c r="A73" s="36"/>
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="2"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="2"/>
+      <c r="G73" s="2"/>
+      <c r="H73" s="2"/>
+      <c r="I73" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="L73" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A74" s="33"/>
+      <c r="A74" s="36"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
       <c r="D74" s="2"/>
-      <c r="E74" s="4"/>
+      <c r="E74" s="2"/>
       <c r="F74" s="2"/>
-      <c r="G74" s="4"/>
+      <c r="G74" s="2"/>
       <c r="H74" s="2"/>
       <c r="I74" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="J74" s="9"/>
-      <c r="K74" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L74" s="10"/>
+        <v>132</v>
+      </c>
+      <c r="L74" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A75" s="33"/>
-      <c r="B75" s="2"/>
-      <c r="C75" s="2"/>
-      <c r="D75" s="2"/>
-      <c r="E75" s="4"/>
-      <c r="F75" s="2"/>
-      <c r="G75" s="4"/>
-      <c r="H75" s="2"/>
-      <c r="I75" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="J75" s="9"/>
-      <c r="K75" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L75" s="10"/>
+      <c r="A75" s="37"/>
+      <c r="B75" s="13"/>
+      <c r="D75" s="13"/>
+      <c r="E75" s="13"/>
+      <c r="F75" s="13"/>
+      <c r="G75" s="13"/>
+      <c r="H75" s="13"/>
+      <c r="I75" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="J75" s="13"/>
+      <c r="L75" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A76" s="33"/>
-      <c r="B76" s="2"/>
-      <c r="C76" s="2"/>
-      <c r="D76" s="2"/>
-      <c r="E76" s="4"/>
-      <c r="F76" s="2"/>
-      <c r="G76" s="4"/>
-      <c r="H76" s="2"/>
-      <c r="I76" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="J76" s="9"/>
-      <c r="K76" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L76" s="10"/>
+      <c r="A76" s="35" t="s">
+        <v>74</v>
+      </c>
+      <c r="B76" s="16">
+        <v>1</v>
+      </c>
+      <c r="C76" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D76" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="E76" s="17"/>
+      <c r="F76" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="G76" s="16">
+        <v>8</v>
+      </c>
+      <c r="H76" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="I76" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="J76" s="18"/>
+      <c r="K76" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="L76" s="22"/>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A77" s="33"/>
+      <c r="A77" s="36"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
       <c r="D77" s="2"/>
-      <c r="E77" s="4"/>
+      <c r="E77" s="3"/>
       <c r="F77" s="2"/>
-      <c r="G77" s="4"/>
+      <c r="G77" s="3"/>
       <c r="H77" s="2"/>
       <c r="I77" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="J77" s="9"/>
-      <c r="K77" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L77" s="10"/>
+        <v>109</v>
+      </c>
+      <c r="J77" s="8"/>
+      <c r="K77" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L77" s="9"/>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A78" s="33"/>
+      <c r="A78" s="36"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
       <c r="D78" s="2"/>
-      <c r="E78" s="4"/>
+      <c r="E78" s="3"/>
       <c r="F78" s="2"/>
-      <c r="G78" s="4"/>
+      <c r="G78" s="3"/>
       <c r="H78" s="2"/>
       <c r="I78" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="J78" s="9"/>
-      <c r="K78" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L78" s="10"/>
+        <v>110</v>
+      </c>
+      <c r="J78" s="8"/>
+      <c r="K78" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L78" s="9"/>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A79" s="33"/>
+      <c r="A79" s="36"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
       <c r="D79" s="2"/>
-      <c r="E79" s="4"/>
+      <c r="E79" s="3"/>
       <c r="F79" s="2"/>
-      <c r="G79" s="4"/>
+      <c r="G79" s="3"/>
       <c r="H79" s="2"/>
       <c r="I79" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="J79" s="9"/>
-      <c r="K79" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L79" s="10"/>
+        <v>111</v>
+      </c>
+      <c r="J79" s="8"/>
+      <c r="K79" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L79" s="9"/>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A80" s="34"/>
-      <c r="B80" s="15"/>
-      <c r="C80" s="15"/>
-      <c r="D80" s="15"/>
-      <c r="E80" s="21"/>
-      <c r="F80" s="15"/>
-      <c r="G80" s="21"/>
-      <c r="H80" s="15"/>
-      <c r="I80" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="J80" s="22"/>
-      <c r="K80" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="L80" s="11"/>
+      <c r="A80" s="36"/>
+      <c r="B80" s="2"/>
+      <c r="C80" s="2"/>
+      <c r="D80" s="2"/>
+      <c r="E80" s="3"/>
+      <c r="F80" s="2"/>
+      <c r="G80" s="3"/>
+      <c r="H80" s="2"/>
+      <c r="I80" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="J80" s="8"/>
+      <c r="K80" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L80" s="9"/>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A81" s="32" t="s">
-        <v>90</v>
-      </c>
-      <c r="B81" s="2">
-        <v>1</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E81" s="4"/>
-      <c r="F81" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G81" s="2">
-        <v>14</v>
-      </c>
-      <c r="H81" s="2" t="s">
-        <v>29</v>
-      </c>
+      <c r="A81" s="36"/>
+      <c r="B81" s="2"/>
+      <c r="C81" s="2"/>
+      <c r="D81" s="2"/>
+      <c r="E81" s="3"/>
+      <c r="F81" s="2"/>
+      <c r="G81" s="3"/>
+      <c r="H81" s="2"/>
       <c r="I81" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="K81" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L81" s="26"/>
+        <v>113</v>
+      </c>
+      <c r="J81" s="8"/>
+      <c r="K81" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L81" s="9"/>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A82" s="33"/>
+      <c r="A82" s="36"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
       <c r="D82" s="2"/>
-      <c r="E82" s="2"/>
+      <c r="E82" s="3"/>
       <c r="F82" s="2"/>
-      <c r="G82" s="2"/>
+      <c r="G82" s="3"/>
       <c r="H82" s="2"/>
       <c r="I82" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="K82" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L82" s="26"/>
+        <v>114</v>
+      </c>
+      <c r="J82" s="8"/>
+      <c r="K82" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L82" s="9"/>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A83" s="33"/>
-      <c r="B83" s="2"/>
-      <c r="C83" s="2"/>
-      <c r="D83" s="2"/>
-      <c r="E83" s="2"/>
-      <c r="F83" s="2"/>
-      <c r="G83" s="2"/>
-      <c r="H83" s="2"/>
-      <c r="I83" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="K83" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L83" s="26"/>
+      <c r="A83" s="37"/>
+      <c r="B83" s="14"/>
+      <c r="C83" s="14"/>
+      <c r="D83" s="14"/>
+      <c r="E83" s="20"/>
+      <c r="F83" s="14"/>
+      <c r="G83" s="20"/>
+      <c r="H83" s="14"/>
+      <c r="I83" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="J83" s="21"/>
+      <c r="K83" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L83" s="10"/>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A84" s="33"/>
-      <c r="B84" s="2"/>
-      <c r="C84" s="2"/>
-      <c r="D84" s="2"/>
-      <c r="E84" s="2"/>
-      <c r="F84" s="2"/>
-      <c r="G84" s="2"/>
-      <c r="H84" s="2"/>
+      <c r="A84" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="B84" s="2">
+        <v>1</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E84" s="3"/>
+      <c r="F84" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G84" s="2">
+        <v>14</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="I84" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="K84" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L84" s="26"/>
+        <v>82</v>
+      </c>
+      <c r="K84" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L84" s="25"/>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" s="33"/>
@@ -2831,12 +2800,12 @@
       <c r="G85" s="2"/>
       <c r="H85" s="2"/>
       <c r="I85" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="K85" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L85" s="26"/>
+        <v>83</v>
+      </c>
+      <c r="K85" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L85" s="25"/>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" s="33"/>
@@ -2848,12 +2817,12 @@
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
       <c r="I86" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="K86" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L86" s="26"/>
+        <v>84</v>
+      </c>
+      <c r="K86" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L86" s="25"/>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" s="33"/>
@@ -2865,31 +2834,29 @@
       <c r="G87" s="2"/>
       <c r="H87" s="2"/>
       <c r="I87" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="K87" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L87" s="26"/>
+        <v>85</v>
+      </c>
+      <c r="K87" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L87" s="25"/>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" s="33"/>
       <c r="B88" s="2"/>
-      <c r="C88" s="31" t="s">
-        <v>117</v>
-      </c>
+      <c r="C88" s="2"/>
       <c r="D88" s="2"/>
       <c r="E88" s="2"/>
       <c r="F88" s="2"/>
       <c r="G88" s="2"/>
       <c r="H88" s="2"/>
       <c r="I88" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="K88" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L88" s="26"/>
+        <v>87</v>
+      </c>
+      <c r="K88" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L88" s="25"/>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" s="33"/>
@@ -2901,12 +2868,12 @@
       <c r="G89" s="2"/>
       <c r="H89" s="2"/>
       <c r="I89" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="K89" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L89" s="26"/>
+        <v>88</v>
+      </c>
+      <c r="K89" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L89" s="25"/>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" s="33"/>
@@ -2918,29 +2885,31 @@
       <c r="G90" s="2"/>
       <c r="H90" s="2"/>
       <c r="I90" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="K90" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L90" s="26"/>
+        <v>89</v>
+      </c>
+      <c r="K90" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L90" s="25"/>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" s="33"/>
       <c r="B91" s="2"/>
-      <c r="C91" s="2"/>
+      <c r="C91" s="28" t="s">
+        <v>102</v>
+      </c>
       <c r="D91" s="2"/>
       <c r="E91" s="2"/>
       <c r="F91" s="2"/>
       <c r="G91" s="2"/>
       <c r="H91" s="2"/>
       <c r="I91" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="K91" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L91" s="26"/>
+        <v>86</v>
+      </c>
+      <c r="K91" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L91" s="25"/>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" s="33"/>
@@ -2952,12 +2921,12 @@
       <c r="G92" s="2"/>
       <c r="H92" s="2"/>
       <c r="I92" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="K92" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L92" s="26"/>
+        <v>90</v>
+      </c>
+      <c r="K92" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L92" s="25"/>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" s="33"/>
@@ -2969,12 +2938,12 @@
       <c r="G93" s="2"/>
       <c r="H93" s="2"/>
       <c r="I93" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="K93" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L93" s="26"/>
+        <v>91</v>
+      </c>
+      <c r="K93" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L93" s="25"/>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" s="33"/>
@@ -2986,41 +2955,29 @@
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
       <c r="I94" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="K94" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L94" s="26"/>
+        <v>77</v>
+      </c>
+      <c r="K94" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L94" s="25"/>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" s="33"/>
-      <c r="B95" s="2">
-        <v>2</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E95" s="4"/>
-      <c r="F95" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G95" s="2">
-        <v>6</v>
-      </c>
-      <c r="H95" s="2" t="s">
-        <v>29</v>
-      </c>
+      <c r="B95" s="2"/>
+      <c r="C95" s="2"/>
+      <c r="D95" s="2"/>
+      <c r="E95" s="2"/>
+      <c r="F95" s="2"/>
+      <c r="G95" s="2"/>
+      <c r="H95" s="2"/>
       <c r="I95" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="K95" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L95" s="26"/>
+        <v>92</v>
+      </c>
+      <c r="K95" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L95" s="25"/>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" s="33"/>
@@ -3032,12 +2989,12 @@
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
       <c r="I96" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="K96" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L96" s="26"/>
+        <v>93</v>
+      </c>
+      <c r="K96" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L96" s="25"/>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" s="33"/>
@@ -3049,78 +3006,305 @@
       <c r="G97" s="2"/>
       <c r="H97" s="2"/>
       <c r="I97" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="K97" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L97" s="26"/>
+        <v>94</v>
+      </c>
+      <c r="K97" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L97" s="25"/>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" s="33"/>
-      <c r="B98" s="2"/>
-      <c r="C98" s="2"/>
-      <c r="D98" s="2"/>
-      <c r="E98" s="2"/>
-      <c r="F98" s="2"/>
-      <c r="G98" s="2"/>
-      <c r="H98" s="2"/>
+      <c r="B98" s="2">
+        <v>2</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E98" s="3"/>
+      <c r="F98" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G98" s="2">
+        <v>6</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="I98" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="K98" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L98" s="26"/>
+        <v>95</v>
+      </c>
+      <c r="K98" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L98" s="25"/>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" s="33"/>
       <c r="B99" s="2"/>
-      <c r="C99" s="2" t="s">
-        <v>95</v>
-      </c>
+      <c r="C99" s="2"/>
       <c r="D99" s="2"/>
       <c r="E99" s="2"/>
       <c r="F99" s="2"/>
       <c r="G99" s="2"/>
       <c r="H99" s="2"/>
       <c r="I99" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="K99" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L99" s="26"/>
+        <v>96</v>
+      </c>
+      <c r="K99" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L99" s="25"/>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A100" s="34"/>
-      <c r="B100" s="15"/>
-      <c r="C100" s="15"/>
-      <c r="D100" s="15"/>
-      <c r="E100" s="15"/>
-      <c r="F100" s="15"/>
-      <c r="G100" s="15"/>
-      <c r="H100" s="15"/>
-      <c r="I100" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="J100" s="14"/>
-      <c r="K100" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="L100" s="30"/>
+      <c r="A100" s="33"/>
+      <c r="B100" s="2"/>
+      <c r="C100" s="2"/>
+      <c r="D100" s="2"/>
+      <c r="E100" s="2"/>
+      <c r="F100" s="2"/>
+      <c r="G100" s="2"/>
+      <c r="H100" s="2"/>
+      <c r="I100" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="K100" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L100" s="25"/>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A101" s="33"/>
+      <c r="B101" s="2"/>
+      <c r="C101" s="2"/>
+      <c r="D101" s="2"/>
+      <c r="E101" s="2"/>
+      <c r="F101" s="2"/>
+      <c r="G101" s="2"/>
+      <c r="H101" s="2"/>
+      <c r="I101" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="K101" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L101" s="25"/>
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A102" s="33"/>
+      <c r="B102" s="2"/>
+      <c r="C102" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D102" s="2"/>
+      <c r="E102" s="2"/>
+      <c r="F102" s="2"/>
+      <c r="G102" s="2"/>
+      <c r="H102" s="2"/>
+      <c r="I102" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="K102" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L102" s="25"/>
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A103" s="33"/>
+      <c r="B103" s="2"/>
+      <c r="C103" s="2"/>
+      <c r="D103" s="2"/>
+      <c r="E103" s="2"/>
+      <c r="F103" s="2"/>
+      <c r="G103" s="2"/>
+      <c r="H103" s="2"/>
+      <c r="I103" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="K103" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L103" s="25"/>
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A104" s="33"/>
+      <c r="B104" s="2">
+        <v>3</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E104" s="2">
+        <v>1</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="G104" s="2">
+        <v>4</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I104" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="K104" s="27"/>
+      <c r="L104" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A105" s="33"/>
+      <c r="B105" s="2"/>
+      <c r="C105" s="2"/>
+      <c r="D105" s="2"/>
+      <c r="E105" s="2"/>
+      <c r="F105" s="2"/>
+      <c r="G105" s="2"/>
+      <c r="H105" s="2"/>
+      <c r="I105" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="K105" s="27"/>
+      <c r="L105" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A106" s="33"/>
+      <c r="B106" s="2"/>
+      <c r="C106" s="2"/>
+      <c r="D106" s="2"/>
+      <c r="E106" s="2"/>
+      <c r="F106" s="2"/>
+      <c r="G106" s="2"/>
+      <c r="H106" s="2"/>
+      <c r="I106" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="K106" s="27"/>
+      <c r="L106" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A107" s="33"/>
+      <c r="B107" s="2"/>
+      <c r="C107" s="2"/>
+      <c r="D107" s="2"/>
+      <c r="E107" s="2"/>
+      <c r="F107" s="2"/>
+      <c r="G107" s="2"/>
+      <c r="H107" s="2"/>
+      <c r="I107" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="K107" s="27"/>
+      <c r="L107" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A108" s="33"/>
+      <c r="B108" s="2">
+        <v>4</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E108" s="2">
+        <v>1</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="G108" s="2">
+        <v>4</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I108" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="K108" s="27"/>
+      <c r="L108" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A109" s="33"/>
+      <c r="B109" s="2"/>
+      <c r="C109" s="2"/>
+      <c r="D109" s="2"/>
+      <c r="E109" s="2"/>
+      <c r="F109" s="2"/>
+      <c r="G109" s="2"/>
+      <c r="H109" s="2"/>
+      <c r="I109" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="K109" s="27"/>
+      <c r="L109" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A110" s="33"/>
+      <c r="B110" s="2"/>
+      <c r="C110" s="2"/>
+      <c r="D110" s="2"/>
+      <c r="E110" s="2"/>
+      <c r="F110" s="2"/>
+      <c r="G110" s="2"/>
+      <c r="H110" s="2"/>
+      <c r="I110" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="K110" s="27"/>
+      <c r="L110" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A111" s="34"/>
+      <c r="B111" s="14"/>
+      <c r="C111" s="14"/>
+      <c r="D111" s="14"/>
+      <c r="E111" s="14"/>
+      <c r="F111" s="14"/>
+      <c r="G111" s="14"/>
+      <c r="H111" s="14"/>
+      <c r="I111" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="J111" s="13"/>
+      <c r="K111" s="31"/>
+      <c r="L111" s="29" t="s">
+        <v>16</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A61:A68"/>
-    <mergeCell ref="A69:A72"/>
-    <mergeCell ref="A73:A80"/>
-    <mergeCell ref="A81:A100"/>
+    <mergeCell ref="A84:A111"/>
+    <mergeCell ref="A44:A53"/>
+    <mergeCell ref="A54:A75"/>
+    <mergeCell ref="A76:A83"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A4:A29"/>
-    <mergeCell ref="A33:A40"/>
-    <mergeCell ref="A41:A60"/>
+    <mergeCell ref="A4:A21"/>
+    <mergeCell ref="A24:A31"/>
+    <mergeCell ref="A32:A43"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3128,6 +3312,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="d7b47298-7dbc-4c4a-b955-e35738c83845" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EA9F74FD6C93414BACF2D33AB9B46B1F" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="85e183139a7bf430a5cd367af777ffd1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="d7b47298-7dbc-4c4a-b955-e35738c83845" xmlns:ns4="4c7a27d0-c111-49d1-947f-3e415c425751" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5e8b728fb78f9c3c3084b9e953d972a7" ns3:_="" ns4:_="">
     <xsd:import namespace="d7b47298-7dbc-4c4a-b955-e35738c83845"/>
@@ -3360,38 +3561,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="d7b47298-7dbc-4c4a-b955-e35738c83845" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CAFAC10-0FD0-4107-B657-53CDB5D6D5F8}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0006E415-A18B-4726-A1A0-54EC3A4B0653}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="d7b47298-7dbc-4c4a-b955-e35738c83845"/>
-    <ds:schemaRef ds:uri="4c7a27d0-c111-49d1-947f-3e415c425751"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3414,9 +3587,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0006E415-A18B-4726-A1A0-54EC3A4B0653}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CAFAC10-0FD0-4107-B657-53CDB5D6D5F8}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="d7b47298-7dbc-4c4a-b955-e35738c83845"/>
+    <ds:schemaRef ds:uri="4c7a27d0-c111-49d1-947f-3e415c425751"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Greyform/Python_Application/PinAllocationBOMforPBU_T1am.xlsx
+++ b/Greyform/Python_Application/PinAllocationBOMforPBU_T1am.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MokZhiZhuan\OneDrive - WINSYS TECHNOLOGY PTE LTD\Documents\GitHub\GreyForm_UI\Greyform\Python_Application\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{534C980F-46BD-49E5-BADD-F4C8F4ED3DF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DA9823D-99F2-4B36-99F8-BE660052CAB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{10577398-EA94-4D34-AF72-AAEF7879495C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="147">
   <si>
     <t>Wall</t>
   </si>
@@ -185,18 +185,6 @@
     <t>BSS.HAND SHOWER SET.MASTER BATH</t>
   </si>
   <si>
-    <t>TMP3S2b1</t>
-  </si>
-  <si>
-    <t>TMP3S2b2</t>
-  </si>
-  <si>
-    <t>TMP3S2b3</t>
-  </si>
-  <si>
-    <t>TMP3S2b4</t>
-  </si>
-  <si>
     <t>Tile</t>
   </si>
   <si>
@@ -230,9 +218,6 @@
     <t>TMP4S2a2</t>
   </si>
   <si>
-    <t>TMP4S2b1</t>
-  </si>
-  <si>
     <t>Wall 5</t>
   </si>
   <si>
@@ -248,18 +233,6 @@
     <t>TMP5S2a3</t>
   </si>
   <si>
-    <t>TMP5S2a4</t>
-  </si>
-  <si>
-    <t>TMP4S2b2</t>
-  </si>
-  <si>
-    <t>TMP4S2b3</t>
-  </si>
-  <si>
-    <t>TMP4S2b4</t>
-  </si>
-  <si>
     <t>Wall 6</t>
   </si>
   <si>
@@ -492,6 +465,18 @@
   </si>
   <si>
     <t>BSS.GOMGO.PH.GG-6106</t>
+  </si>
+  <si>
+    <t>TMP5S2b4</t>
+  </si>
+  <si>
+    <t>TMP5S2b1</t>
+  </si>
+  <si>
+    <t>TMP5S2b2</t>
+  </si>
+  <si>
+    <t>TMP5S2b3</t>
   </si>
 </sst>
 </file>
@@ -728,7 +713,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -811,6 +796,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -841,10 +829,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -1180,7 +1164,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45C9410D-7727-4F15-9679-20A483A9E846}">
-  <dimension ref="A1:L111"/>
+  <dimension ref="A1:L106"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.42578125" bestFit="1" customWidth="1"/>
@@ -1196,34 +1180,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="38"/>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="38"/>
-      <c r="L1" s="38"/>
+      <c r="A1" s="39"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="39"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="39" t="s">
-        <v>81</v>
-      </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="41"/>
+      <c r="A2" s="40" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="42"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
@@ -1264,12 +1248,12 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="36"/>
+      <c r="A4" s="37"/>
       <c r="B4" s="2">
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>12</v>
@@ -1294,7 +1278,7 @@
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="36"/>
+      <c r="A5" s="37"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
@@ -1312,7 +1296,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="36"/>
+      <c r="A6" s="37"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
@@ -1330,7 +1314,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="36"/>
+      <c r="A7" s="37"/>
       <c r="B7" s="2"/>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
@@ -1348,15 +1332,15 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="36"/>
+      <c r="A8" s="37"/>
       <c r="B8" s="2">
         <v>3</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="2" t="s">
@@ -1378,7 +1362,7 @@
       <c r="L8" s="9"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="36"/>
+      <c r="A9" s="37"/>
       <c r="B9" s="2"/>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
@@ -1396,7 +1380,7 @@
       <c r="L9" s="9"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="36"/>
+      <c r="A10" s="37"/>
       <c r="B10" s="2"/>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
@@ -1414,7 +1398,7 @@
       <c r="L10" s="9"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="36"/>
+      <c r="A11" s="37"/>
       <c r="B11" s="2"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
@@ -1432,13 +1416,13 @@
       <c r="L11" s="9"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="36"/>
+      <c r="A12" s="37"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
@@ -1456,7 +1440,7 @@
       <c r="L12" s="9"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="36"/>
+      <c r="A13" s="37"/>
       <c r="B13" s="2"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
@@ -1474,7 +1458,7 @@
       <c r="L13" s="9"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="36"/>
+      <c r="A14" s="37"/>
       <c r="B14" s="2"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
@@ -1492,7 +1476,7 @@
       <c r="L14" s="9"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="36"/>
+      <c r="A15" s="37"/>
       <c r="B15" s="2"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
@@ -1510,7 +1494,7 @@
       <c r="L15" s="9"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="36"/>
+      <c r="A16" s="37"/>
       <c r="B16" s="2">
         <v>4</v>
       </c>
@@ -1518,7 +1502,7 @@
         <v>21</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="2" t="s">
@@ -1540,7 +1524,7 @@
       <c r="L16" s="9"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="36"/>
+      <c r="A17" s="37"/>
       <c r="B17" s="2"/>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
@@ -1558,7 +1542,7 @@
       <c r="L17" s="9"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="36"/>
+      <c r="A18" s="37"/>
       <c r="B18" s="2"/>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
@@ -1576,7 +1560,7 @@
       <c r="L18" s="9"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="36"/>
+      <c r="A19" s="37"/>
       <c r="B19" s="2"/>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
@@ -1594,13 +1578,13 @@
       <c r="L19" s="9"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="36"/>
+      <c r="A20" s="37"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
@@ -1609,7 +1593,7 @@
         <v>23</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="J20" s="8"/>
       <c r="K20" s="4" t="s">
@@ -1618,7 +1602,7 @@
       <c r="L20" s="9"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="36"/>
+      <c r="A21" s="37"/>
       <c r="B21" s="2"/>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
@@ -1627,7 +1611,7 @@
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
       <c r="I21" s="2" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="J21" s="8"/>
       <c r="K21" s="4" t="s">
@@ -1645,7 +1629,7 @@
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
       <c r="I22" s="2" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="J22" s="8"/>
       <c r="K22" s="4" t="s">
@@ -1663,7 +1647,7 @@
       <c r="G23" s="20"/>
       <c r="H23" s="20"/>
       <c r="I23" s="14" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="J23" s="21"/>
       <c r="K23" s="15" t="s">
@@ -1672,7 +1656,7 @@
       <c r="L23" s="10"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="36" t="s">
+      <c r="A24" s="37" t="s">
         <v>36</v>
       </c>
       <c r="B24" s="2">
@@ -1682,7 +1666,7 @@
         <v>21</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="2" t="s">
@@ -1703,7 +1687,7 @@
       <c r="L24" s="24"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="36"/>
+      <c r="A25" s="37"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
@@ -1720,7 +1704,7 @@
       <c r="L25" s="24"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="36"/>
+      <c r="A26" s="37"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
@@ -1737,7 +1721,7 @@
       <c r="L26" s="24"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="36"/>
+      <c r="A27" s="37"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
@@ -1754,14 +1738,10 @@
       <c r="L27" s="24"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="36"/>
+      <c r="A28" s="37"/>
       <c r="B28" s="2"/>
-      <c r="C28" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>54</v>
-      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
@@ -1775,7 +1755,7 @@
       <c r="L28" s="24"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="36"/>
+      <c r="A29" s="37"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
@@ -1792,7 +1772,7 @@
       <c r="L29" s="24"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="36"/>
+      <c r="A30" s="37"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
@@ -1801,7 +1781,7 @@
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="K30" s="4" t="s">
         <v>16</v>
@@ -1809,7 +1789,7 @@
       <c r="L30" s="24"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="37"/>
+      <c r="A31" s="38"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
@@ -1818,7 +1798,7 @@
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="J31" s="2"/>
       <c r="K31" s="4" t="s">
@@ -1827,7 +1807,7 @@
       <c r="L31" s="30"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="36" t="s">
+      <c r="A32" s="37" t="s">
         <v>43</v>
       </c>
       <c r="B32" s="16">
@@ -1859,7 +1839,7 @@
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="36"/>
+      <c r="A33" s="37"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
@@ -1877,7 +1857,7 @@
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="36"/>
+      <c r="A34" s="37"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
@@ -1895,7 +1875,7 @@
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="36"/>
+      <c r="A35" s="37"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
@@ -1913,7 +1893,7 @@
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="36"/>
+      <c r="A36" s="37"/>
       <c r="B36" s="2">
         <v>2</v>
       </c>
@@ -1921,7 +1901,7 @@
         <v>21</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="2" t="s">
@@ -1934,7 +1914,7 @@
         <v>23</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K36" s="4" t="s">
         <v>16</v>
@@ -1942,7 +1922,7 @@
       <c r="L36" s="25"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A37" s="36"/>
+      <c r="A37" s="37"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
@@ -1951,7 +1931,7 @@
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
       <c r="I37" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="K37" s="4" t="s">
         <v>16</v>
@@ -1959,7 +1939,7 @@
       <c r="L37" s="25"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38" s="36"/>
+      <c r="A38" s="37"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
@@ -1968,57 +1948,94 @@
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
       <c r="I38" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="K38" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L38" s="25"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A39" s="37"/>
+      <c r="B39" s="14"/>
+      <c r="C39" s="14"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="14"/>
+      <c r="F39" s="14"/>
+      <c r="G39" s="14"/>
+      <c r="H39" s="14"/>
+      <c r="I39" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="J39" s="13"/>
+      <c r="K39" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L39" s="32"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A40" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="B40" s="2">
+        <v>1</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E40" s="3"/>
+      <c r="F40" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G40" s="2">
+        <v>5</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J40" s="27"/>
+      <c r="K40" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L40" s="9"/>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A41" s="37"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="J41" s="27"/>
+      <c r="K41" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L41" s="9"/>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A42" s="37"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="K38" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L38" s="25"/>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39" s="36"/>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="K39" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L39" s="25"/>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A40" s="36"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="I40" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="K40" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L40" s="9"/>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A41" s="36"/>
-      <c r="I41" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="K41" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L41" s="9"/>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A42" s="36"/>
-      <c r="I42" s="2" t="s">
-        <v>51</v>
-      </c>
+      <c r="J42" s="27"/>
       <c r="K42" s="4" t="s">
         <v>16</v>
       </c>
@@ -2026,92 +2043,85 @@
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="37"/>
-      <c r="B43" s="13"/>
-      <c r="C43" s="13"/>
-      <c r="D43" s="13"/>
-      <c r="E43" s="13"/>
-      <c r="F43" s="13"/>
-      <c r="G43" s="13"/>
-      <c r="H43" s="13"/>
-      <c r="I43" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="J43" s="13"/>
-      <c r="K43" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="L43" s="10"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="J43" s="27"/>
+      <c r="K43" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L43" s="9"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A44" s="35" t="s">
-        <v>59</v>
-      </c>
-      <c r="B44" s="2">
+      <c r="A44" s="37"/>
+      <c r="C44" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="L44" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A45" s="38"/>
+      <c r="B45" s="13"/>
+      <c r="C45" s="13"/>
+      <c r="D45" s="13"/>
+      <c r="E45" s="13"/>
+      <c r="F45" s="13"/>
+      <c r="G45" s="13"/>
+      <c r="H45" s="13"/>
+      <c r="I45" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="J45" s="13"/>
+      <c r="K45" s="13"/>
+      <c r="L45" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A46" s="36" t="s">
+        <v>60</v>
+      </c>
+      <c r="B46" s="2">
         <v>1</v>
       </c>
-      <c r="C44" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E44" s="3"/>
-      <c r="F44" s="2" t="s">
+      <c r="C46" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D46" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G44" s="2">
-        <v>5</v>
-      </c>
-      <c r="H44" s="2" t="s">
+      <c r="E46" s="3"/>
+      <c r="F46" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G46" s="2">
+        <v>4</v>
+      </c>
+      <c r="H46" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="I44" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="J44" s="27"/>
-      <c r="K44" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L44" s="9"/>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A45" s="36"/>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="J45" s="27"/>
-      <c r="K45" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L45" s="9"/>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A46" s="36"/>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
       <c r="I46" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="J46" s="27"/>
+        <v>62</v>
+      </c>
       <c r="K46" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L46" s="9"/>
+      <c r="L46" s="25"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A47" s="36"/>
+      <c r="A47" s="37"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
@@ -2120,16 +2130,15 @@
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
       <c r="I47" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="J47" s="27"/>
+        <v>63</v>
+      </c>
       <c r="K47" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L47" s="9"/>
+      <c r="L47" s="25"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A48" s="36"/>
+      <c r="A48" s="37"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
@@ -2140,106 +2149,119 @@
       <c r="I48" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="J48" s="27"/>
       <c r="K48" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L48" s="9"/>
+      <c r="L48" s="25"/>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A49" s="36"/>
+      <c r="A49" s="37"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
       <c r="I49" s="2" t="s">
-        <v>71</v>
+        <v>144</v>
       </c>
       <c r="K49" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L49" s="9"/>
+      <c r="L49" s="25"/>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A50" s="36"/>
+      <c r="A50" s="37"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
       <c r="I50" s="2" t="s">
-        <v>72</v>
+        <v>145</v>
       </c>
       <c r="K50" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L50" s="9"/>
+      <c r="L50" s="25"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A51" s="36"/>
-      <c r="I51" s="42" t="s">
-        <v>73</v>
+      <c r="A51" s="37"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2" t="s">
+        <v>146</v>
       </c>
       <c r="K51" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L51" s="9"/>
+      <c r="L51" s="25"/>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A52" s="36"/>
-      <c r="C52" s="28" t="s">
-        <v>151</v>
-      </c>
-      <c r="I52" s="42" t="s">
-        <v>149</v>
-      </c>
-      <c r="K52" s="43"/>
-      <c r="L52" s="7" t="s">
-        <v>16</v>
-      </c>
+      <c r="A52" s="37"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="K52" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L52" s="25"/>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="37"/>
-      <c r="B53" s="13"/>
-      <c r="C53" s="13"/>
-      <c r="D53" s="13"/>
-      <c r="E53" s="13"/>
-      <c r="F53" s="13"/>
-      <c r="G53" s="13"/>
-      <c r="H53" s="13"/>
-      <c r="I53" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="J53" s="13"/>
-      <c r="K53" s="13"/>
-      <c r="L53" s="29" t="s">
+      <c r="B53" s="2"/>
+      <c r="C53" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G53" s="2"/>
+      <c r="H53" s="2"/>
+      <c r="I53" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="L53" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A54" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="B54" s="2">
-        <v>1</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E54" s="3"/>
-      <c r="F54" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G54" s="2">
-        <v>4</v>
-      </c>
-      <c r="H54" s="2" t="s">
-        <v>23</v>
-      </c>
+      <c r="A54" s="37"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="2"/>
+      <c r="F54" s="2"/>
+      <c r="G54" s="2"/>
+      <c r="H54" s="2"/>
       <c r="I54" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="K54" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L54" s="25"/>
+        <v>111</v>
+      </c>
+      <c r="L54" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A55" s="36"/>
+      <c r="A55" s="37"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
@@ -2248,15 +2270,14 @@
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
       <c r="I55" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="K55" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L55" s="25"/>
+        <v>112</v>
+      </c>
+      <c r="L55" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A56" s="36"/>
+      <c r="A56" s="37"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
       <c r="D56" s="2"/>
@@ -2265,15 +2286,14 @@
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
       <c r="I56" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="K56" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L56" s="25"/>
+        <v>126</v>
+      </c>
+      <c r="L56" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A57" s="36"/>
+      <c r="A57" s="37"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
@@ -2282,18 +2302,17 @@
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
       <c r="I57" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="K57" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L57" s="25"/>
+        <v>128</v>
+      </c>
+      <c r="L57" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A58" s="36"/>
+      <c r="A58" s="37"/>
       <c r="B58" s="2"/>
       <c r="C58" s="28" t="s">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>12</v>
@@ -2305,14 +2324,14 @@
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
       <c r="I58" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="L58" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A59" s="36"/>
+      <c r="A59" s="37"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
       <c r="D59" s="2"/>
@@ -2321,14 +2340,14 @@
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
       <c r="I59" s="2" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="L59" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A60" s="36"/>
+      <c r="A60" s="37"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
       <c r="D60" s="2"/>
@@ -2337,14 +2356,14 @@
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
       <c r="I60" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="L60" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A61" s="36"/>
+      <c r="A61" s="37"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
       <c r="D61" s="2"/>
@@ -2353,14 +2372,14 @@
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
       <c r="I61" s="2" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="L61" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A62" s="36"/>
+      <c r="A62" s="37"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
       <c r="D62" s="2"/>
@@ -2369,36 +2388,36 @@
       <c r="G62" s="2"/>
       <c r="H62" s="2"/>
       <c r="I62" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L62" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A63" s="36"/>
+      <c r="A63" s="37"/>
       <c r="B63" s="2"/>
       <c r="C63" s="28" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" s="2" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
       <c r="I63" s="2" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="L63" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A64" s="36"/>
+      <c r="A64" s="37"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
       <c r="D64" s="2"/>
@@ -2407,14 +2426,14 @@
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
       <c r="I64" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L64" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A65" s="36"/>
+      <c r="A65" s="37"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
       <c r="D65" s="2"/>
@@ -2423,14 +2442,14 @@
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
       <c r="I65" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="L65" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A66" s="36"/>
+      <c r="A66" s="37"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
       <c r="D66" s="2"/>
@@ -2439,52 +2458,52 @@
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
       <c r="I66" s="2" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="L66" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A67" s="36"/>
+      <c r="A67" s="37"/>
       <c r="B67" s="2"/>
-      <c r="C67" s="2"/>
-      <c r="D67" s="2"/>
+      <c r="C67" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="E67" s="2"/>
-      <c r="F67" s="2"/>
+      <c r="F67" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
       <c r="I67" s="2" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="L67" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A68" s="36"/>
+      <c r="A68" s="37"/>
       <c r="B68" s="2"/>
-      <c r="C68" s="28" t="s">
-        <v>125</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" s="2"/>
       <c r="E68" s="2"/>
-      <c r="F68" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="F68" s="2"/>
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
       <c r="I68" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="L68" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A69" s="36"/>
+      <c r="A69" s="37"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
       <c r="D69" s="2"/>
@@ -2493,148 +2512,152 @@
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
       <c r="I69" s="2" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L69" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A70" s="36"/>
-      <c r="B70" s="2"/>
-      <c r="C70" s="2"/>
-      <c r="D70" s="2"/>
-      <c r="E70" s="2"/>
-      <c r="F70" s="2"/>
-      <c r="G70" s="2"/>
-      <c r="H70" s="2"/>
-      <c r="I70" s="2" t="s">
-        <v>128</v>
-      </c>
+      <c r="A70" s="38"/>
+      <c r="B70" s="13"/>
+      <c r="D70" s="13"/>
+      <c r="E70" s="13"/>
+      <c r="F70" s="13"/>
+      <c r="G70" s="13"/>
+      <c r="H70" s="13"/>
+      <c r="I70" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="J70" s="13"/>
       <c r="L70" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A71" s="36"/>
-      <c r="B71" s="2"/>
-      <c r="C71" s="2"/>
-      <c r="D71" s="2"/>
-      <c r="E71" s="2"/>
-      <c r="F71" s="2"/>
-      <c r="G71" s="2"/>
-      <c r="H71" s="2"/>
-      <c r="I71" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="L71" s="7" t="s">
-        <v>16</v>
-      </c>
+      <c r="A71" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="B71" s="16">
+        <v>1</v>
+      </c>
+      <c r="C71" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D71" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="E71" s="17"/>
+      <c r="F71" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="G71" s="16">
+        <v>8</v>
+      </c>
+      <c r="H71" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="I71" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="J71" s="18"/>
+      <c r="K71" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="L71" s="22"/>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A72" s="36"/>
+      <c r="A72" s="37"/>
       <c r="B72" s="2"/>
-      <c r="C72" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E72" s="2"/>
-      <c r="F72" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G72" s="2"/>
+      <c r="C72" s="2"/>
+      <c r="D72" s="2"/>
+      <c r="E72" s="3"/>
+      <c r="F72" s="2"/>
+      <c r="G72" s="3"/>
       <c r="H72" s="2"/>
       <c r="I72" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="L72" s="7" t="s">
-        <v>16</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="J72" s="8"/>
+      <c r="K72" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L72" s="9"/>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A73" s="36"/>
+      <c r="A73" s="37"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
       <c r="D73" s="2"/>
-      <c r="E73" s="2"/>
+      <c r="E73" s="3"/>
       <c r="F73" s="2"/>
-      <c r="G73" s="2"/>
+      <c r="G73" s="3"/>
       <c r="H73" s="2"/>
       <c r="I73" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="L73" s="7" t="s">
-        <v>16</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="J73" s="8"/>
+      <c r="K73" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L73" s="9"/>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A74" s="36"/>
+      <c r="A74" s="37"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
       <c r="D74" s="2"/>
-      <c r="E74" s="2"/>
+      <c r="E74" s="3"/>
       <c r="F74" s="2"/>
-      <c r="G74" s="2"/>
+      <c r="G74" s="3"/>
       <c r="H74" s="2"/>
       <c r="I74" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="L74" s="7" t="s">
-        <v>16</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="J74" s="8"/>
+      <c r="K74" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L74" s="9"/>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" s="37"/>
-      <c r="B75" s="13"/>
-      <c r="D75" s="13"/>
-      <c r="E75" s="13"/>
-      <c r="F75" s="13"/>
-      <c r="G75" s="13"/>
-      <c r="H75" s="13"/>
-      <c r="I75" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="J75" s="13"/>
-      <c r="L75" s="7" t="s">
-        <v>16</v>
-      </c>
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="3"/>
+      <c r="F75" s="2"/>
+      <c r="G75" s="3"/>
+      <c r="H75" s="2"/>
+      <c r="I75" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="J75" s="8"/>
+      <c r="K75" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L75" s="9"/>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A76" s="35" t="s">
-        <v>74</v>
-      </c>
-      <c r="B76" s="16">
-        <v>1</v>
-      </c>
-      <c r="C76" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="D76" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="E76" s="17"/>
-      <c r="F76" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="G76" s="16">
-        <v>8</v>
-      </c>
-      <c r="H76" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="I76" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="J76" s="18"/>
-      <c r="K76" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="L76" s="22"/>
+      <c r="A76" s="37"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="3"/>
+      <c r="F76" s="2"/>
+      <c r="G76" s="3"/>
+      <c r="H76" s="2"/>
+      <c r="I76" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="J76" s="8"/>
+      <c r="K76" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L76" s="9"/>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A77" s="36"/>
+      <c r="A77" s="37"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
       <c r="D77" s="2"/>
@@ -2643,7 +2666,7 @@
       <c r="G77" s="3"/>
       <c r="H77" s="2"/>
       <c r="I77" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="J77" s="8"/>
       <c r="K77" s="4" t="s">
@@ -2652,138 +2675,133 @@
       <c r="L77" s="9"/>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A78" s="36"/>
-      <c r="B78" s="2"/>
-      <c r="C78" s="2"/>
-      <c r="D78" s="2"/>
-      <c r="E78" s="3"/>
-      <c r="F78" s="2"/>
-      <c r="G78" s="3"/>
-      <c r="H78" s="2"/>
-      <c r="I78" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="J78" s="8"/>
-      <c r="K78" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L78" s="9"/>
+      <c r="A78" s="38"/>
+      <c r="B78" s="14"/>
+      <c r="C78" s="14"/>
+      <c r="D78" s="14"/>
+      <c r="E78" s="20"/>
+      <c r="F78" s="14"/>
+      <c r="G78" s="20"/>
+      <c r="H78" s="14"/>
+      <c r="I78" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="J78" s="21"/>
+      <c r="K78" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L78" s="10"/>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A79" s="36"/>
-      <c r="B79" s="2"/>
-      <c r="C79" s="2"/>
-      <c r="D79" s="2"/>
+      <c r="A79" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="B79" s="2">
+        <v>1</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>22</v>
+      </c>
       <c r="E79" s="3"/>
-      <c r="F79" s="2"/>
-      <c r="G79" s="3"/>
-      <c r="H79" s="2"/>
+      <c r="F79" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G79" s="2">
+        <v>14</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="I79" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="J79" s="8"/>
+        <v>73</v>
+      </c>
       <c r="K79" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L79" s="9"/>
+      <c r="L79" s="25"/>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A80" s="36"/>
+      <c r="A80" s="34"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
       <c r="D80" s="2"/>
-      <c r="E80" s="3"/>
+      <c r="E80" s="2"/>
       <c r="F80" s="2"/>
-      <c r="G80" s="3"/>
+      <c r="G80" s="2"/>
       <c r="H80" s="2"/>
       <c r="I80" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="J80" s="8"/>
+        <v>74</v>
+      </c>
       <c r="K80" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L80" s="9"/>
+      <c r="L80" s="25"/>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A81" s="36"/>
+      <c r="A81" s="34"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
       <c r="D81" s="2"/>
-      <c r="E81" s="3"/>
+      <c r="E81" s="2"/>
       <c r="F81" s="2"/>
-      <c r="G81" s="3"/>
+      <c r="G81" s="2"/>
       <c r="H81" s="2"/>
       <c r="I81" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="J81" s="8"/>
+        <v>75</v>
+      </c>
       <c r="K81" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L81" s="9"/>
+      <c r="L81" s="25"/>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A82" s="36"/>
+      <c r="A82" s="34"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
       <c r="D82" s="2"/>
-      <c r="E82" s="3"/>
+      <c r="E82" s="2"/>
       <c r="F82" s="2"/>
-      <c r="G82" s="3"/>
+      <c r="G82" s="2"/>
       <c r="H82" s="2"/>
       <c r="I82" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="J82" s="8"/>
+        <v>76</v>
+      </c>
       <c r="K82" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L82" s="9"/>
+      <c r="L82" s="25"/>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A83" s="37"/>
-      <c r="B83" s="14"/>
-      <c r="C83" s="14"/>
-      <c r="D83" s="14"/>
-      <c r="E83" s="20"/>
-      <c r="F83" s="14"/>
-      <c r="G83" s="20"/>
-      <c r="H83" s="14"/>
-      <c r="I83" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="J83" s="21"/>
-      <c r="K83" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="L83" s="10"/>
+      <c r="A83" s="34"/>
+      <c r="B83" s="2"/>
+      <c r="C83" s="2"/>
+      <c r="D83" s="2"/>
+      <c r="E83" s="2"/>
+      <c r="F83" s="2"/>
+      <c r="G83" s="2"/>
+      <c r="H83" s="2"/>
+      <c r="I83" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="K83" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L83" s="25"/>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A84" s="32" t="s">
-        <v>75</v>
-      </c>
-      <c r="B84" s="2">
-        <v>1</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E84" s="3"/>
-      <c r="F84" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G84" s="2">
-        <v>14</v>
-      </c>
-      <c r="H84" s="2" t="s">
-        <v>23</v>
-      </c>
+      <c r="A84" s="34"/>
+      <c r="B84" s="2"/>
+      <c r="C84" s="2"/>
+      <c r="D84" s="2"/>
+      <c r="E84" s="2"/>
+      <c r="F84" s="2"/>
+      <c r="G84" s="2"/>
+      <c r="H84" s="2"/>
       <c r="I84" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="K84" s="4" t="s">
         <v>16</v>
@@ -2791,7 +2809,7 @@
       <c r="L84" s="25"/>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A85" s="33"/>
+      <c r="A85" s="34"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
       <c r="D85" s="2"/>
@@ -2800,7 +2818,7 @@
       <c r="G85" s="2"/>
       <c r="H85" s="2"/>
       <c r="I85" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="K85" s="4" t="s">
         <v>16</v>
@@ -2808,16 +2826,18 @@
       <c r="L85" s="25"/>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A86" s="33"/>
+      <c r="A86" s="34"/>
       <c r="B86" s="2"/>
-      <c r="C86" s="2"/>
+      <c r="C86" s="28" t="s">
+        <v>93</v>
+      </c>
       <c r="D86" s="2"/>
       <c r="E86" s="2"/>
       <c r="F86" s="2"/>
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
       <c r="I86" s="2" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="K86" s="4" t="s">
         <v>16</v>
@@ -2825,7 +2845,7 @@
       <c r="L86" s="25"/>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A87" s="33"/>
+      <c r="A87" s="34"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
       <c r="D87" s="2"/>
@@ -2834,7 +2854,7 @@
       <c r="G87" s="2"/>
       <c r="H87" s="2"/>
       <c r="I87" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K87" s="4" t="s">
         <v>16</v>
@@ -2842,7 +2862,7 @@
       <c r="L87" s="25"/>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A88" s="33"/>
+      <c r="A88" s="34"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
       <c r="D88" s="2"/>
@@ -2851,7 +2871,7 @@
       <c r="G88" s="2"/>
       <c r="H88" s="2"/>
       <c r="I88" s="2" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="K88" s="4" t="s">
         <v>16</v>
@@ -2859,7 +2879,7 @@
       <c r="L88" s="25"/>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A89" s="33"/>
+      <c r="A89" s="34"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
       <c r="D89" s="2"/>
@@ -2868,7 +2888,7 @@
       <c r="G89" s="2"/>
       <c r="H89" s="2"/>
       <c r="I89" s="2" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="K89" s="4" t="s">
         <v>16</v>
@@ -2876,7 +2896,7 @@
       <c r="L89" s="25"/>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A90" s="33"/>
+      <c r="A90" s="34"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
       <c r="D90" s="2"/>
@@ -2885,7 +2905,7 @@
       <c r="G90" s="2"/>
       <c r="H90" s="2"/>
       <c r="I90" s="2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="K90" s="4" t="s">
         <v>16</v>
@@ -2893,18 +2913,16 @@
       <c r="L90" s="25"/>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A91" s="33"/>
+      <c r="A91" s="34"/>
       <c r="B91" s="2"/>
-      <c r="C91" s="28" t="s">
-        <v>102</v>
-      </c>
+      <c r="C91" s="2"/>
       <c r="D91" s="2"/>
       <c r="E91" s="2"/>
       <c r="F91" s="2"/>
       <c r="G91" s="2"/>
       <c r="H91" s="2"/>
       <c r="I91" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K91" s="4" t="s">
         <v>16</v>
@@ -2912,7 +2930,7 @@
       <c r="L91" s="25"/>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A92" s="33"/>
+      <c r="A92" s="34"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
       <c r="D92" s="2"/>
@@ -2921,7 +2939,7 @@
       <c r="G92" s="2"/>
       <c r="H92" s="2"/>
       <c r="I92" s="2" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="K92" s="4" t="s">
         <v>16</v>
@@ -2929,16 +2947,28 @@
       <c r="L92" s="25"/>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A93" s="33"/>
-      <c r="B93" s="2"/>
-      <c r="C93" s="2"/>
-      <c r="D93" s="2"/>
-      <c r="E93" s="2"/>
-      <c r="F93" s="2"/>
-      <c r="G93" s="2"/>
-      <c r="H93" s="2"/>
+      <c r="A93" s="34"/>
+      <c r="B93" s="2">
+        <v>2</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E93" s="3"/>
+      <c r="F93" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G93" s="2">
+        <v>6</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="I93" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="K93" s="4" t="s">
         <v>16</v>
@@ -2946,7 +2976,7 @@
       <c r="L93" s="25"/>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A94" s="33"/>
+      <c r="A94" s="34"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
       <c r="D94" s="2"/>
@@ -2955,7 +2985,7 @@
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
       <c r="I94" s="2" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K94" s="4" t="s">
         <v>16</v>
@@ -2963,7 +2993,7 @@
       <c r="L94" s="25"/>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A95" s="33"/>
+      <c r="A95" s="34"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
       <c r="D95" s="2"/>
@@ -2972,7 +3002,7 @@
       <c r="G95" s="2"/>
       <c r="H95" s="2"/>
       <c r="I95" s="2" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="K95" s="4" t="s">
         <v>16</v>
@@ -2980,7 +3010,7 @@
       <c r="L95" s="25"/>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A96" s="33"/>
+      <c r="A96" s="34"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
       <c r="D96" s="2"/>
@@ -2989,7 +3019,7 @@
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
       <c r="I96" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="K96" s="4" t="s">
         <v>16</v>
@@ -2997,16 +3027,18 @@
       <c r="L96" s="25"/>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A97" s="33"/>
+      <c r="A97" s="34"/>
       <c r="B97" s="2"/>
-      <c r="C97" s="2"/>
+      <c r="C97" s="2" t="s">
+        <v>71</v>
+      </c>
       <c r="D97" s="2"/>
       <c r="E97" s="2"/>
       <c r="F97" s="2"/>
       <c r="G97" s="2"/>
       <c r="H97" s="2"/>
       <c r="I97" s="2" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="K97" s="4" t="s">
         <v>16</v>
@@ -3014,28 +3046,16 @@
       <c r="L97" s="25"/>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A98" s="33"/>
-      <c r="B98" s="2">
-        <v>2</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E98" s="3"/>
-      <c r="F98" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G98" s="2">
-        <v>6</v>
-      </c>
-      <c r="H98" s="2" t="s">
-        <v>23</v>
-      </c>
+      <c r="A98" s="34"/>
+      <c r="B98" s="2"/>
+      <c r="C98" s="2"/>
+      <c r="D98" s="2"/>
+      <c r="E98" s="2"/>
+      <c r="F98" s="2"/>
+      <c r="G98" s="2"/>
+      <c r="H98" s="2"/>
       <c r="I98" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="K98" s="4" t="s">
         <v>16</v>
@@ -3043,24 +3063,38 @@
       <c r="L98" s="25"/>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A99" s="33"/>
-      <c r="B99" s="2"/>
-      <c r="C99" s="2"/>
-      <c r="D99" s="2"/>
-      <c r="E99" s="2"/>
-      <c r="F99" s="2"/>
-      <c r="G99" s="2"/>
-      <c r="H99" s="2"/>
+      <c r="A99" s="34"/>
+      <c r="B99" s="2">
+        <v>3</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E99" s="2">
+        <v>1</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G99" s="2">
+        <v>4</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="I99" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="K99" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L99" s="25"/>
+        <v>131</v>
+      </c>
+      <c r="K99" s="27"/>
+      <c r="L99" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A100" s="33"/>
+      <c r="A100" s="34"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
       <c r="D100" s="2"/>
@@ -3069,15 +3103,15 @@
       <c r="G100" s="2"/>
       <c r="H100" s="2"/>
       <c r="I100" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="K100" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L100" s="25"/>
+        <v>132</v>
+      </c>
+      <c r="K100" s="27"/>
+      <c r="L100" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A101" s="33"/>
+      <c r="A101" s="34"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
       <c r="D101" s="2"/>
@@ -3086,74 +3120,72 @@
       <c r="G101" s="2"/>
       <c r="H101" s="2"/>
       <c r="I101" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="K101" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L101" s="25"/>
+        <v>133</v>
+      </c>
+      <c r="K101" s="27"/>
+      <c r="L101" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A102" s="33"/>
+      <c r="A102" s="34"/>
       <c r="B102" s="2"/>
-      <c r="C102" s="2" t="s">
-        <v>80</v>
-      </c>
+      <c r="C102" s="2"/>
       <c r="D102" s="2"/>
       <c r="E102" s="2"/>
       <c r="F102" s="2"/>
       <c r="G102" s="2"/>
       <c r="H102" s="2"/>
       <c r="I102" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="K102" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L102" s="25"/>
+        <v>134</v>
+      </c>
+      <c r="K102" s="27"/>
+      <c r="L102" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A103" s="33"/>
-      <c r="B103" s="2"/>
-      <c r="C103" s="2"/>
-      <c r="D103" s="2"/>
-      <c r="E103" s="2"/>
-      <c r="F103" s="2"/>
-      <c r="G103" s="2"/>
-      <c r="H103" s="2"/>
+      <c r="A103" s="34"/>
+      <c r="B103" s="2">
+        <v>4</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E103" s="2">
+        <v>1</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G103" s="2">
+        <v>4</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="I103" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="K103" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L103" s="25"/>
+        <v>135</v>
+      </c>
+      <c r="K103" s="27"/>
+      <c r="L103" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A104" s="33"/>
-      <c r="B104" s="2">
-        <v>3</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E104" s="2">
-        <v>1</v>
-      </c>
-      <c r="F104" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="G104" s="2">
-        <v>4</v>
-      </c>
-      <c r="H104" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="A104" s="34"/>
+      <c r="B104" s="2"/>
+      <c r="C104" s="2"/>
+      <c r="D104" s="2"/>
+      <c r="E104" s="2"/>
+      <c r="F104" s="2"/>
+      <c r="G104" s="2"/>
+      <c r="H104" s="2"/>
       <c r="I104" s="2" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="K104" s="27"/>
       <c r="L104" s="7" t="s">
@@ -3161,7 +3193,7 @@
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A105" s="33"/>
+      <c r="A105" s="34"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
       <c r="D105" s="2"/>
@@ -3170,7 +3202,7 @@
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
       <c r="I105" s="2" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="K105" s="27"/>
       <c r="L105" s="7" t="s">
@@ -3178,133 +3210,34 @@
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A106" s="33"/>
-      <c r="B106" s="2"/>
-      <c r="C106" s="2"/>
-      <c r="D106" s="2"/>
-      <c r="E106" s="2"/>
-      <c r="F106" s="2"/>
-      <c r="G106" s="2"/>
-      <c r="H106" s="2"/>
-      <c r="I106" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="K106" s="27"/>
-      <c r="L106" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A107" s="33"/>
-      <c r="B107" s="2"/>
-      <c r="C107" s="2"/>
-      <c r="D107" s="2"/>
-      <c r="E107" s="2"/>
-      <c r="F107" s="2"/>
-      <c r="G107" s="2"/>
-      <c r="H107" s="2"/>
-      <c r="I107" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="K107" s="27"/>
-      <c r="L107" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A108" s="33"/>
-      <c r="B108" s="2">
-        <v>4</v>
-      </c>
-      <c r="C108" s="2" t="s">
+      <c r="A106" s="35"/>
+      <c r="B106" s="14"/>
+      <c r="C106" s="14"/>
+      <c r="D106" s="14"/>
+      <c r="E106" s="14"/>
+      <c r="F106" s="14"/>
+      <c r="G106" s="14"/>
+      <c r="H106" s="14"/>
+      <c r="I106" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="D108" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E108" s="2">
-        <v>1</v>
-      </c>
-      <c r="F108" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="G108" s="2">
-        <v>4</v>
-      </c>
-      <c r="H108" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I108" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="K108" s="27"/>
-      <c r="L108" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A109" s="33"/>
-      <c r="B109" s="2"/>
-      <c r="C109" s="2"/>
-      <c r="D109" s="2"/>
-      <c r="E109" s="2"/>
-      <c r="F109" s="2"/>
-      <c r="G109" s="2"/>
-      <c r="H109" s="2"/>
-      <c r="I109" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="K109" s="27"/>
-      <c r="L109" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A110" s="33"/>
-      <c r="B110" s="2"/>
-      <c r="C110" s="2"/>
-      <c r="D110" s="2"/>
-      <c r="E110" s="2"/>
-      <c r="F110" s="2"/>
-      <c r="G110" s="2"/>
-      <c r="H110" s="2"/>
-      <c r="I110" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="K110" s="27"/>
-      <c r="L110" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A111" s="34"/>
-      <c r="B111" s="14"/>
-      <c r="C111" s="14"/>
-      <c r="D111" s="14"/>
-      <c r="E111" s="14"/>
-      <c r="F111" s="14"/>
-      <c r="G111" s="14"/>
-      <c r="H111" s="14"/>
-      <c r="I111" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="J111" s="13"/>
-      <c r="K111" s="31"/>
-      <c r="L111" s="29" t="s">
+      <c r="J106" s="13"/>
+      <c r="K106" s="31"/>
+      <c r="L106" s="29" t="s">
         <v>16</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A84:A111"/>
-    <mergeCell ref="A44:A53"/>
-    <mergeCell ref="A54:A75"/>
-    <mergeCell ref="A76:A83"/>
+    <mergeCell ref="A79:A106"/>
+    <mergeCell ref="A40:A45"/>
+    <mergeCell ref="A46:A70"/>
+    <mergeCell ref="A71:A78"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A4:A21"/>
     <mergeCell ref="A24:A31"/>
-    <mergeCell ref="A32:A43"/>
+    <mergeCell ref="A32:A39"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3312,15 +3245,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_activity xmlns="d7b47298-7dbc-4c4a-b955-e35738c83845" xsi:nil="true"/>
@@ -3328,7 +3252,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EA9F74FD6C93414BACF2D33AB9B46B1F" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="85e183139a7bf430a5cd367af777ffd1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="d7b47298-7dbc-4c4a-b955-e35738c83845" xmlns:ns4="4c7a27d0-c111-49d1-947f-3e415c425751" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5e8b728fb78f9c3c3084b9e953d972a7" ns3:_="" ns4:_="">
     <xsd:import namespace="d7b47298-7dbc-4c4a-b955-e35738c83845"/>
@@ -3561,15 +3485,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0006E415-A18B-4726-A1A0-54EC3A4B0653}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE34F84B-F271-4B1B-8B21-90DAF7F40D50}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
@@ -3586,7 +3511,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CAFAC10-0FD0-4107-B657-53CDB5D6D5F8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3603,4 +3528,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0006E415-A18B-4726-A1A0-54EC3A4B0653}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Greyform/Python_Application/PinAllocationBOMforPBU_T1am.xlsx
+++ b/Greyform/Python_Application/PinAllocationBOMforPBU_T1am.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MokZhiZhuan\OneDrive - WINSYS TECHNOLOGY PTE LTD\Documents\GitHub\GreyForm_UI\Greyform\Python_Application\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DA9823D-99F2-4B36-99F8-BE660052CAB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{574328C9-F561-4520-BE02-CF2D7A57EA8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{10577398-EA94-4D34-AF72-AAEF7879495C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="139">
   <si>
     <t>Wall</t>
   </si>
@@ -155,12 +155,6 @@
     <t>TMP2S2b2</t>
   </si>
   <si>
-    <t>TMP2S2c1</t>
-  </si>
-  <si>
-    <t>TMP2S2c2</t>
-  </si>
-  <si>
     <t>TMP2S2a1</t>
   </si>
   <si>
@@ -311,12 +305,6 @@
     <t>BSS.TECE.CHAIR BRACKET</t>
   </si>
   <si>
-    <t>TMP2S2c3</t>
-  </si>
-  <si>
-    <t>TMP2S2c4</t>
-  </si>
-  <si>
     <t>BSS.FLOOR DRAIN_150</t>
   </si>
   <si>
@@ -465,18 +453,6 @@
   </si>
   <si>
     <t>BSS.GOMGO.PH.GG-6106</t>
-  </si>
-  <si>
-    <t>TMP5S2b4</t>
-  </si>
-  <si>
-    <t>TMP5S2b1</t>
-  </si>
-  <si>
-    <t>TMP5S2b2</t>
-  </si>
-  <si>
-    <t>TMP5S2b3</t>
   </si>
 </sst>
 </file>
@@ -713,7 +689,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -788,9 +764,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1164,7 +1137,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45C9410D-7727-4F15-9679-20A483A9E846}">
-  <dimension ref="A1:L106"/>
+  <dimension ref="A1:L98"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.42578125" bestFit="1" customWidth="1"/>
@@ -1180,34 +1153,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="39"/>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
+      <c r="A1" s="38"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="40" t="s">
-        <v>72</v>
-      </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="42"/>
+      <c r="A2" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="41"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
@@ -1248,12 +1221,12 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="37"/>
+      <c r="A4" s="36"/>
       <c r="B4" s="2">
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>12</v>
@@ -1278,7 +1251,7 @@
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="37"/>
+      <c r="A5" s="36"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
@@ -1296,7 +1269,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="37"/>
+      <c r="A6" s="36"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
@@ -1314,7 +1287,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="37"/>
+      <c r="A7" s="36"/>
       <c r="B7" s="2"/>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
@@ -1332,15 +1305,15 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="37"/>
+      <c r="A8" s="36"/>
       <c r="B8" s="2">
         <v>3</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="2" t="s">
@@ -1362,7 +1335,7 @@
       <c r="L8" s="9"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="37"/>
+      <c r="A9" s="36"/>
       <c r="B9" s="2"/>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
@@ -1380,7 +1353,7 @@
       <c r="L9" s="9"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="37"/>
+      <c r="A10" s="36"/>
       <c r="B10" s="2"/>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
@@ -1398,7 +1371,7 @@
       <c r="L10" s="9"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="37"/>
+      <c r="A11" s="36"/>
       <c r="B11" s="2"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
@@ -1416,13 +1389,13 @@
       <c r="L11" s="9"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="37"/>
+      <c r="A12" s="36"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
@@ -1440,7 +1413,7 @@
       <c r="L12" s="9"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="37"/>
+      <c r="A13" s="36"/>
       <c r="B13" s="2"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
@@ -1458,7 +1431,7 @@
       <c r="L13" s="9"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="37"/>
+      <c r="A14" s="36"/>
       <c r="B14" s="2"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
@@ -1476,7 +1449,7 @@
       <c r="L14" s="9"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="37"/>
+      <c r="A15" s="36"/>
       <c r="B15" s="2"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
@@ -1494,7 +1467,7 @@
       <c r="L15" s="9"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="37"/>
+      <c r="A16" s="36"/>
       <c r="B16" s="2">
         <v>4</v>
       </c>
@@ -1502,7 +1475,7 @@
         <v>21</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="2" t="s">
@@ -1524,7 +1497,7 @@
       <c r="L16" s="9"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="37"/>
+      <c r="A17" s="36"/>
       <c r="B17" s="2"/>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
@@ -1542,7 +1515,7 @@
       <c r="L17" s="9"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="37"/>
+      <c r="A18" s="36"/>
       <c r="B18" s="2"/>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
@@ -1560,7 +1533,7 @@
       <c r="L18" s="9"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="37"/>
+      <c r="A19" s="36"/>
       <c r="B19" s="2"/>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
@@ -1578,13 +1551,13 @@
       <c r="L19" s="9"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="37"/>
+      <c r="A20" s="36"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
@@ -1593,7 +1566,7 @@
         <v>23</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="J20" s="8"/>
       <c r="K20" s="4" t="s">
@@ -1602,7 +1575,7 @@
       <c r="L20" s="9"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="37"/>
+      <c r="A21" s="36"/>
       <c r="B21" s="2"/>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
@@ -1611,7 +1584,7 @@
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
       <c r="I21" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J21" s="8"/>
       <c r="K21" s="4" t="s">
@@ -1629,7 +1602,7 @@
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
       <c r="I22" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="J22" s="8"/>
       <c r="K22" s="4" t="s">
@@ -1647,7 +1620,7 @@
       <c r="G23" s="20"/>
       <c r="H23" s="20"/>
       <c r="I23" s="14" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="J23" s="21"/>
       <c r="K23" s="15" t="s">
@@ -1656,7 +1629,7 @@
       <c r="L23" s="10"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="37" t="s">
+      <c r="A24" s="35" t="s">
         <v>36</v>
       </c>
       <c r="B24" s="2">
@@ -1666,7 +1639,7 @@
         <v>21</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="2" t="s">
@@ -1679,7 +1652,7 @@
         <v>23</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K24" s="4" t="s">
         <v>16</v>
@@ -1687,7 +1660,7 @@
       <c r="L24" s="24"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="37"/>
+      <c r="A25" s="36"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
@@ -1696,7 +1669,7 @@
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K25" s="4" t="s">
         <v>16</v>
@@ -1704,7 +1677,7 @@
       <c r="L25" s="24"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="37"/>
+      <c r="A26" s="36"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
@@ -1738,24 +1711,39 @@
       <c r="L27" s="24"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="37"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="K28" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L28" s="24"/>
+      <c r="A28" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="B28" s="16">
+        <v>1</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="G28" s="16">
+        <v>4</v>
+      </c>
+      <c r="H28" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="I28" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="J28" s="23"/>
+      <c r="K28" s="23"/>
+      <c r="L28" s="26" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="37"/>
+      <c r="A29" s="36"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
@@ -1764,15 +1752,16 @@
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="K29" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L29" s="24"/>
+        <v>43</v>
+      </c>
+      <c r="J29" s="27"/>
+      <c r="K29" s="27"/>
+      <c r="L29" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="37"/>
+      <c r="A30" s="36"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
@@ -1781,15 +1770,16 @@
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="K30" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L30" s="24"/>
+        <v>44</v>
+      </c>
+      <c r="J30" s="27"/>
+      <c r="K30" s="27"/>
+      <c r="L30" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="38"/>
+      <c r="A31" s="36"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
@@ -1798,48 +1788,45 @@
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="J31" s="2"/>
-      <c r="K31" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L31" s="30"/>
+        <v>45</v>
+      </c>
+      <c r="J31" s="27"/>
+      <c r="K31" s="27"/>
+      <c r="L31" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="37" t="s">
-        <v>43</v>
-      </c>
-      <c r="B32" s="16">
-        <v>1</v>
-      </c>
-      <c r="C32" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="D32" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="E32" s="16"/>
-      <c r="F32" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="G32" s="16">
-        <v>4</v>
-      </c>
-      <c r="H32" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="I32" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="J32" s="23"/>
-      <c r="K32" s="23"/>
-      <c r="L32" s="26" t="s">
-        <v>16</v>
-      </c>
+      <c r="A32" s="36"/>
+      <c r="B32" s="2">
+        <v>2</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E32" s="3"/>
+      <c r="F32" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G32" s="2">
+        <v>8</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="K32" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L32" s="25"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="37"/>
+      <c r="A33" s="36"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
@@ -1848,16 +1835,15 @@
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="J33" s="27"/>
-      <c r="K33" s="27"/>
-      <c r="L33" s="7" t="s">
-        <v>16</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="K33" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L33" s="25"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="37"/>
+      <c r="A34" s="36"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
@@ -1866,63 +1852,65 @@
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="J34" s="27"/>
-      <c r="K34" s="27"/>
-      <c r="L34" s="7" t="s">
-        <v>16</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="K34" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L34" s="25"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="37"/>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="J35" s="27"/>
-      <c r="K35" s="27"/>
-      <c r="L35" s="7" t="s">
-        <v>16</v>
-      </c>
+      <c r="A35" s="36"/>
+      <c r="B35" s="14"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
+      <c r="H35" s="14"/>
+      <c r="I35" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J35" s="13"/>
+      <c r="K35" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L35" s="31"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="37"/>
+      <c r="A36" s="35" t="s">
+        <v>53</v>
+      </c>
       <c r="B36" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G36" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>23</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>51</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="J36" s="27"/>
       <c r="K36" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L36" s="25"/>
+      <c r="L36" s="9"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A37" s="37"/>
+      <c r="A37" s="36"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
@@ -1931,15 +1919,16 @@
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
       <c r="I37" s="2" t="s">
-        <v>52</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="J37" s="27"/>
       <c r="K37" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L37" s="25"/>
+      <c r="L37" s="9"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38" s="37"/>
+      <c r="A38" s="36"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
@@ -1948,101 +1937,95 @@
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
       <c r="I38" s="2" t="s">
-        <v>53</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="J38" s="27"/>
       <c r="K38" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L38" s="25"/>
+      <c r="L38" s="9"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39" s="37"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="J39" s="13"/>
-      <c r="K39" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="L39" s="32"/>
+      <c r="A39" s="36"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J39" s="27"/>
+      <c r="K39" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L39" s="9"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A40" s="36" t="s">
-        <v>55</v>
-      </c>
-      <c r="B40" s="2">
-        <v>1</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E40" s="3"/>
-      <c r="F40" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G40" s="2">
-        <v>5</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>23</v>
+      <c r="A40" s="36"/>
+      <c r="C40" s="28" t="s">
+        <v>138</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="J40" s="27"/>
-      <c r="K40" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L40" s="9"/>
+        <v>136</v>
+      </c>
+      <c r="L40" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="37"/>
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2" t="s">
+      <c r="B41" s="13"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="13"/>
+      <c r="G41" s="13"/>
+      <c r="H41" s="13"/>
+      <c r="I41" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="J41" s="13"/>
+      <c r="K41" s="13"/>
+      <c r="L41" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A42" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="B42" s="2">
+        <v>1</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="J41" s="27"/>
-      <c r="K41" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L41" s="9"/>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A42" s="37"/>
-      <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
-      <c r="H42" s="2"/>
+      <c r="D42" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E42" s="3"/>
+      <c r="F42" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G42" s="2">
+        <v>4</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="I42" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="J42" s="27"/>
+        <v>60</v>
+      </c>
       <c r="K42" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L42" s="9"/>
+      <c r="L42" s="25"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A43" s="37"/>
+      <c r="A43" s="36"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
@@ -2051,77 +2034,70 @@
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
       <c r="I43" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="J43" s="27"/>
+        <v>61</v>
+      </c>
       <c r="K43" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L43" s="9"/>
+      <c r="L43" s="25"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A44" s="37"/>
-      <c r="C44" s="28" t="s">
-        <v>142</v>
-      </c>
+      <c r="A44" s="36"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
       <c r="I44" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="L44" s="7" t="s">
-        <v>16</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="K44" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L44" s="25"/>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A45" s="38"/>
-      <c r="B45" s="13"/>
-      <c r="C45" s="13"/>
-      <c r="D45" s="13"/>
-      <c r="E45" s="13"/>
-      <c r="F45" s="13"/>
-      <c r="G45" s="13"/>
-      <c r="H45" s="13"/>
-      <c r="I45" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="J45" s="13"/>
-      <c r="K45" s="13"/>
-      <c r="L45" s="29" t="s">
+      <c r="A45" s="36"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="L45" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A46" s="36" t="s">
-        <v>60</v>
-      </c>
-      <c r="B46" s="2">
-        <v>1</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E46" s="3"/>
-      <c r="F46" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G46" s="2">
-        <v>4</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>23</v>
-      </c>
+      <c r="A46" s="36"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
       <c r="I46" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="K46" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L46" s="25"/>
+        <v>107</v>
+      </c>
+      <c r="L46" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A47" s="37"/>
+      <c r="A47" s="36"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
@@ -2130,15 +2106,14 @@
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
       <c r="I47" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="K47" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L47" s="25"/>
+        <v>108</v>
+      </c>
+      <c r="L47" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A48" s="37"/>
+      <c r="A48" s="36"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
@@ -2147,15 +2122,14 @@
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
       <c r="I48" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="K48" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L48" s="25"/>
+        <v>122</v>
+      </c>
+      <c r="L48" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A49" s="37"/>
+      <c r="A49" s="36"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
       <c r="D49" s="2"/>
@@ -2164,32 +2138,36 @@
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
       <c r="I49" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="K49" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L49" s="25"/>
+        <v>124</v>
+      </c>
+      <c r="L49" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A50" s="37"/>
+      <c r="A50" s="36"/>
       <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
+      <c r="C50" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="E50" s="2"/>
-      <c r="F50" s="2"/>
+      <c r="F50" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
       <c r="I50" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="K50" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L50" s="25"/>
+        <v>109</v>
+      </c>
+      <c r="L50" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A51" s="37"/>
+      <c r="A51" s="36"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
       <c r="D51" s="2"/>
@@ -2198,15 +2176,14 @@
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
       <c r="I51" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="K51" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L51" s="25"/>
+        <v>110</v>
+      </c>
+      <c r="L51" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A52" s="37"/>
+      <c r="A52" s="36"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
@@ -2215,37 +2192,30 @@
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
       <c r="I52" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="K52" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L52" s="25"/>
+        <v>111</v>
+      </c>
+      <c r="L52" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A53" s="37"/>
+      <c r="A53" s="36"/>
       <c r="B53" s="2"/>
-      <c r="C53" s="28" t="s">
-        <v>109</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
       <c r="E53" s="2"/>
-      <c r="F53" s="2" t="s">
-        <v>20</v>
-      </c>
+      <c r="F53" s="2"/>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
       <c r="I53" s="2" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="L53" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A54" s="37"/>
+      <c r="A54" s="36"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
@@ -2254,30 +2224,36 @@
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
       <c r="I54" s="2" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="L54" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A55" s="37"/>
+      <c r="A55" s="36"/>
       <c r="B55" s="2"/>
-      <c r="C55" s="2"/>
-      <c r="D55" s="2"/>
+      <c r="C55" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="E55" s="2"/>
-      <c r="F55" s="2"/>
+      <c r="F55" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
       <c r="I55" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L55" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A56" s="37"/>
+      <c r="A56" s="36"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
       <c r="D56" s="2"/>
@@ -2286,14 +2262,14 @@
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
       <c r="I56" s="2" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="L56" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A57" s="37"/>
+      <c r="A57" s="36"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
@@ -2302,52 +2278,52 @@
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
       <c r="I57" s="2" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="L57" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A58" s="37"/>
+      <c r="A58" s="36"/>
       <c r="B58" s="2"/>
-      <c r="C58" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
       <c r="E58" s="2"/>
-      <c r="F58" s="2" t="s">
-        <v>20</v>
-      </c>
+      <c r="F58" s="2"/>
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
       <c r="I58" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="L58" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A59" s="37"/>
+      <c r="A59" s="36"/>
       <c r="B59" s="2"/>
-      <c r="C59" s="2"/>
-      <c r="D59" s="2"/>
+      <c r="C59" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="E59" s="2"/>
-      <c r="F59" s="2"/>
+      <c r="F59" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
       <c r="I59" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="L59" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A60" s="37"/>
+      <c r="A60" s="36"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
       <c r="D60" s="2"/>
@@ -2356,14 +2332,14 @@
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
       <c r="I60" s="2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="L60" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A61" s="37"/>
+      <c r="A61" s="36"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
       <c r="D61" s="2"/>
@@ -2372,7 +2348,7 @@
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
       <c r="I61" s="2" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="L61" s="7" t="s">
         <v>16</v>
@@ -2380,343 +2356,341 @@
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="37"/>
-      <c r="B62" s="2"/>
-      <c r="C62" s="2"/>
-      <c r="D62" s="2"/>
-      <c r="E62" s="2"/>
-      <c r="F62" s="2"/>
-      <c r="G62" s="2"/>
-      <c r="H62" s="2"/>
-      <c r="I62" s="2" t="s">
-        <v>139</v>
-      </c>
+      <c r="B62" s="13"/>
+      <c r="D62" s="13"/>
+      <c r="E62" s="13"/>
+      <c r="F62" s="13"/>
+      <c r="G62" s="13"/>
+      <c r="H62" s="13"/>
+      <c r="I62" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="J62" s="13"/>
       <c r="L62" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A63" s="37"/>
-      <c r="B63" s="2"/>
-      <c r="C63" s="28" t="s">
-        <v>116</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E63" s="2"/>
-      <c r="F63" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G63" s="2"/>
-      <c r="H63" s="2"/>
-      <c r="I63" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="L63" s="7" t="s">
-        <v>16</v>
-      </c>
+      <c r="A63" s="35" t="s">
+        <v>63</v>
+      </c>
+      <c r="B63" s="16">
+        <v>1</v>
+      </c>
+      <c r="C63" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D63" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="E63" s="17"/>
+      <c r="F63" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="G63" s="16">
+        <v>8</v>
+      </c>
+      <c r="H63" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="I63" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="J63" s="18"/>
+      <c r="K63" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="L63" s="22"/>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A64" s="37"/>
+      <c r="A64" s="36"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
       <c r="D64" s="2"/>
-      <c r="E64" s="2"/>
+      <c r="E64" s="3"/>
       <c r="F64" s="2"/>
-      <c r="G64" s="2"/>
+      <c r="G64" s="3"/>
       <c r="H64" s="2"/>
       <c r="I64" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="L64" s="7" t="s">
-        <v>16</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="J64" s="8"/>
+      <c r="K64" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L64" s="9"/>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A65" s="37"/>
+      <c r="A65" s="36"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
       <c r="D65" s="2"/>
-      <c r="E65" s="2"/>
+      <c r="E65" s="3"/>
       <c r="F65" s="2"/>
-      <c r="G65" s="2"/>
+      <c r="G65" s="3"/>
       <c r="H65" s="2"/>
       <c r="I65" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="L65" s="7" t="s">
-        <v>16</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="J65" s="8"/>
+      <c r="K65" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L65" s="9"/>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A66" s="37"/>
+      <c r="A66" s="36"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
       <c r="D66" s="2"/>
-      <c r="E66" s="2"/>
+      <c r="E66" s="3"/>
       <c r="F66" s="2"/>
-      <c r="G66" s="2"/>
+      <c r="G66" s="3"/>
       <c r="H66" s="2"/>
       <c r="I66" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="L66" s="7" t="s">
-        <v>16</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="J66" s="8"/>
+      <c r="K66" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L66" s="9"/>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A67" s="37"/>
+      <c r="A67" s="36"/>
       <c r="B67" s="2"/>
-      <c r="C67" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E67" s="2"/>
-      <c r="F67" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G67" s="2"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="2"/>
+      <c r="E67" s="3"/>
+      <c r="F67" s="2"/>
+      <c r="G67" s="3"/>
       <c r="H67" s="2"/>
       <c r="I67" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="L67" s="7" t="s">
-        <v>16</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="J67" s="8"/>
+      <c r="K67" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L67" s="9"/>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A68" s="37"/>
+      <c r="A68" s="36"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
       <c r="D68" s="2"/>
-      <c r="E68" s="2"/>
+      <c r="E68" s="3"/>
       <c r="F68" s="2"/>
-      <c r="G68" s="2"/>
+      <c r="G68" s="3"/>
       <c r="H68" s="2"/>
       <c r="I68" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="L68" s="7" t="s">
-        <v>16</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="J68" s="8"/>
+      <c r="K68" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L68" s="9"/>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A69" s="37"/>
+      <c r="A69" s="36"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
       <c r="D69" s="2"/>
-      <c r="E69" s="2"/>
+      <c r="E69" s="3"/>
       <c r="F69" s="2"/>
-      <c r="G69" s="2"/>
+      <c r="G69" s="3"/>
       <c r="H69" s="2"/>
       <c r="I69" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="L69" s="7" t="s">
-        <v>16</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="J69" s="8"/>
+      <c r="K69" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L69" s="9"/>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A70" s="38"/>
-      <c r="B70" s="13"/>
-      <c r="D70" s="13"/>
-      <c r="E70" s="13"/>
-      <c r="F70" s="13"/>
-      <c r="G70" s="13"/>
-      <c r="H70" s="13"/>
+      <c r="A70" s="37"/>
+      <c r="B70" s="14"/>
+      <c r="C70" s="14"/>
+      <c r="D70" s="14"/>
+      <c r="E70" s="20"/>
+      <c r="F70" s="14"/>
+      <c r="G70" s="20"/>
+      <c r="H70" s="14"/>
       <c r="I70" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="J70" s="13"/>
-      <c r="L70" s="7" t="s">
-        <v>16</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="J70" s="21"/>
+      <c r="K70" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L70" s="10"/>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A71" s="36" t="s">
+      <c r="A71" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="B71" s="2">
+        <v>1</v>
+      </c>
+      <c r="C71" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B71" s="16">
-        <v>1</v>
-      </c>
-      <c r="C71" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="D71" s="16" t="s">
+      <c r="D71" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E71" s="17"/>
-      <c r="F71" s="16" t="s">
+      <c r="E71" s="3"/>
+      <c r="F71" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G71" s="16">
-        <v>8</v>
-      </c>
-      <c r="H71" s="16" t="s">
+      <c r="G71" s="2">
+        <v>14</v>
+      </c>
+      <c r="H71" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="I71" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="J71" s="18"/>
-      <c r="K71" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="L71" s="22"/>
+      <c r="I71" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="K71" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L71" s="25"/>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A72" s="37"/>
+      <c r="A72" s="33"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
       <c r="D72" s="2"/>
-      <c r="E72" s="3"/>
+      <c r="E72" s="2"/>
       <c r="F72" s="2"/>
-      <c r="G72" s="3"/>
+      <c r="G72" s="2"/>
       <c r="H72" s="2"/>
       <c r="I72" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="J72" s="8"/>
+        <v>72</v>
+      </c>
       <c r="K72" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L72" s="9"/>
+      <c r="L72" s="25"/>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A73" s="37"/>
+      <c r="A73" s="33"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
       <c r="D73" s="2"/>
-      <c r="E73" s="3"/>
+      <c r="E73" s="2"/>
       <c r="F73" s="2"/>
-      <c r="G73" s="3"/>
+      <c r="G73" s="2"/>
       <c r="H73" s="2"/>
       <c r="I73" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="J73" s="8"/>
+        <v>73</v>
+      </c>
       <c r="K73" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L73" s="9"/>
+      <c r="L73" s="25"/>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A74" s="37"/>
+      <c r="A74" s="33"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
       <c r="D74" s="2"/>
-      <c r="E74" s="3"/>
+      <c r="E74" s="2"/>
       <c r="F74" s="2"/>
-      <c r="G74" s="3"/>
+      <c r="G74" s="2"/>
       <c r="H74" s="2"/>
       <c r="I74" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="J74" s="8"/>
+        <v>74</v>
+      </c>
       <c r="K74" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L74" s="9"/>
+      <c r="L74" s="25"/>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A75" s="37"/>
+      <c r="A75" s="33"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
       <c r="D75" s="2"/>
-      <c r="E75" s="3"/>
+      <c r="E75" s="2"/>
       <c r="F75" s="2"/>
-      <c r="G75" s="3"/>
+      <c r="G75" s="2"/>
       <c r="H75" s="2"/>
       <c r="I75" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="J75" s="8"/>
+        <v>76</v>
+      </c>
       <c r="K75" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L75" s="9"/>
+      <c r="L75" s="25"/>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A76" s="37"/>
+      <c r="A76" s="33"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
       <c r="D76" s="2"/>
-      <c r="E76" s="3"/>
+      <c r="E76" s="2"/>
       <c r="F76" s="2"/>
-      <c r="G76" s="3"/>
+      <c r="G76" s="2"/>
       <c r="H76" s="2"/>
       <c r="I76" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="J76" s="8"/>
+        <v>77</v>
+      </c>
       <c r="K76" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L76" s="9"/>
+      <c r="L76" s="25"/>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A77" s="37"/>
+      <c r="A77" s="33"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
       <c r="D77" s="2"/>
-      <c r="E77" s="3"/>
+      <c r="E77" s="2"/>
       <c r="F77" s="2"/>
-      <c r="G77" s="3"/>
+      <c r="G77" s="2"/>
       <c r="H77" s="2"/>
       <c r="I77" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="J77" s="8"/>
+        <v>78</v>
+      </c>
       <c r="K77" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L77" s="9"/>
+      <c r="L77" s="25"/>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A78" s="38"/>
-      <c r="B78" s="14"/>
-      <c r="C78" s="14"/>
-      <c r="D78" s="14"/>
-      <c r="E78" s="20"/>
-      <c r="F78" s="14"/>
-      <c r="G78" s="20"/>
-      <c r="H78" s="14"/>
-      <c r="I78" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="J78" s="21"/>
-      <c r="K78" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="L78" s="10"/>
+      <c r="A78" s="33"/>
+      <c r="B78" s="2"/>
+      <c r="C78" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="D78" s="2"/>
+      <c r="E78" s="2"/>
+      <c r="F78" s="2"/>
+      <c r="G78" s="2"/>
+      <c r="H78" s="2"/>
+      <c r="I78" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="K78" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L78" s="25"/>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A79" s="33" t="s">
-        <v>66</v>
-      </c>
-      <c r="B79" s="2">
-        <v>1</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E79" s="3"/>
-      <c r="F79" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G79" s="2">
-        <v>14</v>
-      </c>
-      <c r="H79" s="2" t="s">
-        <v>23</v>
-      </c>
+      <c r="A79" s="33"/>
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="2"/>
+      <c r="E79" s="2"/>
+      <c r="F79" s="2"/>
+      <c r="G79" s="2"/>
+      <c r="H79" s="2"/>
       <c r="I79" s="2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="K79" s="4" t="s">
         <v>16</v>
@@ -2724,7 +2698,7 @@
       <c r="L79" s="25"/>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A80" s="34"/>
+      <c r="A80" s="33"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
       <c r="D80" s="2"/>
@@ -2733,7 +2707,7 @@
       <c r="G80" s="2"/>
       <c r="H80" s="2"/>
       <c r="I80" s="2" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="K80" s="4" t="s">
         <v>16</v>
@@ -2741,7 +2715,7 @@
       <c r="L80" s="25"/>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A81" s="34"/>
+      <c r="A81" s="33"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
       <c r="D81" s="2"/>
@@ -2750,7 +2724,7 @@
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
       <c r="I81" s="2" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="K81" s="4" t="s">
         <v>16</v>
@@ -2758,7 +2732,7 @@
       <c r="L81" s="25"/>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A82" s="34"/>
+      <c r="A82" s="33"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
       <c r="D82" s="2"/>
@@ -2767,7 +2741,7 @@
       <c r="G82" s="2"/>
       <c r="H82" s="2"/>
       <c r="I82" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="K82" s="4" t="s">
         <v>16</v>
@@ -2775,7 +2749,7 @@
       <c r="L82" s="25"/>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A83" s="34"/>
+      <c r="A83" s="33"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
       <c r="D83" s="2"/>
@@ -2784,7 +2758,7 @@
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
       <c r="I83" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="K83" s="4" t="s">
         <v>16</v>
@@ -2792,7 +2766,7 @@
       <c r="L83" s="25"/>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A84" s="34"/>
+      <c r="A84" s="33"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
       <c r="D84" s="2"/>
@@ -2801,7 +2775,7 @@
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
       <c r="I84" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K84" s="4" t="s">
         <v>16</v>
@@ -2809,16 +2783,28 @@
       <c r="L84" s="25"/>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A85" s="34"/>
-      <c r="B85" s="2"/>
-      <c r="C85" s="2"/>
-      <c r="D85" s="2"/>
-      <c r="E85" s="2"/>
-      <c r="F85" s="2"/>
-      <c r="G85" s="2"/>
-      <c r="H85" s="2"/>
+      <c r="A85" s="33"/>
+      <c r="B85" s="2">
+        <v>2</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E85" s="3"/>
+      <c r="F85" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G85" s="2">
+        <v>6</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="I85" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="K85" s="4" t="s">
         <v>16</v>
@@ -2826,18 +2812,16 @@
       <c r="L85" s="25"/>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A86" s="34"/>
+      <c r="A86" s="33"/>
       <c r="B86" s="2"/>
-      <c r="C86" s="28" t="s">
-        <v>93</v>
-      </c>
+      <c r="C86" s="2"/>
       <c r="D86" s="2"/>
       <c r="E86" s="2"/>
       <c r="F86" s="2"/>
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
       <c r="I86" s="2" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K86" s="4" t="s">
         <v>16</v>
@@ -2845,7 +2829,7 @@
       <c r="L86" s="25"/>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A87" s="34"/>
+      <c r="A87" s="33"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
       <c r="D87" s="2"/>
@@ -2854,7 +2838,7 @@
       <c r="G87" s="2"/>
       <c r="H87" s="2"/>
       <c r="I87" s="2" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="K87" s="4" t="s">
         <v>16</v>
@@ -2862,7 +2846,7 @@
       <c r="L87" s="25"/>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A88" s="34"/>
+      <c r="A88" s="33"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
       <c r="D88" s="2"/>
@@ -2871,7 +2855,7 @@
       <c r="G88" s="2"/>
       <c r="H88" s="2"/>
       <c r="I88" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="K88" s="4" t="s">
         <v>16</v>
@@ -2879,9 +2863,11 @@
       <c r="L88" s="25"/>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A89" s="34"/>
+      <c r="A89" s="33"/>
       <c r="B89" s="2"/>
-      <c r="C89" s="2"/>
+      <c r="C89" s="2" t="s">
+        <v>69</v>
+      </c>
       <c r="D89" s="2"/>
       <c r="E89" s="2"/>
       <c r="F89" s="2"/>
@@ -2896,7 +2882,7 @@
       <c r="L89" s="25"/>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A90" s="34"/>
+      <c r="A90" s="33"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
       <c r="D90" s="2"/>
@@ -2905,7 +2891,7 @@
       <c r="G90" s="2"/>
       <c r="H90" s="2"/>
       <c r="I90" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="K90" s="4" t="s">
         <v>16</v>
@@ -2913,24 +2899,38 @@
       <c r="L90" s="25"/>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A91" s="34"/>
-      <c r="B91" s="2"/>
-      <c r="C91" s="2"/>
-      <c r="D91" s="2"/>
-      <c r="E91" s="2"/>
-      <c r="F91" s="2"/>
-      <c r="G91" s="2"/>
-      <c r="H91" s="2"/>
+      <c r="A91" s="33"/>
+      <c r="B91" s="2">
+        <v>3</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E91" s="2">
+        <v>1</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="G91" s="2">
+        <v>4</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="I91" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="K91" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L91" s="25"/>
+        <v>127</v>
+      </c>
+      <c r="K91" s="27"/>
+      <c r="L91" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A92" s="34"/>
+      <c r="A92" s="33"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
       <c r="D92" s="2"/>
@@ -2939,44 +2939,32 @@
       <c r="G92" s="2"/>
       <c r="H92" s="2"/>
       <c r="I92" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="K92" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L92" s="25"/>
+        <v>128</v>
+      </c>
+      <c r="K92" s="27"/>
+      <c r="L92" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A93" s="34"/>
-      <c r="B93" s="2">
-        <v>2</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E93" s="3"/>
-      <c r="F93" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G93" s="2">
-        <v>6</v>
-      </c>
-      <c r="H93" s="2" t="s">
-        <v>23</v>
-      </c>
+      <c r="A93" s="33"/>
+      <c r="B93" s="2"/>
+      <c r="C93" s="2"/>
+      <c r="D93" s="2"/>
+      <c r="E93" s="2"/>
+      <c r="F93" s="2"/>
+      <c r="G93" s="2"/>
+      <c r="H93" s="2"/>
       <c r="I93" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="K93" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L93" s="25"/>
+        <v>129</v>
+      </c>
+      <c r="K93" s="27"/>
+      <c r="L93" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A94" s="34"/>
+      <c r="A94" s="33"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
       <c r="D94" s="2"/>
@@ -2985,32 +2973,46 @@
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
       <c r="I94" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="K94" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L94" s="25"/>
+        <v>130</v>
+      </c>
+      <c r="K94" s="27"/>
+      <c r="L94" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A95" s="34"/>
-      <c r="B95" s="2"/>
-      <c r="C95" s="2"/>
-      <c r="D95" s="2"/>
-      <c r="E95" s="2"/>
-      <c r="F95" s="2"/>
-      <c r="G95" s="2"/>
-      <c r="H95" s="2"/>
+      <c r="A95" s="33"/>
+      <c r="B95" s="2">
+        <v>4</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E95" s="2">
+        <v>1</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="G95" s="2">
+        <v>4</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="I95" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="K95" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L95" s="25"/>
+        <v>131</v>
+      </c>
+      <c r="K95" s="27"/>
+      <c r="L95" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A96" s="34"/>
+      <c r="A96" s="33"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
       <c r="D96" s="2"/>
@@ -3019,225 +3021,59 @@
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
       <c r="I96" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="K96" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L96" s="25"/>
+        <v>132</v>
+      </c>
+      <c r="K96" s="27"/>
+      <c r="L96" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A97" s="34"/>
+      <c r="A97" s="33"/>
       <c r="B97" s="2"/>
-      <c r="C97" s="2" t="s">
-        <v>71</v>
-      </c>
+      <c r="C97" s="2"/>
       <c r="D97" s="2"/>
       <c r="E97" s="2"/>
       <c r="F97" s="2"/>
       <c r="G97" s="2"/>
       <c r="H97" s="2"/>
       <c r="I97" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="K97" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L97" s="25"/>
+        <v>133</v>
+      </c>
+      <c r="K97" s="27"/>
+      <c r="L97" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" s="34"/>
-      <c r="B98" s="2"/>
-      <c r="C98" s="2"/>
-      <c r="D98" s="2"/>
-      <c r="E98" s="2"/>
-      <c r="F98" s="2"/>
-      <c r="G98" s="2"/>
-      <c r="H98" s="2"/>
-      <c r="I98" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="K98" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L98" s="25"/>
-    </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A99" s="34"/>
-      <c r="B99" s="2">
-        <v>3</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E99" s="2">
-        <v>1</v>
-      </c>
-      <c r="F99" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="G99" s="2">
-        <v>4</v>
-      </c>
-      <c r="H99" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I99" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="K99" s="27"/>
-      <c r="L99" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A100" s="34"/>
-      <c r="B100" s="2"/>
-      <c r="C100" s="2"/>
-      <c r="D100" s="2"/>
-      <c r="E100" s="2"/>
-      <c r="F100" s="2"/>
-      <c r="G100" s="2"/>
-      <c r="H100" s="2"/>
-      <c r="I100" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="K100" s="27"/>
-      <c r="L100" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A101" s="34"/>
-      <c r="B101" s="2"/>
-      <c r="C101" s="2"/>
-      <c r="D101" s="2"/>
-      <c r="E101" s="2"/>
-      <c r="F101" s="2"/>
-      <c r="G101" s="2"/>
-      <c r="H101" s="2"/>
-      <c r="I101" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="K101" s="27"/>
-      <c r="L101" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A102" s="34"/>
-      <c r="B102" s="2"/>
-      <c r="C102" s="2"/>
-      <c r="D102" s="2"/>
-      <c r="E102" s="2"/>
-      <c r="F102" s="2"/>
-      <c r="G102" s="2"/>
-      <c r="H102" s="2"/>
-      <c r="I102" s="2" t="s">
+      <c r="B98" s="14"/>
+      <c r="C98" s="14"/>
+      <c r="D98" s="14"/>
+      <c r="E98" s="14"/>
+      <c r="F98" s="14"/>
+      <c r="G98" s="14"/>
+      <c r="H98" s="14"/>
+      <c r="I98" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="K102" s="27"/>
-      <c r="L102" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A103" s="34"/>
-      <c r="B103" s="2">
-        <v>4</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E103" s="2">
-        <v>1</v>
-      </c>
-      <c r="F103" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="G103" s="2">
-        <v>4</v>
-      </c>
-      <c r="H103" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I103" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="K103" s="27"/>
-      <c r="L103" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A104" s="34"/>
-      <c r="B104" s="2"/>
-      <c r="C104" s="2"/>
-      <c r="D104" s="2"/>
-      <c r="E104" s="2"/>
-      <c r="F104" s="2"/>
-      <c r="G104" s="2"/>
-      <c r="H104" s="2"/>
-      <c r="I104" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="K104" s="27"/>
-      <c r="L104" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A105" s="34"/>
-      <c r="B105" s="2"/>
-      <c r="C105" s="2"/>
-      <c r="D105" s="2"/>
-      <c r="E105" s="2"/>
-      <c r="F105" s="2"/>
-      <c r="G105" s="2"/>
-      <c r="H105" s="2"/>
-      <c r="I105" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="K105" s="27"/>
-      <c r="L105" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A106" s="35"/>
-      <c r="B106" s="14"/>
-      <c r="C106" s="14"/>
-      <c r="D106" s="14"/>
-      <c r="E106" s="14"/>
-      <c r="F106" s="14"/>
-      <c r="G106" s="14"/>
-      <c r="H106" s="14"/>
-      <c r="I106" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="J106" s="13"/>
-      <c r="K106" s="31"/>
-      <c r="L106" s="29" t="s">
+      <c r="J98" s="13"/>
+      <c r="K98" s="30"/>
+      <c r="L98" s="29" t="s">
         <v>16</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A79:A106"/>
-    <mergeCell ref="A40:A45"/>
-    <mergeCell ref="A46:A70"/>
-    <mergeCell ref="A71:A78"/>
+    <mergeCell ref="A71:A98"/>
+    <mergeCell ref="A36:A41"/>
+    <mergeCell ref="A42:A62"/>
+    <mergeCell ref="A63:A70"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A4:A21"/>
-    <mergeCell ref="A24:A31"/>
-    <mergeCell ref="A32:A39"/>
+    <mergeCell ref="A24:A27"/>
+    <mergeCell ref="A28:A35"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3245,11 +3081,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="d7b47298-7dbc-4c4a-b955-e35738c83845" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3486,27 +3323,17 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="d7b47298-7dbc-4c4a-b955-e35738c83845" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE34F84B-F271-4B1B-8B21-90DAF7F40D50}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0006E415-A18B-4726-A1A0-54EC3A4B0653}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="4c7a27d0-c111-49d1-947f-3e415c425751"/>
-    <ds:schemaRef ds:uri="d7b47298-7dbc-4c4a-b955-e35738c83845"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3531,9 +3358,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0006E415-A18B-4726-A1A0-54EC3A4B0653}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE34F84B-F271-4B1B-8B21-90DAF7F40D50}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="4c7a27d0-c111-49d1-947f-3e415c425751"/>
+    <ds:schemaRef ds:uri="d7b47298-7dbc-4c4a-b955-e35738c83845"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Greyform/Python_Application/PinAllocationBOMforPBU_T1am.xlsx
+++ b/Greyform/Python_Application/PinAllocationBOMforPBU_T1am.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MokZhiZhuan\OneDrive - WINSYS TECHNOLOGY PTE LTD\Documents\GitHub\GreyForm_UI\Greyform\Python_Application\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{574328C9-F561-4520-BE02-CF2D7A57EA8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{626FC3E7-BA90-4051-ACD9-6C25ACD0A6BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{10577398-EA94-4D34-AF72-AAEF7879495C}"/>
   </bookViews>
@@ -3081,15 +3081,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EA9F74FD6C93414BACF2D33AB9B46B1F" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="85e183139a7bf430a5cd367af777ffd1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="d7b47298-7dbc-4c4a-b955-e35738c83845" xmlns:ns4="4c7a27d0-c111-49d1-947f-3e415c425751" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5e8b728fb78f9c3c3084b9e953d972a7" ns3:_="" ns4:_="">
     <xsd:import namespace="d7b47298-7dbc-4c4a-b955-e35738c83845"/>
@@ -3322,6 +3313,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -3331,14 +3331,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0006E415-A18B-4726-A1A0-54EC3A4B0653}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CAFAC10-0FD0-4107-B657-53CDB5D6D5F8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3353,6 +3345,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0006E415-A18B-4726-A1A0-54EC3A4B0653}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Greyform/Python_Application/PinAllocationBOMforPBU_T1am.xlsx
+++ b/Greyform/Python_Application/PinAllocationBOMforPBU_T1am.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MokZhiZhuan\OneDrive - WINSYS TECHNOLOGY PTE LTD\Documents\GitHub\GreyForm_UI\Greyform\Python_Application\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{626FC3E7-BA90-4051-ACD9-6C25ACD0A6BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C7CA7B3-ADF5-4354-87E1-B4E85A619DF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{10577398-EA94-4D34-AF72-AAEF7879495C}"/>
+    <workbookView xWindow="3510" yWindow="735" windowWidth="23235" windowHeight="15465" xr2:uid="{10577398-EA94-4D34-AF72-AAEF7879495C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="143">
   <si>
     <t>Wall</t>
   </si>
@@ -453,6 +453,18 @@
   </si>
   <si>
     <t>BSS.GOMGO.PH.GG-6106</t>
+  </si>
+  <si>
+    <t>TMP5S2b1</t>
+  </si>
+  <si>
+    <t>TMP5S2b2</t>
+  </si>
+  <si>
+    <t>TMP5S2b3</t>
+  </si>
+  <si>
+    <t>TMP5S2b4</t>
   </si>
 </sst>
 </file>
@@ -1137,7 +1149,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45C9410D-7727-4F15-9679-20A483A9E846}">
-  <dimension ref="A1:L98"/>
+  <dimension ref="A1:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.42578125" bestFit="1" customWidth="1"/>
@@ -2061,24 +2073,21 @@
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="36"/>
       <c r="B45" s="2"/>
-      <c r="C45" s="28" t="s">
-        <v>105</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="C45" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D45" s="2"/>
       <c r="E45" s="2"/>
-      <c r="F45" s="2" t="s">
-        <v>20</v>
-      </c>
+      <c r="F45" s="2"/>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
       <c r="I45" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="L45" s="7" t="s">
-        <v>16</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="K45" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L45" s="25"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="36"/>
@@ -2090,11 +2099,12 @@
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
       <c r="I46" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="L46" s="7" t="s">
-        <v>16</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="K46" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L46" s="25"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" s="36"/>
@@ -2106,11 +2116,12 @@
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
       <c r="I47" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="L47" s="7" t="s">
-        <v>16</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="K47" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L47" s="25"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="36"/>
@@ -2122,23 +2133,30 @@
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
       <c r="I48" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="L48" s="7" t="s">
-        <v>16</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="K48" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L48" s="25"/>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="36"/>
       <c r="B49" s="2"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
+      <c r="C49" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
+      <c r="F49" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
       <c r="I49" s="2" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="L49" s="7" t="s">
         <v>16</v>
@@ -2147,20 +2165,14 @@
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="36"/>
       <c r="B50" s="2"/>
-      <c r="C50" s="28" t="s">
-        <v>88</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
       <c r="E50" s="2"/>
-      <c r="F50" s="2" t="s">
-        <v>20</v>
-      </c>
+      <c r="F50" s="2"/>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
       <c r="I50" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L50" s="7" t="s">
         <v>16</v>
@@ -2176,7 +2188,7 @@
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
       <c r="I51" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="L51" s="7" t="s">
         <v>16</v>
@@ -2192,7 +2204,7 @@
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
       <c r="I52" s="2" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="L52" s="7" t="s">
         <v>16</v>
@@ -2208,7 +2220,7 @@
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
       <c r="I53" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L53" s="7" t="s">
         <v>16</v>
@@ -2217,14 +2229,20 @@
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="36"/>
       <c r="B54" s="2"/>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
+      <c r="C54" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="E54" s="2"/>
-      <c r="F54" s="2"/>
+      <c r="F54" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
       <c r="I54" s="2" t="s">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="L54" s="7" t="s">
         <v>16</v>
@@ -2233,20 +2251,14 @@
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="36"/>
       <c r="B55" s="2"/>
-      <c r="C55" s="28" t="s">
-        <v>112</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
       <c r="E55" s="2"/>
-      <c r="F55" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="F55" s="2"/>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
       <c r="I55" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="L55" s="7" t="s">
         <v>16</v>
@@ -2262,7 +2274,7 @@
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
       <c r="I56" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="L56" s="7" t="s">
         <v>16</v>
@@ -2278,7 +2290,7 @@
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
       <c r="I57" s="2" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="L57" s="7" t="s">
         <v>16</v>
@@ -2294,7 +2306,7 @@
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
       <c r="I58" s="2" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="L58" s="7" t="s">
         <v>16</v>
@@ -2303,8 +2315,8 @@
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="36"/>
       <c r="B59" s="2"/>
-      <c r="C59" s="2" t="s">
-        <v>121</v>
+      <c r="C59" s="28" t="s">
+        <v>112</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>12</v>
@@ -2316,7 +2328,7 @@
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
       <c r="I59" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="L59" s="7" t="s">
         <v>16</v>
@@ -2332,7 +2344,7 @@
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
       <c r="I60" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="L60" s="7" t="s">
         <v>16</v>
@@ -2348,131 +2360,129 @@
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
       <c r="I61" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L61" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A62" s="37"/>
-      <c r="B62" s="13"/>
-      <c r="D62" s="13"/>
-      <c r="E62" s="13"/>
-      <c r="F62" s="13"/>
-      <c r="G62" s="13"/>
-      <c r="H62" s="13"/>
-      <c r="I62" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="J62" s="13"/>
+      <c r="A62" s="36"/>
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="2"/>
+      <c r="E62" s="2"/>
+      <c r="F62" s="2"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="2"/>
+      <c r="I62" s="2" t="s">
+        <v>116</v>
+      </c>
       <c r="L62" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A63" s="35" t="s">
-        <v>63</v>
-      </c>
-      <c r="B63" s="16">
-        <v>1</v>
-      </c>
-      <c r="C63" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="D63" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="E63" s="17"/>
-      <c r="F63" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="G63" s="16">
-        <v>8</v>
-      </c>
-      <c r="H63" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="I63" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="J63" s="18"/>
-      <c r="K63" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="L63" s="22"/>
+      <c r="A63" s="36"/>
+      <c r="B63" s="2"/>
+      <c r="C63" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G63" s="2"/>
+      <c r="H63" s="2"/>
+      <c r="I63" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="L63" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="36"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
       <c r="D64" s="2"/>
-      <c r="E64" s="3"/>
+      <c r="E64" s="2"/>
       <c r="F64" s="2"/>
-      <c r="G64" s="3"/>
+      <c r="G64" s="2"/>
       <c r="H64" s="2"/>
       <c r="I64" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="J64" s="8"/>
-      <c r="K64" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L64" s="9"/>
+        <v>118</v>
+      </c>
+      <c r="L64" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" s="36"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
       <c r="D65" s="2"/>
-      <c r="E65" s="3"/>
+      <c r="E65" s="2"/>
       <c r="F65" s="2"/>
-      <c r="G65" s="3"/>
+      <c r="G65" s="2"/>
       <c r="H65" s="2"/>
       <c r="I65" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J65" s="8"/>
-      <c r="K65" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L65" s="9"/>
+        <v>119</v>
+      </c>
+      <c r="L65" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A66" s="36"/>
-      <c r="B66" s="2"/>
-      <c r="C66" s="2"/>
-      <c r="D66" s="2"/>
-      <c r="E66" s="3"/>
-      <c r="F66" s="2"/>
-      <c r="G66" s="3"/>
-      <c r="H66" s="2"/>
-      <c r="I66" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="J66" s="8"/>
-      <c r="K66" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L66" s="9"/>
+      <c r="A66" s="37"/>
+      <c r="B66" s="13"/>
+      <c r="D66" s="13"/>
+      <c r="E66" s="13"/>
+      <c r="F66" s="13"/>
+      <c r="G66" s="13"/>
+      <c r="H66" s="13"/>
+      <c r="I66" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="J66" s="13"/>
+      <c r="L66" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A67" s="36"/>
-      <c r="B67" s="2"/>
-      <c r="C67" s="2"/>
-      <c r="D67" s="2"/>
-      <c r="E67" s="3"/>
-      <c r="F67" s="2"/>
-      <c r="G67" s="3"/>
-      <c r="H67" s="2"/>
-      <c r="I67" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="J67" s="8"/>
-      <c r="K67" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L67" s="9"/>
+      <c r="A67" s="35" t="s">
+        <v>63</v>
+      </c>
+      <c r="B67" s="16">
+        <v>1</v>
+      </c>
+      <c r="C67" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D67" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="E67" s="17"/>
+      <c r="F67" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="G67" s="16">
+        <v>8</v>
+      </c>
+      <c r="H67" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="I67" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="J67" s="18"/>
+      <c r="K67" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="L67" s="22"/>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" s="36"/>
@@ -2484,7 +2494,7 @@
       <c r="G68" s="3"/>
       <c r="H68" s="2"/>
       <c r="I68" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="J68" s="8"/>
       <c r="K68" s="4" t="s">
@@ -2502,7 +2512,7 @@
       <c r="G69" s="3"/>
       <c r="H69" s="2"/>
       <c r="I69" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="J69" s="8"/>
       <c r="K69" s="4" t="s">
@@ -2511,116 +2521,120 @@
       <c r="L69" s="9"/>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A70" s="37"/>
-      <c r="B70" s="14"/>
-      <c r="C70" s="14"/>
-      <c r="D70" s="14"/>
-      <c r="E70" s="20"/>
-      <c r="F70" s="14"/>
-      <c r="G70" s="20"/>
-      <c r="H70" s="14"/>
-      <c r="I70" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="J70" s="21"/>
-      <c r="K70" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="L70" s="10"/>
+      <c r="A70" s="36"/>
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="2"/>
+      <c r="E70" s="3"/>
+      <c r="F70" s="2"/>
+      <c r="G70" s="3"/>
+      <c r="H70" s="2"/>
+      <c r="I70" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J70" s="8"/>
+      <c r="K70" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L70" s="9"/>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A71" s="32" t="s">
-        <v>64</v>
-      </c>
-      <c r="B71" s="2">
-        <v>1</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>22</v>
-      </c>
+      <c r="A71" s="36"/>
+      <c r="B71" s="2"/>
+      <c r="C71" s="2"/>
+      <c r="D71" s="2"/>
       <c r="E71" s="3"/>
-      <c r="F71" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G71" s="2">
-        <v>14</v>
-      </c>
-      <c r="H71" s="2" t="s">
-        <v>23</v>
-      </c>
+      <c r="F71" s="2"/>
+      <c r="G71" s="3"/>
+      <c r="H71" s="2"/>
       <c r="I71" s="2" t="s">
-        <v>71</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="J71" s="8"/>
       <c r="K71" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L71" s="25"/>
+      <c r="L71" s="9"/>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A72" s="33"/>
+      <c r="A72" s="36"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
       <c r="D72" s="2"/>
-      <c r="E72" s="2"/>
+      <c r="E72" s="3"/>
       <c r="F72" s="2"/>
-      <c r="G72" s="2"/>
+      <c r="G72" s="3"/>
       <c r="H72" s="2"/>
       <c r="I72" s="2" t="s">
-        <v>72</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="J72" s="8"/>
       <c r="K72" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L72" s="25"/>
+      <c r="L72" s="9"/>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A73" s="33"/>
+      <c r="A73" s="36"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
       <c r="D73" s="2"/>
-      <c r="E73" s="2"/>
+      <c r="E73" s="3"/>
       <c r="F73" s="2"/>
-      <c r="G73" s="2"/>
+      <c r="G73" s="3"/>
       <c r="H73" s="2"/>
       <c r="I73" s="2" t="s">
-        <v>73</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="J73" s="8"/>
       <c r="K73" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L73" s="25"/>
+      <c r="L73" s="9"/>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A74" s="33"/>
-      <c r="B74" s="2"/>
-      <c r="C74" s="2"/>
-      <c r="D74" s="2"/>
-      <c r="E74" s="2"/>
-      <c r="F74" s="2"/>
-      <c r="G74" s="2"/>
-      <c r="H74" s="2"/>
-      <c r="I74" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="K74" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L74" s="25"/>
+      <c r="A74" s="37"/>
+      <c r="B74" s="14"/>
+      <c r="C74" s="14"/>
+      <c r="D74" s="14"/>
+      <c r="E74" s="20"/>
+      <c r="F74" s="14"/>
+      <c r="G74" s="20"/>
+      <c r="H74" s="14"/>
+      <c r="I74" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="J74" s="21"/>
+      <c r="K74" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L74" s="10"/>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A75" s="33"/>
-      <c r="B75" s="2"/>
-      <c r="C75" s="2"/>
-      <c r="D75" s="2"/>
-      <c r="E75" s="2"/>
-      <c r="F75" s="2"/>
-      <c r="G75" s="2"/>
-      <c r="H75" s="2"/>
+      <c r="A75" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="B75" s="2">
+        <v>1</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E75" s="3"/>
+      <c r="F75" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G75" s="2">
+        <v>14</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="I75" s="2" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="K75" s="4" t="s">
         <v>16</v>
@@ -2637,7 +2651,7 @@
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
       <c r="I76" s="2" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="K76" s="4" t="s">
         <v>16</v>
@@ -2654,7 +2668,7 @@
       <c r="G77" s="2"/>
       <c r="H77" s="2"/>
       <c r="I77" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="K77" s="4" t="s">
         <v>16</v>
@@ -2664,16 +2678,14 @@
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" s="33"/>
       <c r="B78" s="2"/>
-      <c r="C78" s="28" t="s">
-        <v>89</v>
-      </c>
+      <c r="C78" s="2"/>
       <c r="D78" s="2"/>
       <c r="E78" s="2"/>
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
       <c r="H78" s="2"/>
       <c r="I78" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K78" s="4" t="s">
         <v>16</v>
@@ -2690,7 +2702,7 @@
       <c r="G79" s="2"/>
       <c r="H79" s="2"/>
       <c r="I79" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K79" s="4" t="s">
         <v>16</v>
@@ -2707,7 +2719,7 @@
       <c r="G80" s="2"/>
       <c r="H80" s="2"/>
       <c r="I80" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="K80" s="4" t="s">
         <v>16</v>
@@ -2724,7 +2736,7 @@
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
       <c r="I81" s="2" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="K81" s="4" t="s">
         <v>16</v>
@@ -2734,14 +2746,16 @@
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" s="33"/>
       <c r="B82" s="2"/>
-      <c r="C82" s="2"/>
+      <c r="C82" s="28" t="s">
+        <v>89</v>
+      </c>
       <c r="D82" s="2"/>
       <c r="E82" s="2"/>
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
       <c r="H82" s="2"/>
       <c r="I82" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="K82" s="4" t="s">
         <v>16</v>
@@ -2758,7 +2772,7 @@
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
       <c r="I83" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="K83" s="4" t="s">
         <v>16</v>
@@ -2775,7 +2789,7 @@
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
       <c r="I84" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="K84" s="4" t="s">
         <v>16</v>
@@ -2784,27 +2798,15 @@
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" s="33"/>
-      <c r="B85" s="2">
-        <v>2</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E85" s="3"/>
-      <c r="F85" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G85" s="2">
-        <v>6</v>
-      </c>
-      <c r="H85" s="2" t="s">
-        <v>23</v>
-      </c>
+      <c r="B85" s="2"/>
+      <c r="C85" s="2"/>
+      <c r="D85" s="2"/>
+      <c r="E85" s="2"/>
+      <c r="F85" s="2"/>
+      <c r="G85" s="2"/>
+      <c r="H85" s="2"/>
       <c r="I85" s="2" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="K85" s="4" t="s">
         <v>16</v>
@@ -2821,7 +2823,7 @@
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
       <c r="I86" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K86" s="4" t="s">
         <v>16</v>
@@ -2838,7 +2840,7 @@
       <c r="G87" s="2"/>
       <c r="H87" s="2"/>
       <c r="I87" s="2" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="K87" s="4" t="s">
         <v>16</v>
@@ -2855,7 +2857,7 @@
       <c r="G88" s="2"/>
       <c r="H88" s="2"/>
       <c r="I88" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="K88" s="4" t="s">
         <v>16</v>
@@ -2864,17 +2866,27 @@
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" s="33"/>
-      <c r="B89" s="2"/>
+      <c r="B89" s="2">
+        <v>2</v>
+      </c>
       <c r="C89" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D89" s="2"/>
-      <c r="E89" s="2"/>
-      <c r="F89" s="2"/>
-      <c r="G89" s="2"/>
-      <c r="H89" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E89" s="3"/>
+      <c r="F89" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G89" s="2">
+        <v>6</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="I89" s="2" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="K89" s="4" t="s">
         <v>16</v>
@@ -2891,7 +2903,7 @@
       <c r="G90" s="2"/>
       <c r="H90" s="2"/>
       <c r="I90" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K90" s="4" t="s">
         <v>16</v>
@@ -2900,34 +2912,20 @@
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" s="33"/>
-      <c r="B91" s="2">
-        <v>3</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E91" s="2">
-        <v>1</v>
-      </c>
-      <c r="F91" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="G91" s="2">
-        <v>4</v>
-      </c>
-      <c r="H91" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="B91" s="2"/>
+      <c r="C91" s="2"/>
+      <c r="D91" s="2"/>
+      <c r="E91" s="2"/>
+      <c r="F91" s="2"/>
+      <c r="G91" s="2"/>
+      <c r="H91" s="2"/>
       <c r="I91" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="K91" s="27"/>
-      <c r="L91" s="7" t="s">
-        <v>16</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="K91" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L91" s="25"/>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" s="33"/>
@@ -2939,29 +2937,31 @@
       <c r="G92" s="2"/>
       <c r="H92" s="2"/>
       <c r="I92" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="K92" s="27"/>
-      <c r="L92" s="7" t="s">
-        <v>16</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="K92" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L92" s="25"/>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" s="33"/>
       <c r="B93" s="2"/>
-      <c r="C93" s="2"/>
+      <c r="C93" s="2" t="s">
+        <v>69</v>
+      </c>
       <c r="D93" s="2"/>
       <c r="E93" s="2"/>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
       <c r="H93" s="2"/>
       <c r="I93" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="K93" s="27"/>
-      <c r="L93" s="7" t="s">
-        <v>16</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="K93" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L93" s="25"/>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" s="33"/>
@@ -2973,20 +2973,20 @@
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
       <c r="I94" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="K94" s="27"/>
-      <c r="L94" s="7" t="s">
-        <v>16</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="K94" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L94" s="25"/>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" s="33"/>
       <c r="B95" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>125</v>
+        <v>89</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>12</v>
@@ -3004,7 +3004,7 @@
         <v>14</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="K95" s="27"/>
       <c r="L95" s="7" t="s">
@@ -3021,7 +3021,7 @@
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
       <c r="I96" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="K96" s="27"/>
       <c r="L96" s="7" t="s">
@@ -3038,7 +3038,7 @@
       <c r="G97" s="2"/>
       <c r="H97" s="2"/>
       <c r="I97" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="K97" s="27"/>
       <c r="L97" s="7" t="s">
@@ -3046,29 +3046,111 @@
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A98" s="34"/>
-      <c r="B98" s="14"/>
-      <c r="C98" s="14"/>
-      <c r="D98" s="14"/>
-      <c r="E98" s="14"/>
-      <c r="F98" s="14"/>
-      <c r="G98" s="14"/>
-      <c r="H98" s="14"/>
-      <c r="I98" s="14" t="s">
+      <c r="A98" s="33"/>
+      <c r="B98" s="2"/>
+      <c r="C98" s="2"/>
+      <c r="D98" s="2"/>
+      <c r="E98" s="2"/>
+      <c r="F98" s="2"/>
+      <c r="G98" s="2"/>
+      <c r="H98" s="2"/>
+      <c r="I98" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="K98" s="27"/>
+      <c r="L98" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A99" s="33"/>
+      <c r="B99" s="2">
+        <v>4</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E99" s="2">
+        <v>1</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="G99" s="2">
+        <v>4</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I99" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="K99" s="27"/>
+      <c r="L99" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A100" s="33"/>
+      <c r="B100" s="2"/>
+      <c r="C100" s="2"/>
+      <c r="D100" s="2"/>
+      <c r="E100" s="2"/>
+      <c r="F100" s="2"/>
+      <c r="G100" s="2"/>
+      <c r="H100" s="2"/>
+      <c r="I100" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="K100" s="27"/>
+      <c r="L100" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A101" s="33"/>
+      <c r="B101" s="2"/>
+      <c r="C101" s="2"/>
+      <c r="D101" s="2"/>
+      <c r="E101" s="2"/>
+      <c r="F101" s="2"/>
+      <c r="G101" s="2"/>
+      <c r="H101" s="2"/>
+      <c r="I101" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="K101" s="27"/>
+      <c r="L101" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A102" s="34"/>
+      <c r="B102" s="14"/>
+      <c r="C102" s="14"/>
+      <c r="D102" s="14"/>
+      <c r="E102" s="14"/>
+      <c r="F102" s="14"/>
+      <c r="G102" s="14"/>
+      <c r="H102" s="14"/>
+      <c r="I102" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="J98" s="13"/>
-      <c r="K98" s="30"/>
-      <c r="L98" s="29" t="s">
+      <c r="J102" s="13"/>
+      <c r="K102" s="30"/>
+      <c r="L102" s="29" t="s">
         <v>16</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A71:A98"/>
+    <mergeCell ref="A75:A102"/>
     <mergeCell ref="A36:A41"/>
-    <mergeCell ref="A42:A62"/>
-    <mergeCell ref="A63:A70"/>
+    <mergeCell ref="A42:A66"/>
+    <mergeCell ref="A67:A74"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A4:A21"/>
@@ -3081,6 +3163,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EA9F74FD6C93414BACF2D33AB9B46B1F" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="85e183139a7bf430a5cd367af777ffd1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="d7b47298-7dbc-4c4a-b955-e35738c83845" xmlns:ns4="4c7a27d0-c111-49d1-947f-3e415c425751" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5e8b728fb78f9c3c3084b9e953d972a7" ns3:_="" ns4:_="">
     <xsd:import namespace="d7b47298-7dbc-4c4a-b955-e35738c83845"/>
@@ -3313,15 +3404,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -3331,6 +3413,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0006E415-A18B-4726-A1A0-54EC3A4B0653}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CAFAC10-0FD0-4107-B657-53CDB5D6D5F8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3345,14 +3435,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0006E415-A18B-4726-A1A0-54EC3A4B0653}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Greyform/Python_Application/PinAllocationBOMforPBU_T1am.xlsx
+++ b/Greyform/Python_Application/PinAllocationBOMforPBU_T1am.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MokZhiZhuan\OneDrive - WINSYS TECHNOLOGY PTE LTD\Documents\GitHub\GreyForm_UI\Greyform\Python_Application\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C7CA7B3-ADF5-4354-87E1-B4E85A619DF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5755E839-B70A-4D09-81A5-7C939583A930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="735" windowWidth="23235" windowHeight="15465" xr2:uid="{10577398-EA94-4D34-AF72-AAEF7879495C}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="23235" windowHeight="15465" xr2:uid="{10577398-EA94-4D34-AF72-AAEF7879495C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="148">
   <si>
     <t>Wall</t>
   </si>
@@ -465,6 +465,21 @@
   </si>
   <si>
     <t>TMP5S2b4</t>
+  </si>
+  <si>
+    <t>BSS.GESSI.SM.49079</t>
+  </si>
+  <si>
+    <t>LP3S3b1</t>
+  </si>
+  <si>
+    <t>LP3S3b2</t>
+  </si>
+  <si>
+    <t>LP3S3b3</t>
+  </si>
+  <si>
+    <t>LP3S3b4</t>
   </si>
 </sst>
 </file>
@@ -701,7 +716,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -813,6 +828,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1149,7 +1167,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45C9410D-7727-4F15-9679-20A483A9E846}">
-  <dimension ref="A1:L102"/>
+  <dimension ref="A1:L106"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.42578125" bestFit="1" customWidth="1"/>
@@ -1319,7 +1337,7 @@
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="36"/>
       <c r="B8" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>94</v>
@@ -1481,7 +1499,7 @@
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="36"/>
       <c r="B16" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>21</v>
@@ -1564,7 +1582,9 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="36"/>
-      <c r="B20" s="2"/>
+      <c r="B20" s="2">
+        <v>4</v>
+      </c>
       <c r="C20" s="2" t="s">
         <v>88</v>
       </c>
@@ -1793,10 +1813,9 @@
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="36"/>
       <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
+      <c r="D31" s="42"/>
       <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
+      <c r="F31" s="42"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2" t="s">
@@ -1810,91 +1829,83 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="36"/>
-      <c r="B32" s="2">
-        <v>2</v>
-      </c>
+      <c r="B32" s="2"/>
       <c r="C32" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E32" s="3"/>
-      <c r="F32" s="2" t="s">
-        <v>22</v>
+        <v>143</v>
+      </c>
+      <c r="D32" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="E32" s="2"/>
+      <c r="F32" s="42" t="s">
+        <v>13</v>
       </c>
       <c r="G32" s="2">
-        <v>8</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>23</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="H32" s="2"/>
       <c r="I32" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="K32" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L32" s="25"/>
+        <v>144</v>
+      </c>
+      <c r="J32" s="27"/>
+      <c r="K32" s="27"/>
+      <c r="L32" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="36"/>
       <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
+      <c r="D33" s="42"/>
       <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
+      <c r="F33" s="42"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="K33" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L33" s="25"/>
+        <v>145</v>
+      </c>
+      <c r="J33" s="27"/>
+      <c r="K33" s="27"/>
+      <c r="L33" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="36"/>
       <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
+      <c r="D34" s="42"/>
       <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
+      <c r="F34" s="42"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="K34" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L34" s="25"/>
+        <v>146</v>
+      </c>
+      <c r="J34" s="27"/>
+      <c r="K34" s="27"/>
+      <c r="L34" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="36"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="J35" s="13"/>
-      <c r="K35" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="L35" s="31"/>
+      <c r="B35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="J35" s="27"/>
+      <c r="K35" s="27"/>
+      <c r="L35" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="35" t="s">
-        <v>53</v>
-      </c>
+      <c r="A36" s="36"/>
       <c r="B36" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>21</v>
@@ -1907,19 +1918,18 @@
         <v>22</v>
       </c>
       <c r="G36" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>23</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="J36" s="27"/>
+        <v>49</v>
+      </c>
       <c r="K36" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L36" s="9"/>
+      <c r="L36" s="25"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="36"/>
@@ -1931,13 +1941,12 @@
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
       <c r="I37" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="J37" s="27"/>
+        <v>50</v>
+      </c>
       <c r="K37" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L37" s="9"/>
+      <c r="L37" s="25"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="36"/>
@@ -1949,92 +1958,98 @@
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
       <c r="I38" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="J38" s="27"/>
+        <v>51</v>
+      </c>
       <c r="K38" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L38" s="9"/>
+      <c r="L38" s="25"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="36"/>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="J39" s="27"/>
-      <c r="K39" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L39" s="9"/>
+      <c r="B39" s="14"/>
+      <c r="C39" s="14"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="14"/>
+      <c r="F39" s="14"/>
+      <c r="G39" s="14"/>
+      <c r="H39" s="14"/>
+      <c r="I39" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J39" s="13"/>
+      <c r="K39" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L39" s="31"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A40" s="36"/>
-      <c r="C40" s="28" t="s">
-        <v>138</v>
+      <c r="A40" s="35" t="s">
+        <v>53</v>
+      </c>
+      <c r="B40" s="2">
+        <v>1</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E40" s="3"/>
+      <c r="F40" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G40" s="2">
+        <v>5</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="L40" s="7" t="s">
-        <v>16</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="J40" s="27"/>
+      <c r="K40" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L40" s="9"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A41" s="37"/>
-      <c r="B41" s="13"/>
-      <c r="C41" s="13"/>
-      <c r="D41" s="13"/>
-      <c r="E41" s="13"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="13"/>
-      <c r="H41" s="13"/>
-      <c r="I41" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="J41" s="13"/>
-      <c r="K41" s="13"/>
-      <c r="L41" s="29" t="s">
-        <v>16</v>
-      </c>
+      <c r="A41" s="36"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="J41" s="27"/>
+      <c r="K41" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L41" s="9"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A42" s="35" t="s">
-        <v>58</v>
-      </c>
-      <c r="B42" s="2">
-        <v>1</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E42" s="3"/>
-      <c r="F42" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G42" s="2">
-        <v>4</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>23</v>
-      </c>
+      <c r="A42" s="36"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
       <c r="I42" s="2" t="s">
-        <v>60</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="J42" s="27"/>
       <c r="K42" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L42" s="25"/>
+      <c r="L42" s="9"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="36"/>
@@ -2046,60 +2061,72 @@
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
       <c r="I43" s="2" t="s">
-        <v>61</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="J43" s="27"/>
       <c r="K43" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L43" s="25"/>
+      <c r="L43" s="9"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="36"/>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2"/>
+      <c r="B44" s="28">
+        <v>2</v>
+      </c>
+      <c r="C44" s="28" t="s">
+        <v>138</v>
+      </c>
       <c r="I44" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="K44" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L44" s="25"/>
+        <v>136</v>
+      </c>
+      <c r="L44" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A45" s="36"/>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2" t="s">
+      <c r="A45" s="37"/>
+      <c r="B45" s="13"/>
+      <c r="C45" s="13"/>
+      <c r="D45" s="13"/>
+      <c r="E45" s="13"/>
+      <c r="F45" s="13"/>
+      <c r="G45" s="13"/>
+      <c r="H45" s="13"/>
+      <c r="I45" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="J45" s="13"/>
+      <c r="K45" s="13"/>
+      <c r="L45" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A46" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="B46" s="2">
+        <v>1</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="K45" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L45" s="25"/>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A46" s="36"/>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
+      <c r="D46" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E46" s="3"/>
+      <c r="F46" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G46" s="2">
+        <v>4</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="I46" s="2" t="s">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="K46" s="4" t="s">
         <v>16</v>
@@ -2116,7 +2143,7 @@
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
       <c r="I47" s="2" t="s">
-        <v>141</v>
+        <v>61</v>
       </c>
       <c r="K47" s="4" t="s">
         <v>16</v>
@@ -2133,7 +2160,7 @@
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
       <c r="I48" s="2" t="s">
-        <v>142</v>
+        <v>62</v>
       </c>
       <c r="K48" s="4" t="s">
         <v>16</v>
@@ -2142,25 +2169,24 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="36"/>
-      <c r="B49" s="2"/>
-      <c r="C49" s="28" t="s">
-        <v>105</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="B49" s="2">
+        <v>2</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D49" s="2"/>
       <c r="E49" s="2"/>
-      <c r="F49" s="2" t="s">
-        <v>20</v>
-      </c>
+      <c r="F49" s="2"/>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
       <c r="I49" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="L49" s="7" t="s">
-        <v>16</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="K49" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L49" s="25"/>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="36"/>
@@ -2172,11 +2198,12 @@
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
       <c r="I50" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="L50" s="7" t="s">
-        <v>16</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="K50" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L50" s="25"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="36"/>
@@ -2188,11 +2215,12 @@
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
       <c r="I51" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="L51" s="7" t="s">
-        <v>16</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="K51" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L51" s="25"/>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="36"/>
@@ -2204,23 +2232,32 @@
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
       <c r="I52" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="L52" s="7" t="s">
-        <v>16</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="K52" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L52" s="25"/>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="36"/>
-      <c r="B53" s="2"/>
-      <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
+      <c r="B53" s="2">
+        <v>3</v>
+      </c>
+      <c r="C53" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="E53" s="2"/>
-      <c r="F53" s="2"/>
+      <c r="F53" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
       <c r="I53" s="2" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="L53" s="7" t="s">
         <v>16</v>
@@ -2229,20 +2266,14 @@
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="36"/>
       <c r="B54" s="2"/>
-      <c r="C54" s="28" t="s">
-        <v>88</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
       <c r="E54" s="2"/>
-      <c r="F54" s="2" t="s">
-        <v>20</v>
-      </c>
+      <c r="F54" s="2"/>
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
       <c r="I54" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L54" s="7" t="s">
         <v>16</v>
@@ -2258,7 +2289,7 @@
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
       <c r="I55" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="L55" s="7" t="s">
         <v>16</v>
@@ -2274,7 +2305,7 @@
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
       <c r="I56" s="2" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="L56" s="7" t="s">
         <v>16</v>
@@ -2290,7 +2321,7 @@
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
       <c r="I57" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L57" s="7" t="s">
         <v>16</v>
@@ -2298,15 +2329,23 @@
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="36"/>
-      <c r="B58" s="2"/>
-      <c r="C58" s="2"/>
-      <c r="D58" s="2"/>
+      <c r="B58" s="2">
+        <v>4</v>
+      </c>
+      <c r="C58" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="E58" s="2"/>
-      <c r="F58" s="2"/>
+      <c r="F58" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
       <c r="I58" s="2" t="s">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="L58" s="7" t="s">
         <v>16</v>
@@ -2315,20 +2354,14 @@
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="36"/>
       <c r="B59" s="2"/>
-      <c r="C59" s="28" t="s">
-        <v>112</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
       <c r="E59" s="2"/>
-      <c r="F59" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="F59" s="2"/>
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
       <c r="I59" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="L59" s="7" t="s">
         <v>16</v>
@@ -2344,7 +2377,7 @@
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
       <c r="I60" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="L60" s="7" t="s">
         <v>16</v>
@@ -2360,7 +2393,7 @@
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
       <c r="I61" s="2" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="L61" s="7" t="s">
         <v>16</v>
@@ -2376,7 +2409,7 @@
       <c r="G62" s="2"/>
       <c r="H62" s="2"/>
       <c r="I62" s="2" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="L62" s="7" t="s">
         <v>16</v>
@@ -2384,9 +2417,11 @@
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="36"/>
-      <c r="B63" s="2"/>
-      <c r="C63" s="2" t="s">
-        <v>121</v>
+      <c r="B63" s="2">
+        <v>5</v>
+      </c>
+      <c r="C63" s="28" t="s">
+        <v>112</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>12</v>
@@ -2398,7 +2433,7 @@
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
       <c r="I63" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="L63" s="7" t="s">
         <v>16</v>
@@ -2414,7 +2449,7 @@
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
       <c r="I64" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="L64" s="7" t="s">
         <v>16</v>
@@ -2430,131 +2465,131 @@
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
       <c r="I65" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L65" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A66" s="37"/>
-      <c r="B66" s="13"/>
-      <c r="D66" s="13"/>
-      <c r="E66" s="13"/>
-      <c r="F66" s="13"/>
-      <c r="G66" s="13"/>
-      <c r="H66" s="13"/>
-      <c r="I66" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="J66" s="13"/>
+      <c r="A66" s="36"/>
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="2"/>
+      <c r="E66" s="2"/>
+      <c r="F66" s="2"/>
+      <c r="G66" s="2"/>
+      <c r="H66" s="2"/>
+      <c r="I66" s="2" t="s">
+        <v>116</v>
+      </c>
       <c r="L66" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A67" s="35" t="s">
-        <v>63</v>
-      </c>
-      <c r="B67" s="16">
-        <v>1</v>
-      </c>
-      <c r="C67" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="D67" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="E67" s="17"/>
-      <c r="F67" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="G67" s="16">
-        <v>8</v>
-      </c>
-      <c r="H67" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="I67" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="J67" s="18"/>
-      <c r="K67" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="L67" s="22"/>
+      <c r="A67" s="36"/>
+      <c r="B67" s="2">
+        <v>6</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G67" s="2"/>
+      <c r="H67" s="2"/>
+      <c r="I67" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="L67" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" s="36"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
       <c r="D68" s="2"/>
-      <c r="E68" s="3"/>
+      <c r="E68" s="2"/>
       <c r="F68" s="2"/>
-      <c r="G68" s="3"/>
+      <c r="G68" s="2"/>
       <c r="H68" s="2"/>
       <c r="I68" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="J68" s="8"/>
-      <c r="K68" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L68" s="9"/>
+        <v>118</v>
+      </c>
+      <c r="L68" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" s="36"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
       <c r="D69" s="2"/>
-      <c r="E69" s="3"/>
+      <c r="E69" s="2"/>
       <c r="F69" s="2"/>
-      <c r="G69" s="3"/>
+      <c r="G69" s="2"/>
       <c r="H69" s="2"/>
       <c r="I69" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J69" s="8"/>
-      <c r="K69" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L69" s="9"/>
+        <v>119</v>
+      </c>
+      <c r="L69" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A70" s="36"/>
-      <c r="B70" s="2"/>
-      <c r="C70" s="2"/>
-      <c r="D70" s="2"/>
-      <c r="E70" s="3"/>
-      <c r="F70" s="2"/>
-      <c r="G70" s="3"/>
-      <c r="H70" s="2"/>
-      <c r="I70" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="J70" s="8"/>
-      <c r="K70" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L70" s="9"/>
+      <c r="A70" s="37"/>
+      <c r="B70" s="13"/>
+      <c r="D70" s="13"/>
+      <c r="E70" s="13"/>
+      <c r="F70" s="13"/>
+      <c r="G70" s="13"/>
+      <c r="H70" s="13"/>
+      <c r="I70" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="J70" s="13"/>
+      <c r="L70" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A71" s="36"/>
-      <c r="B71" s="2"/>
-      <c r="C71" s="2"/>
-      <c r="D71" s="2"/>
-      <c r="E71" s="3"/>
-      <c r="F71" s="2"/>
-      <c r="G71" s="3"/>
-      <c r="H71" s="2"/>
-      <c r="I71" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="J71" s="8"/>
-      <c r="K71" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L71" s="9"/>
+      <c r="A71" s="35" t="s">
+        <v>63</v>
+      </c>
+      <c r="B71" s="16">
+        <v>1</v>
+      </c>
+      <c r="C71" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D71" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="E71" s="17"/>
+      <c r="F71" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="G71" s="16">
+        <v>8</v>
+      </c>
+      <c r="H71" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="I71" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="J71" s="18"/>
+      <c r="K71" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="L71" s="22"/>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" s="36"/>
@@ -2566,7 +2601,7 @@
       <c r="G72" s="3"/>
       <c r="H72" s="2"/>
       <c r="I72" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="J72" s="8"/>
       <c r="K72" s="4" t="s">
@@ -2584,7 +2619,7 @@
       <c r="G73" s="3"/>
       <c r="H73" s="2"/>
       <c r="I73" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="J73" s="8"/>
       <c r="K73" s="4" t="s">
@@ -2593,116 +2628,120 @@
       <c r="L73" s="9"/>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A74" s="37"/>
-      <c r="B74" s="14"/>
-      <c r="C74" s="14"/>
-      <c r="D74" s="14"/>
-      <c r="E74" s="20"/>
-      <c r="F74" s="14"/>
-      <c r="G74" s="20"/>
-      <c r="H74" s="14"/>
-      <c r="I74" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="J74" s="21"/>
-      <c r="K74" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="L74" s="10"/>
+      <c r="A74" s="36"/>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="3"/>
+      <c r="F74" s="2"/>
+      <c r="G74" s="3"/>
+      <c r="H74" s="2"/>
+      <c r="I74" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J74" s="8"/>
+      <c r="K74" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L74" s="9"/>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A75" s="32" t="s">
-        <v>64</v>
-      </c>
-      <c r="B75" s="2">
-        <v>1</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>22</v>
-      </c>
+      <c r="A75" s="36"/>
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="2"/>
       <c r="E75" s="3"/>
-      <c r="F75" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G75" s="2">
-        <v>14</v>
-      </c>
-      <c r="H75" s="2" t="s">
-        <v>23</v>
-      </c>
+      <c r="F75" s="2"/>
+      <c r="G75" s="3"/>
+      <c r="H75" s="2"/>
       <c r="I75" s="2" t="s">
-        <v>71</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="J75" s="8"/>
       <c r="K75" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L75" s="25"/>
+      <c r="L75" s="9"/>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A76" s="33"/>
+      <c r="A76" s="36"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
       <c r="D76" s="2"/>
-      <c r="E76" s="2"/>
+      <c r="E76" s="3"/>
       <c r="F76" s="2"/>
-      <c r="G76" s="2"/>
+      <c r="G76" s="3"/>
       <c r="H76" s="2"/>
       <c r="I76" s="2" t="s">
-        <v>72</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="J76" s="8"/>
       <c r="K76" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L76" s="25"/>
+      <c r="L76" s="9"/>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A77" s="33"/>
+      <c r="A77" s="36"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
       <c r="D77" s="2"/>
-      <c r="E77" s="2"/>
+      <c r="E77" s="3"/>
       <c r="F77" s="2"/>
-      <c r="G77" s="2"/>
+      <c r="G77" s="3"/>
       <c r="H77" s="2"/>
       <c r="I77" s="2" t="s">
-        <v>73</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="J77" s="8"/>
       <c r="K77" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L77" s="25"/>
+      <c r="L77" s="9"/>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A78" s="33"/>
-      <c r="B78" s="2"/>
-      <c r="C78" s="2"/>
-      <c r="D78" s="2"/>
-      <c r="E78" s="2"/>
-      <c r="F78" s="2"/>
-      <c r="G78" s="2"/>
-      <c r="H78" s="2"/>
-      <c r="I78" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="K78" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L78" s="25"/>
+      <c r="A78" s="37"/>
+      <c r="B78" s="14"/>
+      <c r="C78" s="14"/>
+      <c r="D78" s="14"/>
+      <c r="E78" s="20"/>
+      <c r="F78" s="14"/>
+      <c r="G78" s="20"/>
+      <c r="H78" s="14"/>
+      <c r="I78" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="J78" s="21"/>
+      <c r="K78" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L78" s="10"/>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A79" s="33"/>
-      <c r="B79" s="2"/>
-      <c r="C79" s="2"/>
-      <c r="D79" s="2"/>
-      <c r="E79" s="2"/>
-      <c r="F79" s="2"/>
-      <c r="G79" s="2"/>
-      <c r="H79" s="2"/>
+      <c r="A79" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="B79" s="2">
+        <v>1</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E79" s="3"/>
+      <c r="F79" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G79" s="2">
+        <v>14</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="I79" s="2" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="K79" s="4" t="s">
         <v>16</v>
@@ -2719,7 +2758,7 @@
       <c r="G80" s="2"/>
       <c r="H80" s="2"/>
       <c r="I80" s="2" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="K80" s="4" t="s">
         <v>16</v>
@@ -2736,7 +2775,7 @@
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
       <c r="I81" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="K81" s="4" t="s">
         <v>16</v>
@@ -2746,16 +2785,14 @@
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" s="33"/>
       <c r="B82" s="2"/>
-      <c r="C82" s="28" t="s">
-        <v>89</v>
-      </c>
+      <c r="C82" s="2"/>
       <c r="D82" s="2"/>
       <c r="E82" s="2"/>
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
       <c r="H82" s="2"/>
       <c r="I82" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K82" s="4" t="s">
         <v>16</v>
@@ -2772,7 +2809,7 @@
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
       <c r="I83" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K83" s="4" t="s">
         <v>16</v>
@@ -2789,7 +2826,7 @@
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
       <c r="I84" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="K84" s="4" t="s">
         <v>16</v>
@@ -2806,7 +2843,7 @@
       <c r="G85" s="2"/>
       <c r="H85" s="2"/>
       <c r="I85" s="2" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="K85" s="4" t="s">
         <v>16</v>
@@ -2815,15 +2852,19 @@
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" s="33"/>
-      <c r="B86" s="2"/>
-      <c r="C86" s="2"/>
+      <c r="B86" s="2">
+        <v>2</v>
+      </c>
+      <c r="C86" s="28" t="s">
+        <v>89</v>
+      </c>
       <c r="D86" s="2"/>
       <c r="E86" s="2"/>
       <c r="F86" s="2"/>
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
       <c r="I86" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="K86" s="4" t="s">
         <v>16</v>
@@ -2840,7 +2881,7 @@
       <c r="G87" s="2"/>
       <c r="H87" s="2"/>
       <c r="I87" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="K87" s="4" t="s">
         <v>16</v>
@@ -2857,7 +2898,7 @@
       <c r="G88" s="2"/>
       <c r="H88" s="2"/>
       <c r="I88" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="K88" s="4" t="s">
         <v>16</v>
@@ -2866,27 +2907,15 @@
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" s="33"/>
-      <c r="B89" s="2">
-        <v>2</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E89" s="3"/>
-      <c r="F89" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G89" s="2">
-        <v>6</v>
-      </c>
-      <c r="H89" s="2" t="s">
-        <v>23</v>
-      </c>
+      <c r="B89" s="2"/>
+      <c r="C89" s="2"/>
+      <c r="D89" s="2"/>
+      <c r="E89" s="2"/>
+      <c r="F89" s="2"/>
+      <c r="G89" s="2"/>
+      <c r="H89" s="2"/>
       <c r="I89" s="2" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="K89" s="4" t="s">
         <v>16</v>
@@ -2903,7 +2932,7 @@
       <c r="G90" s="2"/>
       <c r="H90" s="2"/>
       <c r="I90" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K90" s="4" t="s">
         <v>16</v>
@@ -2920,7 +2949,7 @@
       <c r="G91" s="2"/>
       <c r="H91" s="2"/>
       <c r="I91" s="2" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="K91" s="4" t="s">
         <v>16</v>
@@ -2937,7 +2966,7 @@
       <c r="G92" s="2"/>
       <c r="H92" s="2"/>
       <c r="I92" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="K92" s="4" t="s">
         <v>16</v>
@@ -2946,17 +2975,27 @@
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" s="33"/>
-      <c r="B93" s="2"/>
+      <c r="B93" s="2">
+        <v>3</v>
+      </c>
       <c r="C93" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D93" s="2"/>
-      <c r="E93" s="2"/>
-      <c r="F93" s="2"/>
-      <c r="G93" s="2"/>
-      <c r="H93" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E93" s="3"/>
+      <c r="F93" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G93" s="2">
+        <v>6</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="I93" s="2" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="K93" s="4" t="s">
         <v>16</v>
@@ -2973,7 +3012,7 @@
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
       <c r="I94" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K94" s="4" t="s">
         <v>16</v>
@@ -2982,34 +3021,20 @@
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" s="33"/>
-      <c r="B95" s="2">
-        <v>3</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E95" s="2">
-        <v>1</v>
-      </c>
-      <c r="F95" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="G95" s="2">
-        <v>4</v>
-      </c>
-      <c r="H95" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="B95" s="2"/>
+      <c r="C95" s="2"/>
+      <c r="D95" s="2"/>
+      <c r="E95" s="2"/>
+      <c r="F95" s="2"/>
+      <c r="G95" s="2"/>
+      <c r="H95" s="2"/>
       <c r="I95" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="K95" s="27"/>
-      <c r="L95" s="7" t="s">
-        <v>16</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="K95" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L95" s="25"/>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" s="33"/>
@@ -3021,29 +3046,33 @@
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
       <c r="I96" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="K96" s="27"/>
-      <c r="L96" s="7" t="s">
-        <v>16</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="K96" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L96" s="25"/>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" s="33"/>
-      <c r="B97" s="2"/>
-      <c r="C97" s="2"/>
+      <c r="B97" s="2">
+        <v>4</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>69</v>
+      </c>
       <c r="D97" s="2"/>
       <c r="E97" s="2"/>
       <c r="F97" s="2"/>
       <c r="G97" s="2"/>
       <c r="H97" s="2"/>
       <c r="I97" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="K97" s="27"/>
-      <c r="L97" s="7" t="s">
-        <v>16</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="K97" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L97" s="25"/>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" s="33"/>
@@ -3055,20 +3084,20 @@
       <c r="G98" s="2"/>
       <c r="H98" s="2"/>
       <c r="I98" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="K98" s="27"/>
-      <c r="L98" s="7" t="s">
-        <v>16</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="K98" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L98" s="25"/>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" s="33"/>
       <c r="B99" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>125</v>
+        <v>89</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>12</v>
@@ -3086,7 +3115,7 @@
         <v>14</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="K99" s="27"/>
       <c r="L99" s="7" t="s">
@@ -3103,7 +3132,7 @@
       <c r="G100" s="2"/>
       <c r="H100" s="2"/>
       <c r="I100" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="K100" s="27"/>
       <c r="L100" s="7" t="s">
@@ -3120,7 +3149,7 @@
       <c r="G101" s="2"/>
       <c r="H101" s="2"/>
       <c r="I101" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="K101" s="27"/>
       <c r="L101" s="7" t="s">
@@ -3128,34 +3157,116 @@
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A102" s="34"/>
-      <c r="B102" s="14"/>
-      <c r="C102" s="14"/>
-      <c r="D102" s="14"/>
-      <c r="E102" s="14"/>
-      <c r="F102" s="14"/>
-      <c r="G102" s="14"/>
-      <c r="H102" s="14"/>
-      <c r="I102" s="14" t="s">
+      <c r="A102" s="33"/>
+      <c r="B102" s="2"/>
+      <c r="C102" s="2"/>
+      <c r="D102" s="2"/>
+      <c r="E102" s="2"/>
+      <c r="F102" s="2"/>
+      <c r="G102" s="2"/>
+      <c r="H102" s="2"/>
+      <c r="I102" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="K102" s="27"/>
+      <c r="L102" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A103" s="33"/>
+      <c r="B103" s="2">
+        <v>6</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E103" s="2">
+        <v>1</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="G103" s="2">
+        <v>4</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I103" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="K103" s="27"/>
+      <c r="L103" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A104" s="33"/>
+      <c r="B104" s="2"/>
+      <c r="C104" s="2"/>
+      <c r="D104" s="2"/>
+      <c r="E104" s="2"/>
+      <c r="F104" s="2"/>
+      <c r="G104" s="2"/>
+      <c r="H104" s="2"/>
+      <c r="I104" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="K104" s="27"/>
+      <c r="L104" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A105" s="33"/>
+      <c r="B105" s="2"/>
+      <c r="C105" s="2"/>
+      <c r="D105" s="2"/>
+      <c r="E105" s="2"/>
+      <c r="F105" s="2"/>
+      <c r="G105" s="2"/>
+      <c r="H105" s="2"/>
+      <c r="I105" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="K105" s="27"/>
+      <c r="L105" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A106" s="34"/>
+      <c r="B106" s="14"/>
+      <c r="C106" s="14"/>
+      <c r="D106" s="14"/>
+      <c r="E106" s="14"/>
+      <c r="F106" s="14"/>
+      <c r="G106" s="14"/>
+      <c r="H106" s="14"/>
+      <c r="I106" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="J102" s="13"/>
-      <c r="K102" s="30"/>
-      <c r="L102" s="29" t="s">
+      <c r="J106" s="13"/>
+      <c r="K106" s="30"/>
+      <c r="L106" s="29" t="s">
         <v>16</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A75:A102"/>
-    <mergeCell ref="A36:A41"/>
-    <mergeCell ref="A42:A66"/>
-    <mergeCell ref="A67:A74"/>
+    <mergeCell ref="A79:A106"/>
+    <mergeCell ref="A40:A45"/>
+    <mergeCell ref="A46:A70"/>
+    <mergeCell ref="A71:A78"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A4:A21"/>
     <mergeCell ref="A24:A27"/>
-    <mergeCell ref="A28:A35"/>
+    <mergeCell ref="A28:A39"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3163,12 +3274,11 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="d7b47298-7dbc-4c4a-b955-e35738c83845" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3405,17 +3515,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="d7b47298-7dbc-4c4a-b955-e35738c83845" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0006E415-A18B-4726-A1A0-54EC3A4B0653}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE34F84B-F271-4B1B-8B21-90DAF7F40D50}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="4c7a27d0-c111-49d1-947f-3e415c425751"/>
+    <ds:schemaRef ds:uri="d7b47298-7dbc-4c4a-b955-e35738c83845"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3440,18 +3560,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE34F84B-F271-4B1B-8B21-90DAF7F40D50}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0006E415-A18B-4726-A1A0-54EC3A4B0653}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="4c7a27d0-c111-49d1-947f-3e415c425751"/>
-    <ds:schemaRef ds:uri="d7b47298-7dbc-4c4a-b955-e35738c83845"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Greyform/Python_Application/PinAllocationBOMforPBU_T1am.xlsx
+++ b/Greyform/Python_Application/PinAllocationBOMforPBU_T1am.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MokZhiZhuan\OneDrive - WINSYS TECHNOLOGY PTE LTD\Documents\GitHub\GreyForm_UI\Greyform\Python_Application\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5755E839-B70A-4D09-81A5-7C939583A930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA6426C9-9275-4C56-9E4D-0ABEA90BC70C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="23235" windowHeight="15465" xr2:uid="{10577398-EA94-4D34-AF72-AAEF7879495C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{10577398-EA94-4D34-AF72-AAEF7879495C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="135">
   <si>
     <t>Wall</t>
   </si>
@@ -50,9 +50,6 @@
     <t>Type</t>
   </si>
   <si>
-    <t>Penetrations</t>
-  </si>
-  <si>
     <t>Shape</t>
   </si>
   <si>
@@ -104,48 +101,9 @@
     <t>Basic Wall:BSS.20mm Wall Finishes</t>
   </si>
   <si>
-    <t>None</t>
-  </si>
-  <si>
     <t>TMP</t>
   </si>
   <si>
-    <t>TMP1S2b1</t>
-  </si>
-  <si>
-    <t>TMP1S2b2</t>
-  </si>
-  <si>
-    <t>TMP1S2b3</t>
-  </si>
-  <si>
-    <t>TMP1S2b4</t>
-  </si>
-  <si>
-    <t>TMP1S2a1</t>
-  </si>
-  <si>
-    <t>TMP1S2a2</t>
-  </si>
-  <si>
-    <t>TMP1S2a3</t>
-  </si>
-  <si>
-    <t>TMP1S2a4</t>
-  </si>
-  <si>
-    <t>TMP1S2c1</t>
-  </si>
-  <si>
-    <t>TMP1S2c2</t>
-  </si>
-  <si>
-    <t>TMP1S2c3</t>
-  </si>
-  <si>
-    <t>TMP1S2c4</t>
-  </si>
-  <si>
     <t>Wall 2</t>
   </si>
   <si>
@@ -416,9 +374,6 @@
     <t>BSS.FLOOR DRAIN_100</t>
   </si>
   <si>
-    <t>Square</t>
-  </si>
-  <si>
     <t>LP7S3a1</t>
   </si>
   <si>
@@ -480,6 +435,12 @@
   </si>
   <si>
     <t>LP3S3b4</t>
+  </si>
+  <si>
+    <t>Wall 1</t>
+  </si>
+  <si>
+    <t>Point</t>
   </si>
 </sst>
 </file>
@@ -540,7 +501,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -711,12 +672,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -744,8 +716,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -756,9 +726,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -828,6 +795,16 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1167,52 +1144,50 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45C9410D-7727-4F15-9679-20A483A9E846}">
-  <dimension ref="A1:L106"/>
+  <dimension ref="A1:Z106"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="42.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="38"/>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="38"/>
-      <c r="L1" s="38"/>
-    </row>
-    <row r="2" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="39" t="s">
-        <v>70</v>
-      </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="41"/>
-    </row>
-    <row r="3" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A1" s="35"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+    </row>
+    <row r="2" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="36" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
+      <c r="J2" s="37"/>
+      <c r="K2" s="38"/>
+    </row>
+    <row r="3" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
@@ -1243,2017 +1218,1999 @@
       <c r="J3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="L3" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="36"/>
+      <c r="T3" s="42"/>
+      <c r="U3" s="42"/>
+      <c r="V3" s="42"/>
+      <c r="W3" s="42"/>
+      <c r="X3" s="42"/>
+      <c r="Y3" s="42"/>
+      <c r="Z3" s="42"/>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A4" s="39" t="s">
+        <v>133</v>
+      </c>
       <c r="B4" s="2">
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" s="2">
+        <v>11</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="2">
         <v>4</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="I4" s="8"/>
       <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="36"/>
+      <c r="K4" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="T4" s="43"/>
+      <c r="U4" s="40"/>
+      <c r="V4" s="40"/>
+      <c r="W4" s="40"/>
+      <c r="X4" s="41"/>
+      <c r="Y4" s="43"/>
+      <c r="Z4" s="43"/>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A5" s="33"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="H5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="8"/>
       <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="36"/>
+      <c r="K5" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="T5" s="43"/>
+      <c r="U5" s="41"/>
+      <c r="V5" s="41"/>
+      <c r="W5" s="41"/>
+      <c r="X5" s="41"/>
+      <c r="Y5" s="41"/>
+      <c r="Z5" s="43"/>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A6" s="33"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="2" t="s">
-        <v>18</v>
-      </c>
+      <c r="H6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" s="8"/>
       <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="36"/>
+      <c r="K6" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="T6" s="43"/>
+      <c r="U6" s="41"/>
+      <c r="V6" s="41"/>
+      <c r="W6" s="41"/>
+      <c r="X6" s="41"/>
+      <c r="Y6" s="41"/>
+      <c r="Z6" s="43"/>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A7" s="33"/>
       <c r="B7" s="2"/>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="2" t="s">
-        <v>19</v>
-      </c>
+      <c r="H7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I7" s="8"/>
       <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="36"/>
+      <c r="K7" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="T7" s="43"/>
+      <c r="U7" s="41"/>
+      <c r="V7" s="41"/>
+      <c r="W7" s="41"/>
+      <c r="X7" s="41"/>
+      <c r="Y7" s="41"/>
+      <c r="Z7" s="43"/>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A8" s="33"/>
       <c r="B8" s="2">
         <v>2</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="2">
+        <v>34</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F8" s="2">
         <v>8</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J8" s="8"/>
-      <c r="K8" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L8" s="9"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="36"/>
+      <c r="G8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" s="2" t="str">
+        <f>T7 &amp; MID(A4,6,LEN(A4)-5) &amp; IF(OR(D8="Pipe", I4="ü", I4=TRUE), "S1", IF(OR(D8="Tiles", J4="ü",  J4=TRUE), "S2", IF(OR(D8="Fitting", K4="ü", K4=TRUE), "S3", ""))) &amp; CHAR(96 + INT((ROW()-2)/4)) &amp; MOD(ROW()-2,4)-1</f>
+        <v>1S2a1</v>
+      </c>
+      <c r="I8" s="8"/>
+      <c r="J8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K8" s="9"/>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A9" s="33"/>
       <c r="B9" s="2"/>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="J9" s="8"/>
-      <c r="K9" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L9" s="9"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="36"/>
+      <c r="H9" s="2" t="str">
+        <f>T7 &amp; MID(A4,6,LEN(A4)-5) &amp; IF(OR(I4="✓", I4="ü", I4=TRUE), "S1", IF(OR(J4="✓", J4="ü",  J4=TRUE), "S2", IF(OR(K4="✓", K4="ü", K4=TRUE), "S3", ""))) &amp; CHAR(96 + INT((ROW()-2)/4)) &amp; MOD(ROW()-2,4)-1</f>
+        <v>1S3a2</v>
+      </c>
+      <c r="I9" s="8"/>
+      <c r="J9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K9" s="9"/>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A10" s="33"/>
       <c r="B10" s="2"/>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="J10" s="8"/>
-      <c r="K10" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L10" s="9"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="36"/>
+      <c r="H10" s="2" t="str">
+        <f>T7 &amp; MID(A4,6,LEN(A4)-5) &amp; IF(OR(I4="✓", I4="ü", I4=TRUE), "S1", IF(OR(J4="✓", J4="ü",  J4=TRUE), "S2", IF(OR(K4="✓", K4="ü", K4=TRUE), "S3", ""))) &amp; CHAR(96 + INT((ROW()-2)/4)-1) &amp; MOD(ROW()-2,4)+3</f>
+        <v>1S3a3</v>
+      </c>
+      <c r="I10" s="8"/>
+      <c r="J10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K10" s="9"/>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A11" s="33"/>
       <c r="B11" s="2"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="J11" s="8"/>
-      <c r="K11" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L11" s="9"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="36"/>
+      <c r="H11" s="2" t="str">
+        <f>T7 &amp; MID(A4,6,LEN(A4)-5) &amp; IF(OR(I4="✓", I4="ü", I4=TRUE), "S1", IF(OR(J4="✓", J4="ü",  J4=TRUE), "S2", IF(OR(K4="✓", K4="ü", K4=TRUE), "S3", ""))) &amp; CHAR(96 + INT((ROW()-2)/4)-1) &amp; MOD(ROW()-2,4)+3</f>
+        <v>1S3a4</v>
+      </c>
+      <c r="I11" s="8"/>
+      <c r="J11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K11" s="9"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A12" s="33"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F12" s="3"/>
+      <c r="G12" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J12" s="8"/>
-      <c r="K12" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L12" s="9"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="36"/>
+      <c r="H12" s="2" t="str">
+        <f>T7 &amp; MID(A4,6,LEN(A4)-5) &amp; IF(OR(D8="Pipe", I4="ü", I4=TRUE), "S1", IF(OR(D8="Tiles", J4="ü",  J4=TRUE), "S2", IF(OR(D8="Fitting", K4="ü", K4=TRUE), "S3", ""))) &amp; CHAR(96 + INT((ROW()-2)/4)) &amp; MOD(ROW()-2,4)-1</f>
+        <v>1S2b1</v>
+      </c>
+      <c r="I12" s="8"/>
+      <c r="J12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K12" s="9"/>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A13" s="33"/>
       <c r="B13" s="2"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="J13" s="8"/>
-      <c r="K13" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L13" s="9"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="36"/>
+      <c r="H13" s="2" t="str">
+        <f>T7 &amp; MID(A4,6,LEN(A4)-5) &amp; IF(OR(D8="Pipe", I4="ü", I4=TRUE), "S1", IF(OR(D8="Tiles", J4="ü",  J4=TRUE), "S2", IF(OR(D8="Fitting", K4="ü", K4=TRUE), "S3", ""))) &amp; CHAR(96 + INT((ROW()-2)/4)) &amp; MOD(ROW()-2,4)-1</f>
+        <v>1S2b2</v>
+      </c>
+      <c r="I13" s="8"/>
+      <c r="J13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K13" s="9"/>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A14" s="33"/>
       <c r="B14" s="2"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="J14" s="8"/>
-      <c r="K14" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L14" s="9"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="36"/>
+      <c r="H14" s="2" t="str">
+        <f>T7 &amp; MID(A4,6,LEN(A4)-5) &amp; IF(OR(I4="✓", I4="ü", I4=TRUE), "S1", IF(OR(J4="✓", J4="ü",  J4=TRUE), "S2", IF(OR(K4="✓", K4="ü", K4=TRUE), "S3", ""))) &amp; CHAR(96 + INT((ROW()-2)/4)-1) &amp; MOD(ROW()-2,4)+3</f>
+        <v>1S3b3</v>
+      </c>
+      <c r="I14" s="8"/>
+      <c r="J14" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K14" s="9"/>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A15" s="33"/>
       <c r="B15" s="2"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J15" s="8"/>
-      <c r="K15" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L15" s="9"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="36"/>
+      <c r="H15" s="2" t="str">
+        <f>T7 &amp; MID(A4,6,LEN(A4)-5) &amp; IF(OR(I4="✓", I4="ü", I4=TRUE), "S1", IF(OR(J4="✓", J4="ü",  J4=TRUE), "S2", IF(OR(K4="✓", K4="ü", K4=TRUE), "S3", ""))) &amp; CHAR(96 + INT((ROW()-2)/4)-1) &amp; MOD(ROW()-2,4)+3</f>
+        <v>1S3b4</v>
+      </c>
+      <c r="I15" s="8"/>
+      <c r="J15" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K15" s="9"/>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A16" s="33"/>
       <c r="B16" s="2">
         <v>3</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F16" s="2">
+        <v>8</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G16" s="2">
-        <v>16</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="J16" s="8"/>
-      <c r="K16" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L16" s="9"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="36"/>
+      <c r="H16" s="2" t="str">
+        <f>T7 &amp; MID(A4,6,LEN(A4)-5) &amp; IF(OR(D8="Pipe", I4="ü", I4=TRUE), "S1", IF(OR(D8="Tiles", J4="ü",  J4=TRUE), "S2", IF(OR(D8="Fitting", K4="ü", K4=TRUE), "S3", ""))) &amp; CHAR(96 + INT((ROW()-2)/4)) &amp; MOD(ROW()-2,4)-1</f>
+        <v>1S2c1</v>
+      </c>
+      <c r="I16" s="8"/>
+      <c r="J16" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K16" s="9"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="33"/>
       <c r="B17" s="2"/>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="J17" s="8"/>
-      <c r="K17" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L17" s="9"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="36"/>
+      <c r="H17" s="2" t="str">
+        <f>T7 &amp; MID(A4,6,LEN(A4)-5) &amp; IF(OR(D8="Pipe", I4="ü", I4=TRUE), "S1", IF(OR(D8="Tiles", J4="ü",  J4=TRUE), "S2", IF(OR(D8="Fitting", K4="ü", K4=TRUE), "S3", ""))) &amp; CHAR(96 + INT((ROW()-2)/4)) &amp; MOD(ROW()-2,4)-1</f>
+        <v>1S2c2</v>
+      </c>
+      <c r="I17" s="8"/>
+      <c r="J17" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K17" s="9"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="33"/>
       <c r="B18" s="2"/>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J18" s="8"/>
-      <c r="K18" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L18" s="9"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="36"/>
+      <c r="H18" s="2" t="str">
+        <f>T7 &amp; MID(A4,6,LEN(A4)-5) &amp; IF(OR(I4="✓", I4="ü", I4=TRUE), "S1", IF(OR(J4="✓", J4="ü",  J4=TRUE), "S2", IF(OR(K4="✓", K4="ü", K4=TRUE), "S3", ""))) &amp; CHAR(96 + INT((ROW()-2)/4)-1) &amp; MOD(ROW()-2,4)+3</f>
+        <v>1S3c3</v>
+      </c>
+      <c r="I18" s="8"/>
+      <c r="J18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K18" s="9"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="33"/>
       <c r="B19" s="2"/>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J19" s="8"/>
-      <c r="K19" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L19" s="9"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="36"/>
+      <c r="H19" s="2" t="str">
+        <f>T7 &amp; MID(A4,6,LEN(A4)-5) &amp; IF(OR(I4="✓", I4="ü", I4=TRUE), "S1", IF(OR(J4="✓", J4="ü",  J4=TRUE), "S2", IF(OR(K4="✓", K4="ü", K4=TRUE), "S3", ""))) &amp; CHAR(96 + INT((ROW()-2)/4)-1) &amp; MOD(ROW()-2,4)+3</f>
+        <v>1S3c4</v>
+      </c>
+      <c r="I19" s="8"/>
+      <c r="J19" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K19" s="9"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="33"/>
       <c r="B20" s="2">
         <v>4</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E20" s="3"/>
+        <v>34</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>134</v>
+      </c>
       <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
+      <c r="G20" s="2" t="s">
+        <v>21</v>
+      </c>
       <c r="H20" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="J20" s="8"/>
-      <c r="K20" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L20" s="9"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="36"/>
+        <v>76</v>
+      </c>
+      <c r="I20" s="8"/>
+      <c r="J20" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K20" s="9"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="33"/>
       <c r="B21" s="2"/>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="J21" s="8"/>
-      <c r="K21" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L21" s="9"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="11"/>
+      <c r="H21" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I21" s="8"/>
+      <c r="J21" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K21" s="9"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="33"/>
       <c r="B22" s="2"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="J22" s="8"/>
-      <c r="K22" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L22" s="9"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="12"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="J23" s="21"/>
-      <c r="K23" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="L23" s="10"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="35" t="s">
-        <v>36</v>
+      <c r="H22" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I22" s="8"/>
+      <c r="J22" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K22" s="9"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="34"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="I23" s="18"/>
+      <c r="J23" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="K23" s="10"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="32" t="s">
+        <v>22</v>
       </c>
       <c r="B24" s="2">
         <v>1</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F24" s="2">
+        <v>4</v>
+      </c>
+      <c r="G24" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E24" s="3"/>
-      <c r="F24" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G24" s="2">
-        <v>8</v>
-      </c>
       <c r="H24" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="K24" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L24" s="24"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="36"/>
+        <v>25</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K24" s="21"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="33"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="K25" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L25" s="24"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="36"/>
+      <c r="H25" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K25" s="21"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="33"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="K26" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L26" s="24"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="37"/>
+      <c r="H26" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K26" s="21"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="34"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K27" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L27" s="24"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="36" t="s">
-        <v>41</v>
-      </c>
-      <c r="B28" s="16">
+      <c r="H27" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K27" s="21"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="14">
         <v>1</v>
       </c>
-      <c r="C28" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="D28" s="16" t="s">
+      <c r="C28" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16" t="s">
+      <c r="F28" s="14">
+        <v>4</v>
+      </c>
+      <c r="G28" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="G28" s="16">
-        <v>4</v>
-      </c>
-      <c r="H28" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="I28" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="J28" s="23"/>
-      <c r="K28" s="23"/>
-      <c r="L28" s="26" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="36"/>
+      <c r="H28" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="I28" s="20"/>
+      <c r="J28" s="20"/>
+      <c r="K28" s="23" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="33"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J29" s="27"/>
-      <c r="K29" s="27"/>
-      <c r="L29" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="36"/>
+      <c r="H29" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I29" s="24"/>
+      <c r="J29" s="24"/>
+      <c r="K29" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="33"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J30" s="27"/>
-      <c r="K30" s="27"/>
-      <c r="L30" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="36"/>
+      <c r="H30" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I30" s="24"/>
+      <c r="J30" s="24"/>
+      <c r="K30" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="33"/>
       <c r="B31" s="2"/>
-      <c r="D31" s="42"/>
+      <c r="D31" s="2"/>
       <c r="E31" s="2"/>
-      <c r="F31" s="42"/>
+      <c r="F31" s="2"/>
       <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="J31" s="27"/>
-      <c r="K31" s="27"/>
-      <c r="L31" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="36"/>
+      <c r="H31" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I31" s="24"/>
+      <c r="J31" s="24"/>
+      <c r="K31" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="33"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D32" s="42" t="s">
+        <v>128</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E32" s="2"/>
-      <c r="F32" s="42" t="s">
+      <c r="F32" s="2">
+        <v>4</v>
+      </c>
+      <c r="G32" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G32" s="2">
-        <v>4</v>
-      </c>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="J32" s="27"/>
-      <c r="K32" s="27"/>
-      <c r="L32" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="36"/>
+      <c r="H32" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="I32" s="24"/>
+      <c r="J32" s="24"/>
+      <c r="K32" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="33"/>
       <c r="B33" s="2"/>
-      <c r="D33" s="42"/>
+      <c r="D33" s="2"/>
       <c r="E33" s="2"/>
-      <c r="F33" s="42"/>
+      <c r="F33" s="2"/>
       <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="J33" s="27"/>
-      <c r="K33" s="27"/>
-      <c r="L33" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="36"/>
+      <c r="H33" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="I33" s="24"/>
+      <c r="J33" s="24"/>
+      <c r="K33" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" s="33"/>
       <c r="B34" s="2"/>
-      <c r="D34" s="42"/>
+      <c r="D34" s="2"/>
       <c r="E34" s="2"/>
-      <c r="F34" s="42"/>
+      <c r="F34" s="2"/>
       <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="J34" s="27"/>
-      <c r="K34" s="27"/>
-      <c r="L34" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="36"/>
+      <c r="H34" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="I34" s="24"/>
+      <c r="J34" s="24"/>
+      <c r="K34" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35" s="33"/>
       <c r="B35" s="2"/>
-      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
       <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="J35" s="27"/>
-      <c r="K35" s="27"/>
-      <c r="L35" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="36"/>
+      <c r="H35" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="I35" s="24"/>
+      <c r="J35" s="24"/>
+      <c r="K35" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" s="33"/>
       <c r="B36" s="2">
         <v>2</v>
       </c>
       <c r="C36" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F36" s="2">
+        <v>4</v>
+      </c>
+      <c r="G36" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D36" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E36" s="3"/>
-      <c r="F36" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G36" s="2">
-        <v>8</v>
-      </c>
       <c r="H36" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="K36" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L36" s="25"/>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A37" s="36"/>
+        <v>35</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K36" s="22"/>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37" s="33"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="K37" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L37" s="25"/>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38" s="36"/>
+      <c r="H37" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K37" s="22"/>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38" s="33"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="K38" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L38" s="25"/>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39" s="36"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="J39" s="13"/>
-      <c r="K39" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="L39" s="31"/>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A40" s="35" t="s">
-        <v>53</v>
+      <c r="H38" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="J38" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K38" s="22"/>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39" s="33"/>
+      <c r="B39" s="12"/>
+      <c r="C39" s="12"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="12"/>
+      <c r="G39" s="12"/>
+      <c r="H39" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="I39" s="11"/>
+      <c r="J39" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="K39" s="28"/>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" s="32" t="s">
+        <v>39</v>
       </c>
       <c r="B40" s="2">
         <v>1</v>
       </c>
       <c r="C40" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F40" s="2">
+        <v>4</v>
+      </c>
+      <c r="G40" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D40" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E40" s="3"/>
-      <c r="F40" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G40" s="2">
-        <v>5</v>
-      </c>
       <c r="H40" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I40" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="J40" s="27"/>
-      <c r="K40" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L40" s="9"/>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A41" s="36"/>
+        <v>40</v>
+      </c>
+      <c r="I40" s="24"/>
+      <c r="J40" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K40" s="9"/>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" s="33"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="J41" s="27"/>
-      <c r="K41" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L41" s="9"/>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A42" s="36"/>
+      <c r="H41" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I41" s="24"/>
+      <c r="J41" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K41" s="9"/>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" s="33"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
-      <c r="H42" s="2"/>
-      <c r="I42" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="J42" s="27"/>
-      <c r="K42" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L42" s="9"/>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A43" s="36"/>
+      <c r="H42" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I42" s="24"/>
+      <c r="J42" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K42" s="9"/>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43" s="33"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="J43" s="27"/>
-      <c r="K43" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L43" s="9"/>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A44" s="36"/>
-      <c r="B44" s="28">
+      <c r="H43" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I43" s="24"/>
+      <c r="J43" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K43" s="9"/>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A44" s="33"/>
+      <c r="B44" s="25">
         <v>2</v>
       </c>
-      <c r="C44" s="28" t="s">
-        <v>138</v>
-      </c>
-      <c r="I44" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="L44" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A45" s="37"/>
-      <c r="B45" s="13"/>
-      <c r="C45" s="13"/>
-      <c r="D45" s="13"/>
-      <c r="E45" s="13"/>
-      <c r="F45" s="13"/>
-      <c r="G45" s="13"/>
-      <c r="H45" s="13"/>
-      <c r="I45" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="J45" s="13"/>
-      <c r="K45" s="13"/>
-      <c r="L45" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A46" s="35" t="s">
-        <v>58</v>
+      <c r="C44" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E44" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="F44" s="25">
+        <v>2</v>
+      </c>
+      <c r="G44" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="K44" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45" s="34"/>
+      <c r="B45" s="11"/>
+      <c r="C45" s="11"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="11"/>
+      <c r="F45" s="11"/>
+      <c r="G45" s="11"/>
+      <c r="H45" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="I45" s="11"/>
+      <c r="J45" s="11"/>
+      <c r="K45" s="26" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A46" s="32" t="s">
+        <v>44</v>
       </c>
       <c r="B46" s="2">
         <v>1</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E46" s="3"/>
-      <c r="F46" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G46" s="2">
-        <v>4</v>
+        <v>33</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F46" s="2">
+        <v>7</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I46" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="K46" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L46" s="25"/>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A47" s="36"/>
+        <v>46</v>
+      </c>
+      <c r="J46" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K46" s="22"/>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A47" s="33"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
-      <c r="H47" s="2"/>
-      <c r="I47" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="K47" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L47" s="25"/>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A48" s="36"/>
+      <c r="H47" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="J47" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K47" s="22"/>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A48" s="33"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="K48" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L48" s="25"/>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A49" s="36"/>
+      <c r="H48" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="J48" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K48" s="22"/>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49" s="33"/>
       <c r="B49" s="2">
         <v>2</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
+        <v>45</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>134</v>
+      </c>
       <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="K49" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L49" s="25"/>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A50" s="36"/>
+      <c r="G49" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="J49" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K49" s="22"/>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50" s="33"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
-      <c r="I50" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="K50" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L50" s="25"/>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A51" s="36"/>
+      <c r="H50" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="J50" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K50" s="22"/>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51" s="33"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
       <c r="D51" s="2"/>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="K51" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L51" s="25"/>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A52" s="36"/>
+      <c r="H51" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="J51" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K51" s="22"/>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52" s="33"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
       <c r="E52" s="2"/>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
-      <c r="H52" s="2"/>
-      <c r="I52" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="K52" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L52" s="25"/>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A53" s="36"/>
+      <c r="H52" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="J52" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K52" s="22"/>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A53" s="33"/>
       <c r="B53" s="2">
         <v>3</v>
       </c>
-      <c r="C53" s="28" t="s">
-        <v>105</v>
+      <c r="C53" s="25" t="s">
+        <v>91</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E53" s="2"/>
-      <c r="F53" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G53" s="2"/>
-      <c r="H53" s="2"/>
-      <c r="I53" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="L53" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A54" s="36"/>
+        <v>11</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F53" s="2">
+        <v>5</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="K53" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A54" s="33"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
-      <c r="H54" s="2"/>
-      <c r="I54" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="L54" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A55" s="36"/>
+      <c r="H54" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="K54" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A55" s="33"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
-      <c r="H55" s="2"/>
-      <c r="I55" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="L55" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A56" s="36"/>
+      <c r="H55" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K55" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A56" s="33"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
       <c r="D56" s="2"/>
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
-      <c r="H56" s="2"/>
-      <c r="I56" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="L56" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A57" s="36"/>
+      <c r="H56" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="K56" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A57" s="33"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
-      <c r="H57" s="2"/>
-      <c r="I57" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="L57" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A58" s="36"/>
+      <c r="H57" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="K57" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A58" s="33"/>
       <c r="B58" s="2">
         <v>4</v>
       </c>
-      <c r="C58" s="28" t="s">
-        <v>88</v>
+      <c r="C58" s="25" t="s">
+        <v>74</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E58" s="2"/>
-      <c r="F58" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G58" s="2"/>
-      <c r="H58" s="2"/>
-      <c r="I58" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="L58" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A59" s="36"/>
+        <v>11</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F58" s="2">
+        <v>5</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K58" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A59" s="33"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
       <c r="D59" s="2"/>
       <c r="E59" s="2"/>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
-      <c r="H59" s="2"/>
-      <c r="I59" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="L59" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A60" s="36"/>
+      <c r="H59" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="K59" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A60" s="33"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
       <c r="D60" s="2"/>
       <c r="E60" s="2"/>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
-      <c r="H60" s="2"/>
-      <c r="I60" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="L60" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A61" s="36"/>
+      <c r="H60" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="K60" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A61" s="33"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
       <c r="D61" s="2"/>
       <c r="E61" s="2"/>
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
-      <c r="H61" s="2"/>
-      <c r="I61" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="L61" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A62" s="36"/>
+      <c r="H61" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="K61" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A62" s="33"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
       <c r="D62" s="2"/>
       <c r="E62" s="2"/>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
-      <c r="H62" s="2"/>
-      <c r="I62" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="L62" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A63" s="36"/>
+      <c r="H62" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="K62" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A63" s="33"/>
       <c r="B63" s="2">
         <v>5</v>
       </c>
-      <c r="C63" s="28" t="s">
-        <v>112</v>
+      <c r="C63" s="25" t="s">
+        <v>98</v>
       </c>
       <c r="D63" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E63" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E63" s="2"/>
-      <c r="F63" s="2" t="s">
+      <c r="F63" s="2">
+        <v>4</v>
+      </c>
+      <c r="G63" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G63" s="2"/>
-      <c r="H63" s="2"/>
-      <c r="I63" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="L63" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A64" s="36"/>
+      <c r="H63" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="K63" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A64" s="33"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
       <c r="D64" s="2"/>
       <c r="E64" s="2"/>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
-      <c r="H64" s="2"/>
-      <c r="I64" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="L64" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A65" s="36"/>
+      <c r="H64" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="K64" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A65" s="33"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
       <c r="D65" s="2"/>
       <c r="E65" s="2"/>
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
-      <c r="H65" s="2"/>
-      <c r="I65" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="L65" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A66" s="36"/>
+      <c r="H65" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="K65" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A66" s="33"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
       <c r="D66" s="2"/>
       <c r="E66" s="2"/>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
-      <c r="H66" s="2"/>
-      <c r="I66" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="L66" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A67" s="36"/>
+      <c r="H66" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="K66" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A67" s="33"/>
       <c r="B67" s="2">
         <v>6</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="D67" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E67" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E67" s="2"/>
-      <c r="F67" s="2" t="s">
+      <c r="F67" s="2">
+        <v>4</v>
+      </c>
+      <c r="G67" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G67" s="2"/>
-      <c r="H67" s="2"/>
-      <c r="I67" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="L67" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A68" s="36"/>
+      <c r="H67" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="K67" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A68" s="33"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
       <c r="D68" s="2"/>
       <c r="E68" s="2"/>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
-      <c r="H68" s="2"/>
-      <c r="I68" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="L68" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A69" s="36"/>
+      <c r="H68" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="K68" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A69" s="33"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
       <c r="D69" s="2"/>
       <c r="E69" s="2"/>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
-      <c r="H69" s="2"/>
-      <c r="I69" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="L69" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A70" s="37"/>
-      <c r="B70" s="13"/>
-      <c r="D70" s="13"/>
-      <c r="E70" s="13"/>
-      <c r="F70" s="13"/>
-      <c r="G70" s="13"/>
-      <c r="H70" s="13"/>
-      <c r="I70" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="J70" s="13"/>
-      <c r="L70" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A71" s="35" t="s">
-        <v>63</v>
-      </c>
-      <c r="B71" s="16">
+      <c r="H69" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="K69" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A70" s="34"/>
+      <c r="B70" s="11"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="11"/>
+      <c r="F70" s="11"/>
+      <c r="G70" s="11"/>
+      <c r="H70" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="I70" s="11"/>
+      <c r="K70" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A71" s="32" t="s">
+        <v>49</v>
+      </c>
+      <c r="B71" s="14">
         <v>1</v>
       </c>
-      <c r="C71" s="16" t="s">
+      <c r="C71" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E71" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="F71" s="14">
+        <v>8</v>
+      </c>
+      <c r="G71" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="D71" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="E71" s="17"/>
-      <c r="F71" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="G71" s="16">
-        <v>8</v>
-      </c>
-      <c r="H71" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="I71" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="J71" s="18"/>
-      <c r="K71" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="L71" s="22"/>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A72" s="36"/>
+      <c r="H71" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="I71" s="15"/>
+      <c r="J71" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="K71" s="19"/>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A72" s="33"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
       <c r="D72" s="2"/>
-      <c r="E72" s="3"/>
-      <c r="F72" s="2"/>
-      <c r="G72" s="3"/>
-      <c r="H72" s="2"/>
-      <c r="I72" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="J72" s="8"/>
-      <c r="K72" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L72" s="9"/>
-    </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A73" s="36"/>
+      <c r="E72" s="2"/>
+      <c r="F72" s="3"/>
+      <c r="G72" s="2"/>
+      <c r="H72" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="I72" s="8"/>
+      <c r="J72" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K72" s="9"/>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A73" s="33"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
       <c r="D73" s="2"/>
-      <c r="E73" s="3"/>
-      <c r="F73" s="2"/>
-      <c r="G73" s="3"/>
-      <c r="H73" s="2"/>
-      <c r="I73" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J73" s="8"/>
-      <c r="K73" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L73" s="9"/>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A74" s="36"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="3"/>
+      <c r="G73" s="2"/>
+      <c r="H73" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="I73" s="8"/>
+      <c r="J73" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K73" s="9"/>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A74" s="33"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
       <c r="D74" s="2"/>
-      <c r="E74" s="3"/>
-      <c r="F74" s="2"/>
-      <c r="G74" s="3"/>
-      <c r="H74" s="2"/>
-      <c r="I74" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="J74" s="8"/>
-      <c r="K74" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L74" s="9"/>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A75" s="36"/>
+      <c r="E74" s="2"/>
+      <c r="F74" s="3"/>
+      <c r="G74" s="2"/>
+      <c r="H74" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I74" s="8"/>
+      <c r="J74" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K74" s="9"/>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A75" s="33"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
       <c r="D75" s="2"/>
-      <c r="E75" s="3"/>
-      <c r="F75" s="2"/>
-      <c r="G75" s="3"/>
-      <c r="H75" s="2"/>
-      <c r="I75" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="J75" s="8"/>
-      <c r="K75" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L75" s="9"/>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A76" s="36"/>
+      <c r="E75" s="2"/>
+      <c r="F75" s="3"/>
+      <c r="G75" s="2"/>
+      <c r="H75" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I75" s="8"/>
+      <c r="J75" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K75" s="9"/>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A76" s="33"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
       <c r="D76" s="2"/>
-      <c r="E76" s="3"/>
-      <c r="F76" s="2"/>
-      <c r="G76" s="3"/>
-      <c r="H76" s="2"/>
-      <c r="I76" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="J76" s="8"/>
-      <c r="K76" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L76" s="9"/>
-    </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A77" s="36"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="3"/>
+      <c r="G76" s="2"/>
+      <c r="H76" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I76" s="8"/>
+      <c r="J76" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K76" s="9"/>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A77" s="33"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
       <c r="D77" s="2"/>
-      <c r="E77" s="3"/>
-      <c r="F77" s="2"/>
-      <c r="G77" s="3"/>
-      <c r="H77" s="2"/>
-      <c r="I77" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="J77" s="8"/>
-      <c r="K77" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L77" s="9"/>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A78" s="37"/>
-      <c r="B78" s="14"/>
-      <c r="C78" s="14"/>
-      <c r="D78" s="14"/>
-      <c r="E78" s="20"/>
-      <c r="F78" s="14"/>
-      <c r="G78" s="20"/>
-      <c r="H78" s="14"/>
-      <c r="I78" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="J78" s="21"/>
-      <c r="K78" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="L78" s="10"/>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A79" s="32" t="s">
-        <v>64</v>
+      <c r="E77" s="2"/>
+      <c r="F77" s="3"/>
+      <c r="G77" s="2"/>
+      <c r="H77" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I77" s="8"/>
+      <c r="J77" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K77" s="9"/>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A78" s="34"/>
+      <c r="B78" s="12"/>
+      <c r="C78" s="12"/>
+      <c r="D78" s="12"/>
+      <c r="E78" s="12"/>
+      <c r="F78" s="17"/>
+      <c r="G78" s="12"/>
+      <c r="H78" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="I78" s="18"/>
+      <c r="J78" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="K78" s="10"/>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A79" s="29" t="s">
+        <v>50</v>
       </c>
       <c r="B79" s="2">
         <v>1</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E79" s="3"/>
-      <c r="F79" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G79" s="2">
+        <v>33</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F79" s="2">
         <v>14</v>
       </c>
+      <c r="G79" s="2" t="s">
+        <v>21</v>
+      </c>
       <c r="H79" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I79" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="K79" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L79" s="25"/>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A80" s="33"/>
+        <v>57</v>
+      </c>
+      <c r="J79" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K79" s="22"/>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A80" s="30"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
       <c r="D80" s="2"/>
       <c r="E80" s="2"/>
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
-      <c r="H80" s="2"/>
-      <c r="I80" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="K80" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L80" s="25"/>
-    </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A81" s="33"/>
+      <c r="H80" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="J80" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K80" s="22"/>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A81" s="30"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
       <c r="D81" s="2"/>
       <c r="E81" s="2"/>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
-      <c r="H81" s="2"/>
-      <c r="I81" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="K81" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L81" s="25"/>
-    </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A82" s="33"/>
+      <c r="H81" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="J81" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K81" s="22"/>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A82" s="30"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
       <c r="D82" s="2"/>
       <c r="E82" s="2"/>
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
-      <c r="H82" s="2"/>
-      <c r="I82" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="K82" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L82" s="25"/>
-    </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A83" s="33"/>
+      <c r="H82" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="J82" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K82" s="22"/>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A83" s="30"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
       <c r="D83" s="2"/>
       <c r="E83" s="2"/>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
-      <c r="H83" s="2"/>
-      <c r="I83" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="K83" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L83" s="25"/>
-    </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A84" s="33"/>
+      <c r="H83" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="J83" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K83" s="22"/>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A84" s="30"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
       <c r="D84" s="2"/>
       <c r="E84" s="2"/>
       <c r="F84" s="2"/>
       <c r="G84" s="2"/>
-      <c r="H84" s="2"/>
-      <c r="I84" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="K84" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L84" s="25"/>
-    </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A85" s="33"/>
+      <c r="H84" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="J84" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K84" s="22"/>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A85" s="30"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
       <c r="D85" s="2"/>
       <c r="E85" s="2"/>
       <c r="F85" s="2"/>
       <c r="G85" s="2"/>
-      <c r="H85" s="2"/>
-      <c r="I85" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="K85" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L85" s="25"/>
-    </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A86" s="33"/>
+      <c r="H85" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="J85" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K85" s="22"/>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A86" s="30"/>
       <c r="B86" s="2">
         <v>2</v>
       </c>
-      <c r="C86" s="28" t="s">
-        <v>89</v>
+      <c r="C86" s="25" t="s">
+        <v>75</v>
       </c>
       <c r="D86" s="2"/>
       <c r="E86" s="2"/>
       <c r="F86" s="2"/>
-      <c r="G86" s="2"/>
-      <c r="H86" s="2"/>
-      <c r="I86" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="K86" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L86" s="25"/>
-    </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A87" s="33"/>
+      <c r="G86" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="J86" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K86" s="22"/>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A87" s="30"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
       <c r="D87" s="2"/>
       <c r="E87" s="2"/>
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
-      <c r="H87" s="2"/>
-      <c r="I87" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="K87" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L87" s="25"/>
-    </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A88" s="33"/>
+      <c r="H87" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="J87" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K87" s="22"/>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A88" s="30"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
       <c r="D88" s="2"/>
       <c r="E88" s="2"/>
       <c r="F88" s="2"/>
       <c r="G88" s="2"/>
-      <c r="H88" s="2"/>
-      <c r="I88" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="K88" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L88" s="25"/>
-    </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A89" s="33"/>
+      <c r="H88" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="J88" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K88" s="22"/>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A89" s="30"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
       <c r="D89" s="2"/>
       <c r="E89" s="2"/>
       <c r="F89" s="2"/>
       <c r="G89" s="2"/>
-      <c r="H89" s="2"/>
-      <c r="I89" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="K89" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L89" s="25"/>
-    </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A90" s="33"/>
+      <c r="H89" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="J89" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K89" s="22"/>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A90" s="30"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
       <c r="D90" s="2"/>
       <c r="E90" s="2"/>
       <c r="F90" s="2"/>
       <c r="G90" s="2"/>
-      <c r="H90" s="2"/>
-      <c r="I90" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="K90" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L90" s="25"/>
-    </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A91" s="33"/>
+      <c r="H90" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="J90" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K90" s="22"/>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A91" s="30"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
       <c r="D91" s="2"/>
       <c r="E91" s="2"/>
       <c r="F91" s="2"/>
       <c r="G91" s="2"/>
-      <c r="H91" s="2"/>
-      <c r="I91" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="K91" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L91" s="25"/>
-    </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A92" s="33"/>
+      <c r="H91" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="J91" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K91" s="22"/>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A92" s="30"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
       <c r="D92" s="2"/>
       <c r="E92" s="2"/>
       <c r="F92" s="2"/>
       <c r="G92" s="2"/>
-      <c r="H92" s="2"/>
-      <c r="I92" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="K92" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L92" s="25"/>
-    </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A93" s="33"/>
+      <c r="H92" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="J92" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K92" s="22"/>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A93" s="30"/>
       <c r="B93" s="2">
         <v>3</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E93" s="3"/>
-      <c r="F93" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G93" s="2">
+        <v>33</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F93" s="2">
         <v>6</v>
       </c>
+      <c r="G93" s="2" t="s">
+        <v>21</v>
+      </c>
       <c r="H93" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I93" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="K93" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L93" s="25"/>
-    </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A94" s="33"/>
+        <v>70</v>
+      </c>
+      <c r="J93" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K93" s="22"/>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A94" s="30"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
       <c r="D94" s="2"/>
       <c r="E94" s="2"/>
       <c r="F94" s="2"/>
       <c r="G94" s="2"/>
-      <c r="H94" s="2"/>
-      <c r="I94" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="K94" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L94" s="25"/>
-    </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A95" s="33"/>
+      <c r="H94" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J94" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K94" s="22"/>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A95" s="30"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
       <c r="D95" s="2"/>
       <c r="E95" s="2"/>
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
-      <c r="H95" s="2"/>
-      <c r="I95" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="K95" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L95" s="25"/>
-    </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A96" s="33"/>
+      <c r="H95" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="J95" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K95" s="22"/>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A96" s="30"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
       <c r="D96" s="2"/>
       <c r="E96" s="2"/>
       <c r="F96" s="2"/>
       <c r="G96" s="2"/>
-      <c r="H96" s="2"/>
-      <c r="I96" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="K96" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L96" s="25"/>
-    </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A97" s="33"/>
+      <c r="H96" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="J96" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K96" s="22"/>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A97" s="30"/>
       <c r="B97" s="2">
         <v>4</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="D97" s="2"/>
       <c r="E97" s="2"/>
       <c r="F97" s="2"/>
       <c r="G97" s="2"/>
-      <c r="H97" s="2"/>
-      <c r="I97" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="K97" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L97" s="25"/>
-    </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A98" s="33"/>
+      <c r="H97" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="J97" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K97" s="22"/>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A98" s="30"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
       <c r="D98" s="2"/>
       <c r="E98" s="2"/>
       <c r="F98" s="2"/>
       <c r="G98" s="2"/>
-      <c r="H98" s="2"/>
-      <c r="I98" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="K98" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L98" s="25"/>
-    </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A99" s="33"/>
+      <c r="H98" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="J98" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K98" s="22"/>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A99" s="30"/>
       <c r="B99" s="2">
         <v>5</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="D99" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E99" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E99" s="2">
-        <v>1</v>
-      </c>
-      <c r="F99" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="G99" s="2">
+      <c r="F99" s="2">
         <v>4</v>
       </c>
+      <c r="G99" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="H99" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I99" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="K99" s="27"/>
-      <c r="L99" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A100" s="33"/>
+        <v>112</v>
+      </c>
+      <c r="J99" s="24"/>
+      <c r="K99" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A100" s="30"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
       <c r="D100" s="2"/>
       <c r="E100" s="2"/>
       <c r="F100" s="2"/>
       <c r="G100" s="2"/>
-      <c r="H100" s="2"/>
-      <c r="I100" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="K100" s="27"/>
-      <c r="L100" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A101" s="33"/>
+      <c r="H100" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="J100" s="24"/>
+      <c r="K100" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A101" s="30"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
       <c r="D101" s="2"/>
       <c r="E101" s="2"/>
       <c r="F101" s="2"/>
       <c r="G101" s="2"/>
-      <c r="H101" s="2"/>
-      <c r="I101" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="K101" s="27"/>
-      <c r="L101" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A102" s="33"/>
+      <c r="H101" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="J101" s="24"/>
+      <c r="K101" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A102" s="30"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
       <c r="D102" s="2"/>
       <c r="E102" s="2"/>
       <c r="F102" s="2"/>
       <c r="G102" s="2"/>
-      <c r="H102" s="2"/>
-      <c r="I102" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="K102" s="27"/>
-      <c r="L102" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A103" s="33"/>
+      <c r="H102" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="J102" s="24"/>
+      <c r="K102" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A103" s="30"/>
       <c r="B103" s="2">
         <v>6</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="D103" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E103" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E103" s="2">
-        <v>1</v>
-      </c>
-      <c r="F103" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="G103" s="2">
+      <c r="F103" s="2">
         <v>4</v>
       </c>
+      <c r="G103" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="H103" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I103" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="K103" s="27"/>
-      <c r="L103" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A104" s="33"/>
+        <v>116</v>
+      </c>
+      <c r="J103" s="24"/>
+      <c r="K103" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A104" s="30"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
       <c r="D104" s="2"/>
       <c r="E104" s="2"/>
       <c r="F104" s="2"/>
       <c r="G104" s="2"/>
-      <c r="H104" s="2"/>
-      <c r="I104" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="K104" s="27"/>
-      <c r="L104" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A105" s="33"/>
+      <c r="H104" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="J104" s="24"/>
+      <c r="K104" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A105" s="30"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
       <c r="D105" s="2"/>
       <c r="E105" s="2"/>
       <c r="F105" s="2"/>
       <c r="G105" s="2"/>
-      <c r="H105" s="2"/>
-      <c r="I105" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="K105" s="27"/>
-      <c r="L105" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A106" s="34"/>
-      <c r="B106" s="14"/>
-      <c r="C106" s="14"/>
-      <c r="D106" s="14"/>
-      <c r="E106" s="14"/>
-      <c r="F106" s="14"/>
-      <c r="G106" s="14"/>
-      <c r="H106" s="14"/>
-      <c r="I106" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="J106" s="13"/>
-      <c r="K106" s="30"/>
-      <c r="L106" s="29" t="s">
-        <v>16</v>
+      <c r="H105" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="J105" s="24"/>
+      <c r="K105" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A106" s="31"/>
+      <c r="B106" s="12"/>
+      <c r="C106" s="12"/>
+      <c r="D106" s="12"/>
+      <c r="E106" s="12"/>
+      <c r="F106" s="12"/>
+      <c r="G106" s="12"/>
+      <c r="H106" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="I106" s="11"/>
+      <c r="J106" s="27"/>
+      <c r="K106" s="26" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -3262,23 +3219,35 @@
     <mergeCell ref="A40:A45"/>
     <mergeCell ref="A46:A70"/>
     <mergeCell ref="A71:A78"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A4:A21"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
     <mergeCell ref="A24:A27"/>
     <mergeCell ref="A28:A39"/>
+    <mergeCell ref="A4:A23"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:D106" xr:uid="{54349673-DDCB-4BF8-AD7A-57E435C3CD97}">
+      <formula1>"Tiles, Fitting"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:E106" xr:uid="{0F1F9BD4-1AB3-4E65-8808-72239849D00A}">
+      <formula1>"Round, Rectangle, Point"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G106" xr:uid="{55E61CC2-6F3B-4803-B406-60B5D74BA27B}">
+      <formula1>"LP,TMP"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="d7b47298-7dbc-4c4a-b955-e35738c83845" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3515,27 +3484,17 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="d7b47298-7dbc-4c4a-b955-e35738c83845" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE34F84B-F271-4B1B-8B21-90DAF7F40D50}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0006E415-A18B-4726-A1A0-54EC3A4B0653}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="4c7a27d0-c111-49d1-947f-3e415c425751"/>
-    <ds:schemaRef ds:uri="d7b47298-7dbc-4c4a-b955-e35738c83845"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3560,9 +3519,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0006E415-A18B-4726-A1A0-54EC3A4B0653}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE34F84B-F271-4B1B-8B21-90DAF7F40D50}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="4c7a27d0-c111-49d1-947f-3e415c425751"/>
+    <ds:schemaRef ds:uri="d7b47298-7dbc-4c4a-b955-e35738c83845"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>